--- a/COLM.xlsx
+++ b/COLM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7982EDEA-469A-4212-9792-EDDAECE2E972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9500B8A7-1E3A-41E8-A6E1-BD89BCC92DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{ECC62F7A-C70F-47CF-9717-8932D5683754}"/>
   </bookViews>
@@ -43,7 +43,7 @@
     <author>tc={02328662-4D88-4BC8-91D8-F530CF00DD0F}</author>
   </authors>
   <commentList>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{4511427A-6919-43BC-B48C-3A502B1E98A5}">
+    <comment ref="D15" authorId="0" shapeId="0" xr:uid="{4511427A-6919-43BC-B48C-3A502B1E98A5}">
       <text>
         <r>
           <rPr>
@@ -67,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M10" authorId="1" shapeId="0" xr:uid="{02328662-4D88-4BC8-91D8-F530CF00DD0F}">
+    <comment ref="M15" authorId="1" shapeId="0" xr:uid="{02328662-4D88-4BC8-91D8-F530CF00DD0F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
   <si>
     <t>COLM</t>
   </si>
@@ -225,6 +225,24 @@
   <si>
     <t>Q425</t>
   </si>
+  <si>
+    <t>CEO:</t>
+  </si>
+  <si>
+    <t>Timothy P. Boyle</t>
+  </si>
+  <si>
+    <t>FY24</t>
+  </si>
+  <si>
+    <t>FY25</t>
+  </si>
+  <si>
+    <t>SHOREL</t>
+  </si>
+  <si>
+    <t>FY23</t>
+  </si>
 </sst>
 </file>
 
@@ -332,7 +350,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -351,10 +369,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -697,7 +716,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="M10" dT="2025-12-14T11:31:57.34" personId="{1B5CE0B6-B2B8-49C3-A84C-CB0394E90054}" id="{02328662-4D88-4BC8-91D8-F530CF00DD0F}">
+  <threadedComment ref="M15" dT="2025-12-14T11:31:57.34" personId="{1B5CE0B6-B2B8-49C3-A84C-CB0394E90054}" id="{02328662-4D88-4BC8-91D8-F530CF00DD0F}">
     <text>29 $ mio Godwill Impairment</text>
   </threadedComment>
 </ThreadedComments>
@@ -725,7 +744,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="2">
-        <v>56.66</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -733,10 +752,10 @@
         <v>5</v>
       </c>
       <c r="I3" s="3">
-        <v>53.888891999999998</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>46</v>
+        <v>52.351551999999998</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -748,7 +767,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>3053.3446207199995</v>
+        <v>2880.3823910400001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -759,11 +778,11 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <f>228.832+7.195</f>
-        <v>236.02699999999999</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>46</v>
+        <f>442.028+348.766</f>
+        <v>790.7940000000001</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -773,12 +792,12 @@
       <c r="I6" s="3">
         <v>0</v>
       </c>
-      <c r="J6" s="14" t="s">
-        <v>46</v>
+      <c r="J6" s="15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>39</v>
       </c>
       <c r="H7" s="2" t="s">
@@ -786,7 +805,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>2817.3176207199995</v>
+        <v>2089.5883910399998</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -797,6 +816,12 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -816,7 +841,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B07C55-4E26-4518-8F85-A8F7E5C1C71D}">
-  <dimension ref="A1:AX343"/>
+  <dimension ref="A1:AX348"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -824,12 +849,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
@@ -866,1026 +891,1083 @@
       <c r="N2" s="9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="12">
-        <v>823.36500000000001</v>
-      </c>
-      <c r="E3" s="12">
-        <v>1853.232</v>
-      </c>
-      <c r="G3" s="12">
-        <v>619.05399999999997</v>
-      </c>
-      <c r="H3" s="12">
-        <v>463.94</v>
-      </c>
-      <c r="I3" s="12">
-        <v>1818.35</v>
-      </c>
-      <c r="J3" s="12">
-        <v>868.82299999999998</v>
-      </c>
-      <c r="K3" s="12">
-        <v>628.82000000000005</v>
-      </c>
-      <c r="L3" s="12">
-        <v>494.30200000000002</v>
-      </c>
-      <c r="M3" s="12">
-        <v>734.31500000000005</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="12">
-        <v>236.66900000000001</v>
-      </c>
-      <c r="E4" s="12">
-        <v>573.97699999999998</v>
-      </c>
-      <c r="G4" s="12">
-        <v>150.928</v>
-      </c>
-      <c r="H4" s="12">
-        <v>106.304</v>
-      </c>
-      <c r="I4" s="12">
-        <v>453.64400000000001</v>
-      </c>
-      <c r="J4" s="12">
-        <v>227.76400000000001</v>
-      </c>
-      <c r="K4" s="12">
-        <v>149.63200000000001</v>
-      </c>
-      <c r="L4" s="12">
-        <v>110.944</v>
-      </c>
-      <c r="M4" s="12">
-        <v>209.11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="12">
-        <v>456.4</v>
-      </c>
-      <c r="E5" s="12">
-        <v>1445.13</v>
-      </c>
-      <c r="G5" s="12">
-        <v>390.89699999999999</v>
-      </c>
-      <c r="H5" s="12">
-        <v>278.38400000000001</v>
-      </c>
-      <c r="I5" s="12">
-        <v>1274.498</v>
-      </c>
-      <c r="J5" s="12">
-        <v>459.85899999999998</v>
-      </c>
-      <c r="K5" s="12">
-        <v>399.76900000000001</v>
-      </c>
-      <c r="L5" s="12">
-        <v>317.21800000000002</v>
-      </c>
-      <c r="M5" s="12">
-        <v>605.21699999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="12">
-        <v>636.66099999999994</v>
-      </c>
-      <c r="E6" s="12">
-        <v>982.07899999999995</v>
-      </c>
-      <c r="G6" s="12">
-        <v>379.08499999999998</v>
-      </c>
-      <c r="H6" s="12">
-        <v>291.86</v>
-      </c>
-      <c r="I6" s="12">
-        <v>997.49599999999998</v>
-      </c>
-      <c r="J6" s="12">
-        <v>636.72799999999995</v>
-      </c>
-      <c r="K6" s="12">
-        <v>378.68299999999999</v>
-      </c>
-      <c r="L6" s="12">
-        <v>288.02800000000002</v>
-      </c>
-      <c r="M6" s="12">
-        <v>326.55099999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13">
-        <v>1059.9939999999999</v>
-      </c>
-      <c r="E7" s="13">
-        <v>985.68299999999999</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13">
-        <v>769.98199999999997</v>
-      </c>
-      <c r="H7" s="13">
-        <v>570.24400000000003</v>
-      </c>
-      <c r="I7" s="13">
-        <v>931.76800000000003</v>
-      </c>
-      <c r="J7" s="13">
-        <v>1096.587</v>
-      </c>
-      <c r="K7" s="13">
-        <v>778.452</v>
-      </c>
-      <c r="L7" s="13">
-        <v>605.24599999999998</v>
-      </c>
-      <c r="M7" s="13">
-        <v>943.42499999999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P2" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
+      <c r="Y3" s="12"/>
+      <c r="Z3" s="12"/>
+      <c r="AA3" s="12"/>
+      <c r="AB3" s="12"/>
+      <c r="AC3" s="12"/>
+      <c r="AD3" s="12"/>
+      <c r="AE3" s="12"/>
+      <c r="AF3" s="12"/>
+      <c r="AG3" s="12"/>
+      <c r="AH3" s="12"/>
+      <c r="AI3" s="12"/>
+      <c r="AJ3" s="12"/>
+      <c r="AK3" s="12"/>
+      <c r="AL3" s="12"/>
+      <c r="AM3" s="12"/>
+      <c r="AN3" s="12"/>
+      <c r="AO3" s="12"/>
+      <c r="AP3" s="12"/>
+      <c r="AQ3" s="12"/>
+      <c r="AR3" s="12"/>
+      <c r="AS3" s="12"/>
+      <c r="AT3" s="12"/>
+      <c r="AU3" s="12"/>
+      <c r="AV3" s="12"/>
+      <c r="AW3" s="12"/>
+      <c r="AX3" s="12"/>
+    </row>
+    <row r="4" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B4" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12">
+        <v>2971.1979999999999</v>
+      </c>
+      <c r="R4" s="12">
+        <v>2972.6149999999998</v>
+      </c>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="12"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="12"/>
+      <c r="AI4" s="12"/>
+      <c r="AJ4" s="12"/>
+      <c r="AK4" s="12"/>
+      <c r="AL4" s="12"/>
+      <c r="AM4" s="12"/>
+      <c r="AN4" s="12"/>
+      <c r="AO4" s="12"/>
+      <c r="AP4" s="12"/>
+      <c r="AQ4" s="12"/>
+      <c r="AR4" s="12"/>
+      <c r="AS4" s="12"/>
+      <c r="AT4" s="12"/>
+      <c r="AU4" s="12"/>
+      <c r="AV4" s="12"/>
+      <c r="AW4" s="12"/>
+      <c r="AX4" s="12"/>
+    </row>
+    <row r="5" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12">
+        <v>221.14099999999999</v>
+      </c>
+      <c r="R5" s="12">
+        <v>221.7</v>
+      </c>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="12"/>
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12"/>
+      <c r="AF5" s="12"/>
+      <c r="AG5" s="12"/>
+      <c r="AH5" s="12"/>
+      <c r="AI5" s="12"/>
+      <c r="AJ5" s="12"/>
+      <c r="AK5" s="12"/>
+      <c r="AL5" s="12"/>
+      <c r="AM5" s="12"/>
+      <c r="AN5" s="12"/>
+      <c r="AO5" s="12"/>
+      <c r="AP5" s="12"/>
+      <c r="AQ5" s="12"/>
+      <c r="AR5" s="12"/>
+      <c r="AS5" s="12"/>
+      <c r="AT5" s="12"/>
+      <c r="AU5" s="12"/>
+      <c r="AV5" s="12"/>
+      <c r="AW5" s="12"/>
+      <c r="AX5" s="12"/>
+    </row>
+    <row r="6" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B6" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12">
+        <v>102.81</v>
+      </c>
+      <c r="R6" s="12">
+        <v>102.79600000000001</v>
+      </c>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12"/>
+      <c r="AA6" s="12"/>
+      <c r="AB6" s="12"/>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="12"/>
+      <c r="AE6" s="12"/>
+      <c r="AF6" s="12"/>
+      <c r="AG6" s="12"/>
+      <c r="AH6" s="12"/>
+      <c r="AI6" s="12"/>
+      <c r="AJ6" s="12"/>
+      <c r="AK6" s="12"/>
+      <c r="AL6" s="12"/>
+      <c r="AM6" s="12"/>
+      <c r="AN6" s="12"/>
+      <c r="AO6" s="12"/>
+      <c r="AP6" s="12"/>
+      <c r="AQ6" s="12"/>
+      <c r="AR6" s="12"/>
+      <c r="AS6" s="12"/>
+      <c r="AT6" s="12"/>
+      <c r="AU6" s="12"/>
+      <c r="AV6" s="12"/>
+      <c r="AW6" s="12"/>
+      <c r="AX6" s="12"/>
+    </row>
+    <row r="7" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B7" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12">
+        <v>100.593</v>
+      </c>
+      <c r="R7" s="12">
+        <v>100.24</v>
+      </c>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="12"/>
+      <c r="AB7" s="12"/>
+      <c r="AC7" s="12"/>
+      <c r="AD7" s="12"/>
+      <c r="AE7" s="12"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+    </row>
+    <row r="8" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D8" s="12">
-        <v>523.80399999999997</v>
+        <v>823.36500000000001</v>
       </c>
       <c r="E8" s="12">
-        <v>505.48599999999999</v>
+        <v>1853.232</v>
       </c>
       <c r="G8" s="12">
-        <v>380.423</v>
+        <v>619.05399999999997</v>
       </c>
       <c r="H8" s="12">
-        <v>296.82499999999999</v>
+        <v>463.94</v>
       </c>
       <c r="I8" s="12">
-        <v>464.209</v>
+        <v>1818.35</v>
       </c>
       <c r="J8" s="12">
-        <v>536.03899999999999</v>
+        <v>868.82299999999998</v>
       </c>
       <c r="K8" s="12">
-        <v>382.39499999999998</v>
+        <v>628.82000000000005</v>
       </c>
       <c r="L8" s="12">
-        <v>308.13799999999998</v>
+        <v>494.30200000000002</v>
       </c>
       <c r="M8" s="12">
-        <v>471.60700000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+        <v>734.31500000000005</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>2712.7539999999999</v>
+      </c>
+      <c r="R8" s="12">
+        <v>2712.39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="12">
+        <v>236.66900000000001</v>
+      </c>
+      <c r="E9" s="12">
+        <v>573.97699999999998</v>
+      </c>
+      <c r="G9" s="12">
+        <v>150.928</v>
+      </c>
+      <c r="H9" s="12">
+        <v>106.304</v>
+      </c>
+      <c r="I9" s="12">
+        <v>453.64400000000001</v>
+      </c>
+      <c r="J9" s="12">
+        <v>227.76400000000001</v>
+      </c>
+      <c r="K9" s="12">
+        <v>149.63200000000001</v>
+      </c>
+      <c r="L9" s="12">
+        <v>110.944</v>
+      </c>
+      <c r="M9" s="12">
+        <v>209.11</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>682.98800000000006</v>
+      </c>
+      <c r="R9" s="12">
+        <v>684.96100000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="12">
+        <v>456.4</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1445.13</v>
+      </c>
+      <c r="G10" s="12">
+        <v>390.89699999999999</v>
+      </c>
+      <c r="H10" s="12">
+        <v>278.38400000000001</v>
+      </c>
+      <c r="I10" s="12">
+        <v>1274.498</v>
+      </c>
+      <c r="J10" s="12">
+        <v>459.85899999999998</v>
+      </c>
+      <c r="K10" s="12">
+        <v>399.76900000000001</v>
+      </c>
+      <c r="L10" s="12">
+        <v>317.21800000000002</v>
+      </c>
+      <c r="M10" s="12">
+        <v>605.21699999999998</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>1777.0930000000001</v>
+      </c>
+      <c r="R10" s="12">
+        <v>1780.5540000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="12">
+        <v>636.66099999999994</v>
+      </c>
+      <c r="E11" s="12">
+        <v>982.07899999999995</v>
+      </c>
+      <c r="G11" s="12">
+        <v>379.08499999999998</v>
+      </c>
+      <c r="H11" s="12">
+        <v>291.86</v>
+      </c>
+      <c r="I11" s="12">
+        <v>997.49599999999998</v>
+      </c>
+      <c r="J11" s="12">
+        <v>636.72799999999995</v>
+      </c>
+      <c r="K11" s="12">
+        <v>378.68299999999999</v>
+      </c>
+      <c r="L11" s="12">
+        <v>288.02800000000002</v>
+      </c>
+      <c r="M11" s="12">
+        <v>326.55099999999999</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>1618.6489999999999</v>
+      </c>
+      <c r="R11" s="12">
+        <v>1616.797</v>
+      </c>
+    </row>
+    <row r="12" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13">
+        <v>1059.9939999999999</v>
+      </c>
+      <c r="E12" s="13">
+        <v>985.68299999999999</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13">
+        <v>769.98199999999997</v>
+      </c>
+      <c r="H12" s="13">
+        <v>570.24400000000003</v>
+      </c>
+      <c r="I12" s="13">
+        <v>931.76800000000003</v>
+      </c>
+      <c r="J12" s="13">
+        <v>1096.587</v>
+      </c>
+      <c r="K12" s="13">
+        <v>778.452</v>
+      </c>
+      <c r="L12" s="13">
+        <v>605.24599999999998</v>
+      </c>
+      <c r="M12" s="13">
+        <v>943.42499999999995</v>
+      </c>
+      <c r="P12" s="13">
+        <v>3487.203</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>3368.5819999999999</v>
+      </c>
+      <c r="R12" s="13">
+        <v>3397.3510000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="12">
+        <v>523.80399999999997</v>
+      </c>
+      <c r="E13" s="12">
+        <v>505.48599999999999</v>
+      </c>
+      <c r="G13" s="12">
+        <v>380.423</v>
+      </c>
+      <c r="H13" s="12">
+        <v>296.82499999999999</v>
+      </c>
+      <c r="I13" s="12">
+        <v>464.209</v>
+      </c>
+      <c r="J13" s="12">
+        <v>536.03899999999999</v>
+      </c>
+      <c r="K13" s="12">
+        <v>382.39499999999998</v>
+      </c>
+      <c r="L13" s="12">
+        <v>308.13799999999998</v>
+      </c>
+      <c r="M13" s="12">
+        <v>471.60700000000003</v>
+      </c>
+      <c r="P13" s="12">
+        <v>1757.271</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>1677.4970000000001</v>
+      </c>
+      <c r="R13" s="12">
+        <v>1680.6289999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="12">
-        <f t="shared" ref="C9:H9" si="0">+C7-C8</f>
+      <c r="C14" s="12">
+        <f t="shared" ref="C14:H14" si="0">+C12-C13</f>
         <v>0</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D14" s="12">
         <f t="shared" si="0"/>
         <v>536.18999999999994</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E14" s="12">
         <f t="shared" si="0"/>
         <v>480.197</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F14" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G14" s="12">
         <f t="shared" si="0"/>
         <v>389.55899999999997</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H14" s="12">
         <f t="shared" si="0"/>
         <v>273.41900000000004</v>
       </c>
-      <c r="I9" s="12">
-        <f>+I7-I8</f>
+      <c r="I14" s="12">
+        <f>+I12-I13</f>
         <v>467.55900000000003</v>
       </c>
-      <c r="J9" s="12">
-        <f t="shared" ref="J9:N9" si="1">+J7-J8</f>
+      <c r="J14" s="12">
+        <f t="shared" ref="J14:R14" si="1">+J12-J13</f>
         <v>560.548</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K14" s="12">
         <f t="shared" si="1"/>
         <v>396.05700000000002</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L14" s="12">
         <f t="shared" si="1"/>
         <v>297.108</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M14" s="12">
         <f t="shared" si="1"/>
         <v>471.81799999999993</v>
       </c>
-      <c r="N9" s="12">
+      <c r="N14" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
+      <c r="P14" s="12">
+        <f t="shared" si="1"/>
+        <v>1729.932</v>
+      </c>
+      <c r="Q14" s="12">
+        <f t="shared" si="1"/>
+        <v>1691.0849999999998</v>
+      </c>
+      <c r="R14" s="12">
+        <f t="shared" si="1"/>
+        <v>1716.7220000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D15" s="12">
         <f>404.823+25</f>
         <v>429.82299999999998</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E15" s="12">
         <v>351.56299999999999</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G15" s="12">
         <v>349.27</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H15" s="12">
         <v>302.74900000000002</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I15" s="12">
         <v>361.24299999999999</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J15" s="12">
         <v>430.64499999999998</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K15" s="12">
         <v>354.471</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L15" s="12">
         <v>325.62799999999999</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M15" s="12">
         <f>380.892+29</f>
         <v>409.892</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="12">
-        <v>6.7069999999999999</v>
-      </c>
-      <c r="E11" s="12">
-        <v>5.92</v>
-      </c>
-      <c r="G11" s="12">
-        <v>4.3920000000000003</v>
-      </c>
-      <c r="H11" s="12">
-        <v>5.5279999999999996</v>
-      </c>
-      <c r="I11" s="12">
-        <v>6.2249999999999996</v>
-      </c>
-      <c r="J11" s="12">
-        <v>7.4180000000000001</v>
-      </c>
-      <c r="K11" s="12">
-        <v>4.9219999999999997</v>
-      </c>
-      <c r="L11" s="12">
-        <v>4.9290000000000003</v>
-      </c>
-      <c r="M11" s="12">
-        <v>5.46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="12">
-        <f t="shared" ref="C12:H12" si="2">+C9-C10+C11</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <f t="shared" si="2"/>
-        <v>113.07399999999996</v>
-      </c>
-      <c r="E12" s="12">
-        <f t="shared" si="2"/>
-        <v>134.554</v>
-      </c>
-      <c r="F12" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <f t="shared" si="2"/>
-        <v>44.68099999999999</v>
-      </c>
-      <c r="H12" s="12">
-        <f t="shared" si="2"/>
-        <v>-23.801999999999985</v>
-      </c>
-      <c r="I12" s="12">
-        <f>+I9-I10+I11</f>
-        <v>112.54100000000003</v>
-      </c>
-      <c r="J12" s="12">
-        <f t="shared" ref="J12:N12" si="3">+J9-J10+J11</f>
-        <v>137.32100000000003</v>
-      </c>
-      <c r="K12" s="12">
-        <f t="shared" si="3"/>
-        <v>46.50800000000001</v>
-      </c>
-      <c r="L12" s="12">
-        <f t="shared" si="3"/>
-        <v>-23.59099999999998</v>
-      </c>
-      <c r="M12" s="12">
-        <f t="shared" si="3"/>
-        <v>67.385999999999925</v>
-      </c>
-      <c r="N12" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="12">
-        <v>5.0279999999999996</v>
-      </c>
-      <c r="E13" s="12">
-        <v>1.87</v>
-      </c>
-      <c r="G13" s="12">
-        <v>9.1969999999999992</v>
-      </c>
-      <c r="H13" s="12">
-        <v>8.3439999999999994</v>
-      </c>
-      <c r="I13" s="12">
-        <v>5.3639999999999999</v>
-      </c>
-      <c r="J13" s="12">
-        <v>4.7969999999999997</v>
-      </c>
-      <c r="K13" s="12">
-        <v>6.8170000000000002</v>
-      </c>
-      <c r="L13" s="12">
-        <v>4.8380000000000001</v>
-      </c>
-      <c r="M13" s="12">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="12">
-        <v>1.867</v>
-      </c>
-      <c r="E14" s="12">
-        <v>-0.311</v>
-      </c>
-      <c r="G14" s="12">
-        <v>0.27100000000000002</v>
-      </c>
-      <c r="H14" s="12">
-        <v>0.47599999999999998</v>
-      </c>
-      <c r="I14" s="12">
-        <v>1.2829999999999999</v>
-      </c>
-      <c r="J14" s="12">
-        <v>-2.2869999999999999</v>
-      </c>
-      <c r="K14" s="12">
-        <v>1.5509999999999999</v>
-      </c>
-      <c r="L14" s="12">
-        <v>2.1640000000000001</v>
-      </c>
-      <c r="M14" s="12">
-        <v>0.73199999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="12">
-        <f t="shared" ref="C15:H15" si="4">+C12+SUM(C13:C14)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="12">
-        <f t="shared" si="4"/>
-        <v>119.96899999999995</v>
-      </c>
-      <c r="E15" s="12">
-        <f t="shared" si="4"/>
-        <v>136.113</v>
-      </c>
-      <c r="F15" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="12">
-        <f t="shared" si="4"/>
-        <v>54.148999999999987</v>
-      </c>
-      <c r="H15" s="12">
-        <f t="shared" si="4"/>
-        <v>-14.981999999999985</v>
-      </c>
-      <c r="I15" s="12">
-        <f>+I12+SUM(I13:I14)</f>
-        <v>119.18800000000003</v>
-      </c>
-      <c r="J15" s="12">
-        <f t="shared" ref="J15:N15" si="5">+J12+SUM(J13:J14)</f>
-        <v>139.83100000000002</v>
-      </c>
-      <c r="K15" s="12">
-        <f t="shared" si="5"/>
-        <v>54.876000000000012</v>
-      </c>
-      <c r="L15" s="12">
-        <f t="shared" si="5"/>
-        <v>-16.588999999999977</v>
-      </c>
-      <c r="M15" s="12">
-        <f t="shared" si="5"/>
-        <v>70.987999999999928</v>
-      </c>
-      <c r="N15" s="12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="P15" s="12">
+        <f>1416.313+25</f>
+        <v>1441.3130000000001</v>
+      </c>
+      <c r="Q15" s="12">
+        <v>1443.9059999999999</v>
+      </c>
+      <c r="R15" s="12">
+        <f>1502.506+29</f>
+        <v>1531.5060000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D16" s="12">
-        <v>26.629000000000001</v>
+        <v>6.7069999999999999</v>
       </c>
       <c r="E16" s="12">
-        <v>32.604999999999997</v>
+        <v>5.92</v>
       </c>
       <c r="G16" s="12">
-        <v>11.849</v>
+        <v>4.3920000000000003</v>
       </c>
       <c r="H16" s="12">
-        <v>-3.2410000000000001</v>
+        <v>5.5279999999999996</v>
       </c>
       <c r="I16" s="12">
-        <v>29.030999999999999</v>
+        <v>6.2249999999999996</v>
       </c>
       <c r="J16" s="12">
-        <v>37.274000000000001</v>
+        <v>7.4180000000000001</v>
       </c>
       <c r="K16" s="12">
-        <v>12.628</v>
+        <v>4.9219999999999997</v>
       </c>
       <c r="L16" s="12">
-        <v>-6.3929999999999998</v>
+        <v>4.9290000000000003</v>
       </c>
       <c r="M16" s="12">
-        <v>18.983000000000001</v>
+        <v>5.46</v>
+      </c>
+      <c r="P16" s="12">
+        <v>21.664999999999999</v>
+      </c>
+      <c r="Q16" s="12">
+        <v>23.562000000000001</v>
+      </c>
+      <c r="R16" s="12">
+        <v>21.823</v>
       </c>
     </row>
     <row r="17" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="12">
+        <f t="shared" ref="C17:H17" si="2">+C14-C15+C16</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="12">
+        <f t="shared" si="2"/>
+        <v>113.07399999999996</v>
+      </c>
+      <c r="E17" s="12">
+        <f t="shared" si="2"/>
+        <v>134.554</v>
+      </c>
+      <c r="F17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <f t="shared" si="2"/>
+        <v>44.68099999999999</v>
+      </c>
+      <c r="H17" s="12">
+        <f t="shared" si="2"/>
+        <v>-23.801999999999985</v>
+      </c>
+      <c r="I17" s="12">
+        <f>+I14-I15+I16</f>
+        <v>112.54100000000003</v>
+      </c>
+      <c r="J17" s="12">
+        <f t="shared" ref="J17:R17" si="3">+J14-J15+J16</f>
+        <v>137.32100000000003</v>
+      </c>
+      <c r="K17" s="12">
+        <f t="shared" si="3"/>
+        <v>46.50800000000001</v>
+      </c>
+      <c r="L17" s="12">
+        <f t="shared" si="3"/>
+        <v>-23.59099999999998</v>
+      </c>
+      <c r="M17" s="12">
+        <f t="shared" si="3"/>
+        <v>67.385999999999925</v>
+      </c>
+      <c r="N17" s="12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="12">
+        <f t="shared" si="3"/>
+        <v>310.28399999999993</v>
+      </c>
+      <c r="Q17" s="12">
+        <f t="shared" si="3"/>
+        <v>270.74099999999987</v>
+      </c>
+      <c r="R17" s="12">
+        <f t="shared" si="3"/>
+        <v>207.03900000000013</v>
+      </c>
+    </row>
+    <row r="18" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="12">
+        <v>5.0279999999999996</v>
+      </c>
+      <c r="E18" s="12">
+        <v>1.87</v>
+      </c>
+      <c r="G18" s="12">
+        <v>9.1969999999999992</v>
+      </c>
+      <c r="H18" s="12">
+        <v>8.3439999999999994</v>
+      </c>
+      <c r="I18" s="12">
+        <v>5.3639999999999999</v>
+      </c>
+      <c r="J18" s="12">
+        <v>4.7969999999999997</v>
+      </c>
+      <c r="K18" s="12">
+        <v>6.8170000000000002</v>
+      </c>
+      <c r="L18" s="12">
+        <v>4.8380000000000001</v>
+      </c>
+      <c r="M18" s="12">
+        <v>2.87</v>
+      </c>
+      <c r="P18" s="12">
+        <v>13.686999999999999</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>27.702999999999999</v>
+      </c>
+      <c r="R18" s="12">
+        <v>17.867000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="12">
+        <v>1.867</v>
+      </c>
+      <c r="E19" s="12">
+        <v>-0.311</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="H19" s="12">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="I19" s="12">
+        <v>1.2829999999999999</v>
+      </c>
+      <c r="J19" s="12">
+        <v>-2.2869999999999999</v>
+      </c>
+      <c r="K19" s="12">
+        <v>1.5509999999999999</v>
+      </c>
+      <c r="L19" s="12">
+        <v>2.1640000000000001</v>
+      </c>
+      <c r="M19" s="12">
+        <v>0.73199999999999998</v>
+      </c>
+      <c r="P19" s="12">
+        <v>2.2210000000000001</v>
+      </c>
+      <c r="Q19" s="12">
+        <v>-0.25700000000000001</v>
+      </c>
+      <c r="R19" s="12">
+        <v>4.718</v>
+      </c>
+    </row>
+    <row r="20" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="12">
+        <f t="shared" ref="C20:H20" si="4">+C17+SUM(C18:C19)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="12">
+        <f t="shared" si="4"/>
+        <v>119.96899999999995</v>
+      </c>
+      <c r="E20" s="12">
+        <f t="shared" si="4"/>
+        <v>136.113</v>
+      </c>
+      <c r="F20" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="12">
+        <f t="shared" si="4"/>
+        <v>54.148999999999987</v>
+      </c>
+      <c r="H20" s="12">
+        <f t="shared" si="4"/>
+        <v>-14.981999999999985</v>
+      </c>
+      <c r="I20" s="12">
+        <f>+I17+SUM(I18:I19)</f>
+        <v>119.18800000000003</v>
+      </c>
+      <c r="J20" s="12">
+        <f t="shared" ref="J20:R20" si="5">+J17+SUM(J18:J19)</f>
+        <v>139.83100000000002</v>
+      </c>
+      <c r="K20" s="12">
+        <f t="shared" si="5"/>
+        <v>54.876000000000012</v>
+      </c>
+      <c r="L20" s="12">
+        <f t="shared" si="5"/>
+        <v>-16.588999999999977</v>
+      </c>
+      <c r="M20" s="12">
+        <f t="shared" si="5"/>
+        <v>70.987999999999928</v>
+      </c>
+      <c r="N20" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="12">
+        <f t="shared" si="5"/>
+        <v>326.19199999999995</v>
+      </c>
+      <c r="Q20" s="12">
+        <f t="shared" si="5"/>
+        <v>298.1869999999999</v>
+      </c>
+      <c r="R20" s="12">
+        <f t="shared" si="5"/>
+        <v>229.62400000000014</v>
+      </c>
+    </row>
+    <row r="21" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="12">
+        <v>26.629000000000001</v>
+      </c>
+      <c r="E21" s="12">
+        <v>32.604999999999997</v>
+      </c>
+      <c r="G21" s="12">
+        <v>11.849</v>
+      </c>
+      <c r="H21" s="12">
+        <v>-3.2410000000000001</v>
+      </c>
+      <c r="I21" s="12">
+        <v>29.030999999999999</v>
+      </c>
+      <c r="J21" s="12">
+        <v>37.274000000000001</v>
+      </c>
+      <c r="K21" s="12">
+        <v>12.628</v>
+      </c>
+      <c r="L21" s="12">
+        <v>-6.3929999999999998</v>
+      </c>
+      <c r="M21" s="12">
+        <v>18.983000000000001</v>
+      </c>
+      <c r="P21" s="12">
+        <v>74.792000000000002</v>
+      </c>
+      <c r="Q21" s="12">
+        <v>74.914000000000001</v>
+      </c>
+      <c r="R21" s="12">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="12">
-        <f t="shared" ref="C17:H17" si="6">+C15-C16</f>
+      <c r="C22" s="12">
+        <f t="shared" ref="C22:H22" si="6">+C20-C21</f>
         <v>0</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D22" s="12">
         <f t="shared" si="6"/>
         <v>93.339999999999947</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E22" s="12">
         <f t="shared" si="6"/>
         <v>103.50800000000001</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F22" s="12">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G22" s="12">
         <f t="shared" si="6"/>
         <v>42.299999999999983</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H22" s="12">
         <f t="shared" si="6"/>
         <v>-11.740999999999985</v>
       </c>
-      <c r="I17" s="12">
-        <f>+I15-I16</f>
+      <c r="I22" s="12">
+        <f>+I20-I21</f>
         <v>90.157000000000039</v>
       </c>
-      <c r="J17" s="12">
-        <f t="shared" ref="J17:N17" si="7">+J15-J16</f>
+      <c r="J22" s="12">
+        <f t="shared" ref="J22:R22" si="7">+J20-J21</f>
         <v>102.55700000000002</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K22" s="12">
         <f t="shared" si="7"/>
         <v>42.248000000000012</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L22" s="12">
         <f t="shared" si="7"/>
         <v>-10.195999999999977</v>
       </c>
-      <c r="M17" s="12">
+      <c r="M22" s="12">
         <f t="shared" si="7"/>
         <v>52.004999999999924</v>
       </c>
-      <c r="N17" s="12">
+      <c r="N22" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="B19" s="2" t="s">
+      <c r="P22" s="12">
+        <f t="shared" si="7"/>
+        <v>251.39999999999995</v>
+      </c>
+      <c r="Q22" s="12">
+        <f t="shared" si="7"/>
+        <v>223.27299999999991</v>
+      </c>
+      <c r="R22" s="12">
+        <f t="shared" si="7"/>
+        <v>177.22400000000013</v>
+      </c>
+    </row>
+    <row r="23" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="7" t="e">
-        <f t="shared" ref="C19:I19" si="8">+C17/C20</f>
+      <c r="C24" s="7" t="e">
+        <f t="shared" ref="C24:I24" si="8">+C22/C25</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D24" s="7">
         <f t="shared" si="8"/>
         <v>1.5501378416979432</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E24" s="7">
         <f t="shared" si="8"/>
         <v>1.7012030767207942</v>
       </c>
-      <c r="F19" s="7" t="e">
+      <c r="F24" s="7" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G24" s="7">
         <f t="shared" si="8"/>
         <v>0.70708590341507416</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H24" s="7">
         <f t="shared" si="8"/>
         <v>-0.19868681569729046</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I24" s="7">
         <f t="shared" si="8"/>
         <v>1.5602145885610461</v>
       </c>
-      <c r="J19" s="7">
-        <f t="shared" ref="J19:N19" si="9">+J17/J20</f>
+      <c r="J24" s="7">
+        <f t="shared" ref="J24:R24" si="9">+J22/J25</f>
         <v>1.8101701496752334</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K24" s="7">
         <f t="shared" si="9"/>
         <v>0.75802921017691194</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L24" s="7">
         <f t="shared" si="9"/>
         <v>-0.1861365171513587</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M24" s="7">
         <f t="shared" si="9"/>
         <v>0.95352035203520213</v>
       </c>
-      <c r="N19" s="7" t="e">
+      <c r="N24" s="7" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
-      <c r="AE19" s="3"/>
-      <c r="AF19" s="3"/>
-      <c r="AG19" s="3"/>
-      <c r="AH19" s="3"/>
-      <c r="AI19" s="3"/>
-      <c r="AJ19" s="3"/>
-      <c r="AK19" s="3"/>
-      <c r="AL19" s="3"/>
-      <c r="AM19" s="3"/>
-      <c r="AN19" s="3"/>
-      <c r="AO19" s="3"/>
-      <c r="AP19" s="3"/>
-      <c r="AQ19" s="3"/>
-      <c r="AR19" s="3"/>
-      <c r="AS19" s="3"/>
-      <c r="AT19" s="3"/>
-      <c r="AU19" s="3"/>
-      <c r="AV19" s="3"/>
-      <c r="AW19" s="3"/>
-      <c r="AX19" s="3"/>
-    </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="B20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3">
-        <v>60.213999999999999</v>
-      </c>
-      <c r="E20" s="3">
-        <v>60.844000000000001</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3">
-        <v>59.823</v>
-      </c>
-      <c r="H20" s="3">
-        <v>59.093000000000004</v>
-      </c>
-      <c r="I20" s="3">
-        <v>57.784999999999997</v>
-      </c>
-      <c r="J20" s="3">
-        <v>56.655999999999999</v>
-      </c>
-      <c r="K20" s="11">
-        <v>55.734000000000002</v>
-      </c>
-      <c r="L20" s="3">
-        <v>54.777000000000001</v>
-      </c>
-      <c r="M20" s="3">
-        <v>54.54</v>
-      </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
-      <c r="AB20" s="3"/>
-      <c r="AC20" s="3"/>
-      <c r="AD20" s="3"/>
-      <c r="AE20" s="3"/>
-      <c r="AF20" s="3"/>
-      <c r="AG20" s="3"/>
-      <c r="AH20" s="3"/>
-      <c r="AI20" s="3"/>
-      <c r="AJ20" s="3"/>
-      <c r="AK20" s="3"/>
-      <c r="AL20" s="3"/>
-      <c r="AM20" s="3"/>
-      <c r="AN20" s="3"/>
-      <c r="AO20" s="3"/>
-      <c r="AP20" s="3"/>
-      <c r="AQ20" s="3"/>
-      <c r="AR20" s="3"/>
-      <c r="AS20" s="3"/>
-      <c r="AT20" s="3"/>
-      <c r="AU20" s="3"/>
-      <c r="AV20" s="3"/>
-      <c r="AW20" s="3"/>
-      <c r="AX20" s="3"/>
-    </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="3"/>
-      <c r="AB21" s="3"/>
-      <c r="AC21" s="3"/>
-      <c r="AD21" s="3"/>
-      <c r="AE21" s="3"/>
-      <c r="AF21" s="3"/>
-      <c r="AG21" s="3"/>
-      <c r="AH21" s="3"/>
-      <c r="AI21" s="3"/>
-      <c r="AJ21" s="3"/>
-      <c r="AK21" s="3"/>
-      <c r="AL21" s="3"/>
-      <c r="AM21" s="3"/>
-      <c r="AN21" s="3"/>
-      <c r="AO21" s="3"/>
-      <c r="AP21" s="3"/>
-      <c r="AQ21" s="3"/>
-      <c r="AR21" s="3"/>
-      <c r="AS21" s="3"/>
-      <c r="AT21" s="3"/>
-      <c r="AU21" s="3"/>
-      <c r="AV21" s="3"/>
-      <c r="AW21" s="3"/>
-      <c r="AX21" s="3"/>
-    </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="B22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="10" t="e">
-        <f t="shared" ref="G22:H22" si="10">+G7/C7-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H22" s="10">
-        <f t="shared" si="10"/>
-        <v>-0.46203091715613476</v>
-      </c>
-      <c r="I22" s="10">
-        <f>+I7/E7-1</f>
-        <v>-5.4698112882133443E-2</v>
-      </c>
-      <c r="J22" s="10" t="e">
-        <f t="shared" ref="J22" si="11">+J7/F7-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K22" s="10">
-        <f t="shared" ref="K22" si="12">+K7/G7-1</f>
-        <v>1.1000257148868542E-2</v>
-      </c>
-      <c r="L22" s="10">
-        <f t="shared" ref="L22" si="13">+L7/H7-1</f>
-        <v>6.1380742278743794E-2</v>
-      </c>
-      <c r="M22" s="10">
-        <f t="shared" ref="M22" si="14">+M7/I7-1</f>
-        <v>1.2510624962436934E-2</v>
-      </c>
-      <c r="N22" s="10">
-        <f t="shared" ref="N22" si="15">+N7/J7-1</f>
-        <v>-1</v>
-      </c>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="3"/>
-      <c r="AB22" s="3"/>
-      <c r="AC22" s="3"/>
-      <c r="AD22" s="3"/>
-      <c r="AE22" s="3"/>
-      <c r="AF22" s="3"/>
-      <c r="AG22" s="3"/>
-      <c r="AH22" s="3"/>
-      <c r="AI22" s="3"/>
-      <c r="AJ22" s="3"/>
-      <c r="AK22" s="3"/>
-      <c r="AL22" s="3"/>
-      <c r="AM22" s="3"/>
-      <c r="AN22" s="3"/>
-      <c r="AO22" s="3"/>
-      <c r="AP22" s="3"/>
-      <c r="AQ22" s="3"/>
-      <c r="AR22" s="3"/>
-      <c r="AS22" s="3"/>
-      <c r="AT22" s="3"/>
-      <c r="AU22" s="3"/>
-      <c r="AV22" s="3"/>
-      <c r="AW22" s="3"/>
-      <c r="AX22" s="3"/>
-    </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="B23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="8" t="e">
-        <f t="shared" ref="C23:H23" si="16">+C9/C7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D23" s="8">
-        <f t="shared" si="16"/>
-        <v>0.50584248590086356</v>
-      </c>
-      <c r="E23" s="8">
-        <f t="shared" si="16"/>
-        <v>0.48717183922214341</v>
-      </c>
-      <c r="F23" s="8" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G23" s="8">
-        <f t="shared" si="16"/>
-        <v>0.50593260621676872</v>
-      </c>
-      <c r="H23" s="8">
-        <f t="shared" si="16"/>
-        <v>0.47947720624855328</v>
-      </c>
-      <c r="I23" s="8">
-        <f>+I9/I7</f>
-        <v>0.50179765778605834</v>
-      </c>
-      <c r="J23" s="8">
-        <f t="shared" ref="J23:N23" si="17">+J9/J7</f>
-        <v>0.51117512791962705</v>
-      </c>
-      <c r="K23" s="8">
-        <f t="shared" si="17"/>
-        <v>0.50877510752108035</v>
-      </c>
-      <c r="L23" s="8">
-        <f t="shared" si="17"/>
-        <v>0.49088800256424664</v>
-      </c>
-      <c r="M23" s="8">
-        <f t="shared" si="17"/>
-        <v>0.50011182658928899</v>
-      </c>
-      <c r="N23" s="8" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
-      <c r="AA23" s="3"/>
-      <c r="AB23" s="3"/>
-      <c r="AC23" s="3"/>
-      <c r="AD23" s="3"/>
-      <c r="AE23" s="3"/>
-      <c r="AF23" s="3"/>
-      <c r="AG23" s="3"/>
-      <c r="AH23" s="3"/>
-      <c r="AI23" s="3"/>
-      <c r="AJ23" s="3"/>
-      <c r="AK23" s="3"/>
-      <c r="AL23" s="3"/>
-      <c r="AM23" s="3"/>
-      <c r="AN23" s="3"/>
-      <c r="AO23" s="3"/>
-      <c r="AP23" s="3"/>
-      <c r="AQ23" s="3"/>
-      <c r="AR23" s="3"/>
-      <c r="AS23" s="3"/>
-      <c r="AT23" s="3"/>
-      <c r="AU23" s="3"/>
-      <c r="AV23" s="3"/>
-      <c r="AW23" s="3"/>
-      <c r="AX23" s="3"/>
-    </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="B24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="8" t="e">
-        <f t="shared" ref="C24:H24" si="18">+C12/C7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D24" s="8">
-        <f t="shared" si="18"/>
-        <v>0.10667418872182292</v>
-      </c>
-      <c r="E24" s="8">
-        <f t="shared" si="18"/>
-        <v>0.1365083906286301</v>
-      </c>
-      <c r="F24" s="8" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G24" s="8">
-        <f t="shared" si="18"/>
-        <v>5.8028629240683541E-2</v>
-      </c>
-      <c r="H24" s="8">
-        <f t="shared" si="18"/>
-        <v>-4.174002707612879E-2</v>
-      </c>
-      <c r="I24" s="8">
-        <f>+I12/I7</f>
-        <v>0.12078221188106913</v>
-      </c>
-      <c r="J24" s="8">
-        <f t="shared" ref="J24:N24" si="19">+J12/J7</f>
-        <v>0.12522581427647786</v>
-      </c>
-      <c r="K24" s="8">
-        <f t="shared" si="19"/>
-        <v>5.9744210304553153E-2</v>
-      </c>
-      <c r="L24" s="8">
-        <f t="shared" si="19"/>
-        <v>-3.8977539711125692E-2</v>
-      </c>
-      <c r="M24" s="8">
-        <f t="shared" si="19"/>
-        <v>7.1426981477064874E-2</v>
-      </c>
-      <c r="N24" s="8" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
+      <c r="P24" s="7">
+        <f t="shared" si="9"/>
+        <v>4.105696367912202</v>
+      </c>
+      <c r="Q24" s="7">
+        <f t="shared" si="9"/>
+        <v>3.8275590146229392</v>
+      </c>
+      <c r="R24" s="7">
+        <f t="shared" si="9"/>
+        <v>3.2412304766085107</v>
+      </c>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
@@ -1921,60 +2003,48 @@
     </row>
     <row r="25" spans="1:50" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="8" t="e">
-        <f t="shared" ref="C25:H25" si="20">+C16/C15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D25" s="8">
-        <f t="shared" si="20"/>
-        <v>0.22196567446590379</v>
-      </c>
-      <c r="E25" s="8">
-        <f t="shared" si="20"/>
-        <v>0.23954361449677838</v>
-      </c>
-      <c r="F25" s="8" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G25" s="8">
-        <f t="shared" si="20"/>
-        <v>0.21882213891299937</v>
-      </c>
-      <c r="H25" s="8">
-        <f t="shared" si="20"/>
-        <v>0.21632625817647866</v>
-      </c>
-      <c r="I25" s="8">
-        <f>+I16/I15</f>
-        <v>0.24357317850790342</v>
-      </c>
-      <c r="J25" s="8">
-        <f t="shared" ref="J25:N25" si="21">+J16/J15</f>
-        <v>0.26656463874248199</v>
-      </c>
-      <c r="K25" s="8">
-        <f t="shared" si="21"/>
-        <v>0.23011881332458628</v>
-      </c>
-      <c r="L25" s="8">
-        <f t="shared" si="21"/>
-        <v>0.38537585146784065</v>
-      </c>
-      <c r="M25" s="8">
-        <f t="shared" si="21"/>
-        <v>0.2674113934749538</v>
-      </c>
-      <c r="N25" s="8" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3">
+        <v>60.213999999999999</v>
+      </c>
+      <c r="E25" s="3">
+        <v>60.844000000000001</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3">
+        <v>59.823</v>
+      </c>
+      <c r="H25" s="3">
+        <v>59.093000000000004</v>
+      </c>
+      <c r="I25" s="3">
+        <v>57.784999999999997</v>
+      </c>
+      <c r="J25" s="3">
+        <v>56.655999999999999</v>
+      </c>
+      <c r="K25" s="11">
+        <v>55.734000000000002</v>
+      </c>
+      <c r="L25" s="3">
+        <v>54.777000000000001</v>
+      </c>
+      <c r="M25" s="3">
+        <v>54.54</v>
+      </c>
+      <c r="N25" s="3"/>
       <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
+      <c r="P25" s="3">
+        <v>61.231999999999999</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>58.332999999999998</v>
+      </c>
+      <c r="R25" s="3">
+        <v>54.677999999999997</v>
+      </c>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -2059,22 +2129,55 @@
       <c r="AX26" s="3"/>
     </row>
     <row r="27" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
+      <c r="B27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="10" t="e">
+        <f t="shared" ref="G27:H27" si="10">+G12/C12-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H27" s="10">
+        <f t="shared" si="10"/>
+        <v>-0.46203091715613476</v>
+      </c>
+      <c r="I27" s="10">
+        <f>+I12/E12-1</f>
+        <v>-5.4698112882133443E-2</v>
+      </c>
+      <c r="J27" s="10" t="e">
+        <f t="shared" ref="J27" si="11">+J12/F12-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K27" s="10">
+        <f t="shared" ref="K27" si="12">+K12/G12-1</f>
+        <v>1.1000257148868542E-2</v>
+      </c>
+      <c r="L27" s="10">
+        <f t="shared" ref="L27" si="13">+L12/H12-1</f>
+        <v>6.1380742278743794E-2</v>
+      </c>
+      <c r="M27" s="10">
+        <f t="shared" ref="M27" si="14">+M12/I12-1</f>
+        <v>1.2510624962436934E-2</v>
+      </c>
+      <c r="N27" s="10">
+        <f t="shared" ref="N27" si="15">+N12/J12-1</f>
+        <v>-1</v>
+      </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
+      <c r="Q27" s="10">
+        <f t="shared" ref="Q27:R27" si="16">+Q12/P12-1</f>
+        <v>-3.4016086818002833E-2</v>
+      </c>
+      <c r="R27" s="10">
+        <f>+R12/Q12-1</f>
+        <v>8.5403888045474385E-3</v>
+      </c>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -2109,22 +2212,70 @@
       <c r="AX27" s="3"/>
     </row>
     <row r="28" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
+      <c r="B28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="8" t="e">
+        <f t="shared" ref="C28:H28" si="17">+C14/C12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D28" s="8">
+        <f t="shared" si="17"/>
+        <v>0.50584248590086356</v>
+      </c>
+      <c r="E28" s="8">
+        <f t="shared" si="17"/>
+        <v>0.48717183922214341</v>
+      </c>
+      <c r="F28" s="8" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G28" s="8">
+        <f t="shared" si="17"/>
+        <v>0.50593260621676872</v>
+      </c>
+      <c r="H28" s="8">
+        <f t="shared" si="17"/>
+        <v>0.47947720624855328</v>
+      </c>
+      <c r="I28" s="8">
+        <f>+I14/I12</f>
+        <v>0.50179765778605834</v>
+      </c>
+      <c r="J28" s="8">
+        <f t="shared" ref="J28:N28" si="18">+J14/J12</f>
+        <v>0.51117512791962705</v>
+      </c>
+      <c r="K28" s="8">
+        <f t="shared" si="18"/>
+        <v>0.50877510752108035</v>
+      </c>
+      <c r="L28" s="8">
+        <f t="shared" si="18"/>
+        <v>0.49088800256424664</v>
+      </c>
+      <c r="M28" s="8">
+        <f t="shared" si="18"/>
+        <v>0.50011182658928899</v>
+      </c>
+      <c r="N28" s="8" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
+      <c r="P28" s="8">
+        <f t="shared" ref="P28:R28" si="19">+P14/P12</f>
+        <v>0.49608009628346844</v>
+      </c>
+      <c r="Q28" s="8">
+        <f t="shared" si="19"/>
+        <v>0.50201687238131654</v>
+      </c>
+      <c r="R28" s="8">
+        <f t="shared" si="19"/>
+        <v>0.50531193273818342</v>
+      </c>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
@@ -2159,22 +2310,70 @@
       <c r="AX28" s="3"/>
     </row>
     <row r="29" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
+      <c r="B29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="8" t="e">
+        <f t="shared" ref="C29:H29" si="20">+C17/C12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D29" s="8">
+        <f t="shared" si="20"/>
+        <v>0.10667418872182292</v>
+      </c>
+      <c r="E29" s="8">
+        <f t="shared" si="20"/>
+        <v>0.1365083906286301</v>
+      </c>
+      <c r="F29" s="8" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G29" s="8">
+        <f t="shared" si="20"/>
+        <v>5.8028629240683541E-2</v>
+      </c>
+      <c r="H29" s="8">
+        <f t="shared" si="20"/>
+        <v>-4.174002707612879E-2</v>
+      </c>
+      <c r="I29" s="8">
+        <f>+I17/I12</f>
+        <v>0.12078221188106913</v>
+      </c>
+      <c r="J29" s="8">
+        <f t="shared" ref="J29:N29" si="21">+J17/J12</f>
+        <v>0.12522581427647786</v>
+      </c>
+      <c r="K29" s="8">
+        <f t="shared" si="21"/>
+        <v>5.9744210304553153E-2</v>
+      </c>
+      <c r="L29" s="8">
+        <f t="shared" si="21"/>
+        <v>-3.8977539711125692E-2</v>
+      </c>
+      <c r="M29" s="8">
+        <f t="shared" si="21"/>
+        <v>7.1426981477064874E-2</v>
+      </c>
+      <c r="N29" s="8" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
+      <c r="P29" s="8">
+        <f t="shared" ref="P29:R29" si="22">+P17/P12</f>
+        <v>8.8977900053423889E-2</v>
+      </c>
+      <c r="Q29" s="8">
+        <f t="shared" si="22"/>
+        <v>8.0372394081545256E-2</v>
+      </c>
+      <c r="R29" s="8">
+        <f t="shared" si="22"/>
+        <v>6.094130397477332E-2</v>
+      </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
@@ -2209,22 +2408,70 @@
       <c r="AX29" s="3"/>
     </row>
     <row r="30" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
+      <c r="B30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="8" t="e">
+        <f t="shared" ref="C30:H30" si="23">+C21/C20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D30" s="8">
+        <f t="shared" si="23"/>
+        <v>0.22196567446590379</v>
+      </c>
+      <c r="E30" s="8">
+        <f t="shared" si="23"/>
+        <v>0.23954361449677838</v>
+      </c>
+      <c r="F30" s="8" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G30" s="8">
+        <f t="shared" si="23"/>
+        <v>0.21882213891299937</v>
+      </c>
+      <c r="H30" s="8">
+        <f t="shared" si="23"/>
+        <v>0.21632625817647866</v>
+      </c>
+      <c r="I30" s="8">
+        <f>+I21/I20</f>
+        <v>0.24357317850790342</v>
+      </c>
+      <c r="J30" s="8">
+        <f t="shared" ref="J30:N30" si="24">+J21/J20</f>
+        <v>0.26656463874248199</v>
+      </c>
+      <c r="K30" s="8">
+        <f t="shared" si="24"/>
+        <v>0.23011881332458628</v>
+      </c>
+      <c r="L30" s="8">
+        <f t="shared" si="24"/>
+        <v>0.38537585146784065</v>
+      </c>
+      <c r="M30" s="8">
+        <f t="shared" si="24"/>
+        <v>0.2674113934749538</v>
+      </c>
+      <c r="N30" s="8" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
+      <c r="P30" s="8">
+        <f t="shared" ref="P30:R30" si="25">+P21/P20</f>
+        <v>0.22928827193799975</v>
+      </c>
+      <c r="Q30" s="8">
+        <f t="shared" si="25"/>
+        <v>0.25123160969458774</v>
+      </c>
+      <c r="R30" s="8">
+        <f t="shared" si="25"/>
+        <v>0.22819914294673016</v>
+      </c>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
@@ -17908,6 +18155,256 @@
       <c r="AW343" s="3"/>
       <c r="AX343" s="3"/>
     </row>
+    <row r="344" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="C344" s="3"/>
+      <c r="D344" s="3"/>
+      <c r="E344" s="3"/>
+      <c r="F344" s="3"/>
+      <c r="G344" s="3"/>
+      <c r="H344" s="3"/>
+      <c r="I344" s="3"/>
+      <c r="J344" s="3"/>
+      <c r="K344" s="3"/>
+      <c r="L344" s="3"/>
+      <c r="M344" s="3"/>
+      <c r="N344" s="3"/>
+      <c r="O344" s="3"/>
+      <c r="P344" s="3"/>
+      <c r="Q344" s="3"/>
+      <c r="R344" s="3"/>
+      <c r="S344" s="3"/>
+      <c r="T344" s="3"/>
+      <c r="U344" s="3"/>
+      <c r="V344" s="3"/>
+      <c r="W344" s="3"/>
+      <c r="X344" s="3"/>
+      <c r="Y344" s="3"/>
+      <c r="Z344" s="3"/>
+      <c r="AA344" s="3"/>
+      <c r="AB344" s="3"/>
+      <c r="AC344" s="3"/>
+      <c r="AD344" s="3"/>
+      <c r="AE344" s="3"/>
+      <c r="AF344" s="3"/>
+      <c r="AG344" s="3"/>
+      <c r="AH344" s="3"/>
+      <c r="AI344" s="3"/>
+      <c r="AJ344" s="3"/>
+      <c r="AK344" s="3"/>
+      <c r="AL344" s="3"/>
+      <c r="AM344" s="3"/>
+      <c r="AN344" s="3"/>
+      <c r="AO344" s="3"/>
+      <c r="AP344" s="3"/>
+      <c r="AQ344" s="3"/>
+      <c r="AR344" s="3"/>
+      <c r="AS344" s="3"/>
+      <c r="AT344" s="3"/>
+      <c r="AU344" s="3"/>
+      <c r="AV344" s="3"/>
+      <c r="AW344" s="3"/>
+      <c r="AX344" s="3"/>
+    </row>
+    <row r="345" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="C345" s="3"/>
+      <c r="D345" s="3"/>
+      <c r="E345" s="3"/>
+      <c r="F345" s="3"/>
+      <c r="G345" s="3"/>
+      <c r="H345" s="3"/>
+      <c r="I345" s="3"/>
+      <c r="J345" s="3"/>
+      <c r="K345" s="3"/>
+      <c r="L345" s="3"/>
+      <c r="M345" s="3"/>
+      <c r="N345" s="3"/>
+      <c r="O345" s="3"/>
+      <c r="P345" s="3"/>
+      <c r="Q345" s="3"/>
+      <c r="R345" s="3"/>
+      <c r="S345" s="3"/>
+      <c r="T345" s="3"/>
+      <c r="U345" s="3"/>
+      <c r="V345" s="3"/>
+      <c r="W345" s="3"/>
+      <c r="X345" s="3"/>
+      <c r="Y345" s="3"/>
+      <c r="Z345" s="3"/>
+      <c r="AA345" s="3"/>
+      <c r="AB345" s="3"/>
+      <c r="AC345" s="3"/>
+      <c r="AD345" s="3"/>
+      <c r="AE345" s="3"/>
+      <c r="AF345" s="3"/>
+      <c r="AG345" s="3"/>
+      <c r="AH345" s="3"/>
+      <c r="AI345" s="3"/>
+      <c r="AJ345" s="3"/>
+      <c r="AK345" s="3"/>
+      <c r="AL345" s="3"/>
+      <c r="AM345" s="3"/>
+      <c r="AN345" s="3"/>
+      <c r="AO345" s="3"/>
+      <c r="AP345" s="3"/>
+      <c r="AQ345" s="3"/>
+      <c r="AR345" s="3"/>
+      <c r="AS345" s="3"/>
+      <c r="AT345" s="3"/>
+      <c r="AU345" s="3"/>
+      <c r="AV345" s="3"/>
+      <c r="AW345" s="3"/>
+      <c r="AX345" s="3"/>
+    </row>
+    <row r="346" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="C346" s="3"/>
+      <c r="D346" s="3"/>
+      <c r="E346" s="3"/>
+      <c r="F346" s="3"/>
+      <c r="G346" s="3"/>
+      <c r="H346" s="3"/>
+      <c r="I346" s="3"/>
+      <c r="J346" s="3"/>
+      <c r="K346" s="3"/>
+      <c r="L346" s="3"/>
+      <c r="M346" s="3"/>
+      <c r="N346" s="3"/>
+      <c r="O346" s="3"/>
+      <c r="P346" s="3"/>
+      <c r="Q346" s="3"/>
+      <c r="R346" s="3"/>
+      <c r="S346" s="3"/>
+      <c r="T346" s="3"/>
+      <c r="U346" s="3"/>
+      <c r="V346" s="3"/>
+      <c r="W346" s="3"/>
+      <c r="X346" s="3"/>
+      <c r="Y346" s="3"/>
+      <c r="Z346" s="3"/>
+      <c r="AA346" s="3"/>
+      <c r="AB346" s="3"/>
+      <c r="AC346" s="3"/>
+      <c r="AD346" s="3"/>
+      <c r="AE346" s="3"/>
+      <c r="AF346" s="3"/>
+      <c r="AG346" s="3"/>
+      <c r="AH346" s="3"/>
+      <c r="AI346" s="3"/>
+      <c r="AJ346" s="3"/>
+      <c r="AK346" s="3"/>
+      <c r="AL346" s="3"/>
+      <c r="AM346" s="3"/>
+      <c r="AN346" s="3"/>
+      <c r="AO346" s="3"/>
+      <c r="AP346" s="3"/>
+      <c r="AQ346" s="3"/>
+      <c r="AR346" s="3"/>
+      <c r="AS346" s="3"/>
+      <c r="AT346" s="3"/>
+      <c r="AU346" s="3"/>
+      <c r="AV346" s="3"/>
+      <c r="AW346" s="3"/>
+      <c r="AX346" s="3"/>
+    </row>
+    <row r="347" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="C347" s="3"/>
+      <c r="D347" s="3"/>
+      <c r="E347" s="3"/>
+      <c r="F347" s="3"/>
+      <c r="G347" s="3"/>
+      <c r="H347" s="3"/>
+      <c r="I347" s="3"/>
+      <c r="J347" s="3"/>
+      <c r="K347" s="3"/>
+      <c r="L347" s="3"/>
+      <c r="M347" s="3"/>
+      <c r="N347" s="3"/>
+      <c r="O347" s="3"/>
+      <c r="P347" s="3"/>
+      <c r="Q347" s="3"/>
+      <c r="R347" s="3"/>
+      <c r="S347" s="3"/>
+      <c r="T347" s="3"/>
+      <c r="U347" s="3"/>
+      <c r="V347" s="3"/>
+      <c r="W347" s="3"/>
+      <c r="X347" s="3"/>
+      <c r="Y347" s="3"/>
+      <c r="Z347" s="3"/>
+      <c r="AA347" s="3"/>
+      <c r="AB347" s="3"/>
+      <c r="AC347" s="3"/>
+      <c r="AD347" s="3"/>
+      <c r="AE347" s="3"/>
+      <c r="AF347" s="3"/>
+      <c r="AG347" s="3"/>
+      <c r="AH347" s="3"/>
+      <c r="AI347" s="3"/>
+      <c r="AJ347" s="3"/>
+      <c r="AK347" s="3"/>
+      <c r="AL347" s="3"/>
+      <c r="AM347" s="3"/>
+      <c r="AN347" s="3"/>
+      <c r="AO347" s="3"/>
+      <c r="AP347" s="3"/>
+      <c r="AQ347" s="3"/>
+      <c r="AR347" s="3"/>
+      <c r="AS347" s="3"/>
+      <c r="AT347" s="3"/>
+      <c r="AU347" s="3"/>
+      <c r="AV347" s="3"/>
+      <c r="AW347" s="3"/>
+      <c r="AX347" s="3"/>
+    </row>
+    <row r="348" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="C348" s="3"/>
+      <c r="D348" s="3"/>
+      <c r="E348" s="3"/>
+      <c r="F348" s="3"/>
+      <c r="G348" s="3"/>
+      <c r="H348" s="3"/>
+      <c r="I348" s="3"/>
+      <c r="J348" s="3"/>
+      <c r="K348" s="3"/>
+      <c r="L348" s="3"/>
+      <c r="M348" s="3"/>
+      <c r="N348" s="3"/>
+      <c r="O348" s="3"/>
+      <c r="P348" s="3"/>
+      <c r="Q348" s="3"/>
+      <c r="R348" s="3"/>
+      <c r="S348" s="3"/>
+      <c r="T348" s="3"/>
+      <c r="U348" s="3"/>
+      <c r="V348" s="3"/>
+      <c r="W348" s="3"/>
+      <c r="X348" s="3"/>
+      <c r="Y348" s="3"/>
+      <c r="Z348" s="3"/>
+      <c r="AA348" s="3"/>
+      <c r="AB348" s="3"/>
+      <c r="AC348" s="3"/>
+      <c r="AD348" s="3"/>
+      <c r="AE348" s="3"/>
+      <c r="AF348" s="3"/>
+      <c r="AG348" s="3"/>
+      <c r="AH348" s="3"/>
+      <c r="AI348" s="3"/>
+      <c r="AJ348" s="3"/>
+      <c r="AK348" s="3"/>
+      <c r="AL348" s="3"/>
+      <c r="AM348" s="3"/>
+      <c r="AN348" s="3"/>
+      <c r="AO348" s="3"/>
+      <c r="AP348" s="3"/>
+      <c r="AQ348" s="3"/>
+      <c r="AR348" s="3"/>
+      <c r="AS348" s="3"/>
+      <c r="AT348" s="3"/>
+      <c r="AU348" s="3"/>
+      <c r="AV348" s="3"/>
+      <c r="AW348" s="3"/>
+      <c r="AX348" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{58E36728-A6A6-45EA-A9B9-57D79EA830A5}"/>

--- a/COLM.xlsx
+++ b/COLM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9500B8A7-1E3A-41E8-A6E1-BD89BCC92DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16C1ACD-9897-4316-B117-DF48B73C8E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{ECC62F7A-C70F-47CF-9717-8932D5683754}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{ECC62F7A-C70F-47CF-9717-8932D5683754}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <author>tc={02328662-4D88-4BC8-91D8-F530CF00DD0F}</author>
   </authors>
   <commentList>
-    <comment ref="D15" authorId="0" shapeId="0" xr:uid="{4511427A-6919-43BC-B48C-3A502B1E98A5}">
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{4511427A-6919-43BC-B48C-3A502B1E98A5}">
       <text>
         <r>
           <rPr>
@@ -67,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M15" authorId="1" shapeId="0" xr:uid="{02328662-4D88-4BC8-91D8-F530CF00DD0F}">
+    <comment ref="M14" authorId="1" shapeId="0" xr:uid="{02328662-4D88-4BC8-91D8-F530CF00DD0F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
   <si>
     <t>COLM</t>
   </si>
@@ -243,6 +243,18 @@
   <si>
     <t>FY23</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -252,13 +264,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -347,33 +365,36 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -716,7 +737,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="M15" dT="2025-12-14T11:31:57.34" personId="{1B5CE0B6-B2B8-49C3-A84C-CB0394E90054}" id="{02328662-4D88-4BC8-91D8-F530CF00DD0F}">
+  <threadedComment ref="M14" dT="2025-12-14T11:31:57.34" personId="{1B5CE0B6-B2B8-49C3-A84C-CB0394E90054}" id="{02328662-4D88-4BC8-91D8-F530CF00DD0F}">
     <text>29 $ mio Godwill Impairment</text>
   </threadedComment>
 </ThreadedComments>
@@ -744,7 +765,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="2">
-        <v>55.02</v>
+        <v>58.06</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -752,10 +773,10 @@
         <v>5</v>
       </c>
       <c r="I3" s="3">
-        <v>52.351551999999998</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>47</v>
+        <v>51.140793000000002</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -767,7 +788,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>2880.3823910400001</v>
+        <v>2969.2344415800003</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -778,11 +799,11 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <f>442.028+348.766</f>
-        <v>790.7940000000001</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>47</v>
+        <f>319.341+216.013</f>
+        <v>535.35400000000004</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -792,8 +813,8 @@
       <c r="I6" s="3">
         <v>0</v>
       </c>
-      <c r="J6" s="15" t="s">
-        <v>47</v>
+      <c r="J6" s="17" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -805,7 +826,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>2089.5883910399998</v>
+        <v>2433.8804415800005</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -841,7 +862,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B07C55-4E26-4518-8F85-A8F7E5C1C71D}">
-  <dimension ref="A1:AX348"/>
+  <dimension ref="A1:BB347"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -849,12 +870,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
@@ -891,17 +912,32 @@
       <c r="N2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="O2" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="T2" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="U2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="V2" s="15" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="B3" s="16" t="s">
+        <v>40</v>
+      </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
@@ -910,18 +946,26 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
+      <c r="K3" s="12">
+        <v>683.12099999999998</v>
+      </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
+      <c r="O3" s="12">
+        <v>690.149</v>
+      </c>
       <c r="P3" s="12"/>
       <c r="Q3" s="12"/>
       <c r="R3" s="12"/>
       <c r="S3" s="12"/>
       <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
-      <c r="V3" s="12"/>
+      <c r="U3" s="12">
+        <v>2971.1979999999999</v>
+      </c>
+      <c r="V3" s="12">
+        <v>2972.6149999999998</v>
+      </c>
       <c r="W3" s="12"/>
       <c r="X3" s="12"/>
       <c r="Y3" s="12"/>
@@ -950,10 +994,14 @@
       <c r="AV3" s="12"/>
       <c r="AW3" s="12"/>
       <c r="AX3" s="12"/>
-    </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY3" s="12"/>
+      <c r="AZ3" s="12"/>
+      <c r="BA3" s="12"/>
+      <c r="BB3" s="12"/>
+    </row>
+    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
       <c r="B4" s="16" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -963,22 +1011,26 @@
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
+      <c r="K4" s="12">
+        <v>42.204999999999998</v>
+      </c>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
+      <c r="O4" s="12">
+        <v>37.162999999999997</v>
+      </c>
       <c r="P4" s="12"/>
-      <c r="Q4" s="12">
-        <v>2971.1979999999999</v>
-      </c>
-      <c r="R4" s="12">
-        <v>2972.6149999999998</v>
-      </c>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
       <c r="S4" s="12"/>
       <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
+      <c r="U4" s="12">
+        <v>221.14099999999999</v>
+      </c>
+      <c r="V4" s="12">
+        <v>221.7</v>
+      </c>
       <c r="W4" s="12"/>
       <c r="X4" s="12"/>
       <c r="Y4" s="12"/>
@@ -1007,10 +1059,14 @@
       <c r="AV4" s="12"/>
       <c r="AW4" s="12"/>
       <c r="AX4" s="12"/>
-    </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY4" s="12"/>
+      <c r="AZ4" s="12"/>
+      <c r="BA4" s="12"/>
+      <c r="BB4" s="12"/>
+    </row>
+    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -1020,22 +1076,26 @@
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="K5" s="12">
+        <v>28.114000000000001</v>
+      </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
+      <c r="O5" s="12">
+        <v>26.661000000000001</v>
+      </c>
       <c r="P5" s="12"/>
-      <c r="Q5" s="12">
-        <v>221.14099999999999</v>
-      </c>
-      <c r="R5" s="12">
-        <v>221.7</v>
-      </c>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
       <c r="S5" s="12"/>
       <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
+      <c r="U5" s="12">
+        <v>102.81</v>
+      </c>
+      <c r="V5" s="12">
+        <v>102.79600000000001</v>
+      </c>
       <c r="W5" s="12"/>
       <c r="X5" s="12"/>
       <c r="Y5" s="12"/>
@@ -1064,10 +1124,14 @@
       <c r="AV5" s="12"/>
       <c r="AW5" s="12"/>
       <c r="AX5" s="12"/>
-    </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY5" s="12"/>
+      <c r="AZ5" s="12"/>
+      <c r="BA5" s="12"/>
+      <c r="BB5" s="12"/>
+    </row>
+    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
       <c r="B6" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
@@ -1077,22 +1141,26 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="K6" s="12">
+        <v>25.012</v>
+      </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
+      <c r="O6" s="12">
+        <v>25.04</v>
+      </c>
       <c r="P6" s="12"/>
-      <c r="Q6" s="12">
-        <v>102.81</v>
-      </c>
-      <c r="R6" s="12">
-        <v>102.79600000000001</v>
-      </c>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
       <c r="S6" s="12"/>
       <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
+      <c r="U6" s="12">
+        <v>100.593</v>
+      </c>
+      <c r="V6" s="12">
+        <v>100.24</v>
+      </c>
       <c r="W6" s="12"/>
       <c r="X6" s="12"/>
       <c r="Y6" s="12"/>
@@ -1121,857 +1189,939 @@
       <c r="AV6" s="12"/>
       <c r="AW6" s="12"/>
       <c r="AX6" s="12"/>
-    </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="B7" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12">
-        <v>100.593</v>
-      </c>
-      <c r="R7" s="12">
-        <v>100.24</v>
-      </c>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="12"/>
-      <c r="AB7" s="12"/>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="12"/>
-      <c r="AE7" s="12"/>
-      <c r="AF7" s="12"/>
-      <c r="AG7" s="12"/>
-      <c r="AH7" s="12"/>
-      <c r="AI7" s="12"/>
-      <c r="AJ7" s="12"/>
-      <c r="AK7" s="12"/>
-      <c r="AL7" s="12"/>
-      <c r="AM7" s="12"/>
-      <c r="AN7" s="12"/>
-      <c r="AO7" s="12"/>
-      <c r="AP7" s="12"/>
-      <c r="AQ7" s="12"/>
-      <c r="AR7" s="12"/>
-      <c r="AS7" s="12"/>
-      <c r="AT7" s="12"/>
-      <c r="AU7" s="12"/>
-      <c r="AV7" s="12"/>
-      <c r="AW7" s="12"/>
-      <c r="AX7" s="12"/>
-    </row>
-    <row r="8" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AY6" s="12"/>
+      <c r="AZ6" s="12"/>
+      <c r="BA6" s="12"/>
+      <c r="BB6" s="12"/>
+    </row>
+    <row r="7" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="12">
+        <v>823.36500000000001</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1853.232</v>
+      </c>
+      <c r="G7" s="12">
+        <v>619.05399999999997</v>
+      </c>
+      <c r="H7" s="12">
+        <v>463.94</v>
+      </c>
+      <c r="I7" s="12">
+        <v>1818.35</v>
+      </c>
+      <c r="J7" s="12">
+        <v>868.82299999999998</v>
+      </c>
+      <c r="K7" s="12">
+        <v>628.82000000000005</v>
+      </c>
+      <c r="L7" s="12">
+        <v>494.30200000000002</v>
+      </c>
+      <c r="M7" s="12">
+        <v>734.31500000000005</v>
+      </c>
+      <c r="O7" s="12">
+        <v>623.09299999999996</v>
+      </c>
+      <c r="U7" s="12">
+        <v>2712.7539999999999</v>
+      </c>
+      <c r="V7" s="12">
+        <v>2712.39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="12">
-        <v>823.36500000000001</v>
+        <v>236.66900000000001</v>
       </c>
       <c r="E8" s="12">
-        <v>1853.232</v>
+        <v>573.97699999999998</v>
       </c>
       <c r="G8" s="12">
-        <v>619.05399999999997</v>
+        <v>150.928</v>
       </c>
       <c r="H8" s="12">
-        <v>463.94</v>
+        <v>106.304</v>
       </c>
       <c r="I8" s="12">
-        <v>1818.35</v>
+        <v>453.64400000000001</v>
       </c>
       <c r="J8" s="12">
-        <v>868.82299999999998</v>
+        <v>227.76400000000001</v>
       </c>
       <c r="K8" s="12">
-        <v>628.82000000000005</v>
+        <v>149.63200000000001</v>
       </c>
       <c r="L8" s="12">
-        <v>494.30200000000002</v>
+        <v>110.944</v>
       </c>
       <c r="M8" s="12">
-        <v>734.31500000000005</v>
-      </c>
-      <c r="Q8" s="12">
-        <v>2712.7539999999999</v>
-      </c>
-      <c r="R8" s="12">
-        <v>2712.39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+        <v>209.11</v>
+      </c>
+      <c r="O8" s="12">
+        <v>155.91999999999999</v>
+      </c>
+      <c r="U8" s="12">
+        <v>682.98800000000006</v>
+      </c>
+      <c r="V8" s="12">
+        <v>684.96100000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="12">
-        <v>236.66900000000001</v>
+        <v>456.4</v>
       </c>
       <c r="E9" s="12">
-        <v>573.97699999999998</v>
+        <v>1445.13</v>
       </c>
       <c r="G9" s="12">
-        <v>150.928</v>
+        <v>390.89699999999999</v>
       </c>
       <c r="H9" s="12">
-        <v>106.304</v>
+        <v>278.38400000000001</v>
       </c>
       <c r="I9" s="12">
-        <v>453.64400000000001</v>
+        <v>1274.498</v>
       </c>
       <c r="J9" s="12">
-        <v>227.76400000000001</v>
+        <v>459.85899999999998</v>
       </c>
       <c r="K9" s="12">
-        <v>149.63200000000001</v>
+        <v>399.76900000000001</v>
       </c>
       <c r="L9" s="12">
-        <v>110.944</v>
+        <v>317.21800000000002</v>
       </c>
       <c r="M9" s="12">
-        <v>209.11</v>
-      </c>
-      <c r="Q9" s="12">
-        <v>682.98800000000006</v>
-      </c>
-      <c r="R9" s="12">
-        <v>684.96100000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+        <v>605.21699999999998</v>
+      </c>
+      <c r="O9" s="12">
+        <v>401.072</v>
+      </c>
+      <c r="U9" s="12">
+        <v>1777.0930000000001</v>
+      </c>
+      <c r="V9" s="12">
+        <v>1780.5540000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="12">
-        <v>456.4</v>
+        <v>636.66099999999994</v>
       </c>
       <c r="E10" s="12">
-        <v>1445.13</v>
+        <v>982.07899999999995</v>
       </c>
       <c r="G10" s="12">
-        <v>390.89699999999999</v>
+        <v>379.08499999999998</v>
       </c>
       <c r="H10" s="12">
-        <v>278.38400000000001</v>
+        <v>291.86</v>
       </c>
       <c r="I10" s="12">
-        <v>1274.498</v>
+        <v>997.49599999999998</v>
       </c>
       <c r="J10" s="12">
-        <v>459.85899999999998</v>
+        <v>636.72799999999995</v>
       </c>
       <c r="K10" s="12">
-        <v>399.76900000000001</v>
+        <v>378.68299999999999</v>
       </c>
       <c r="L10" s="12">
-        <v>317.21800000000002</v>
+        <v>288.02800000000002</v>
       </c>
       <c r="M10" s="12">
-        <v>605.21699999999998</v>
-      </c>
-      <c r="Q10" s="12">
-        <v>1777.0930000000001</v>
-      </c>
-      <c r="R10" s="12">
-        <v>1780.5540000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+        <v>326.55099999999999</v>
+      </c>
+      <c r="O10" s="12">
+        <v>377.94099999999997</v>
+      </c>
+      <c r="U10" s="12">
+        <v>1618.6489999999999</v>
+      </c>
+      <c r="V10" s="12">
+        <v>1616.797</v>
+      </c>
+    </row>
+    <row r="11" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="12">
-        <v>636.66099999999994</v>
-      </c>
-      <c r="E11" s="12">
-        <v>982.07899999999995</v>
-      </c>
-      <c r="G11" s="12">
-        <v>379.08499999999998</v>
-      </c>
-      <c r="H11" s="12">
-        <v>291.86</v>
-      </c>
-      <c r="I11" s="12">
-        <v>997.49599999999998</v>
-      </c>
-      <c r="J11" s="12">
-        <v>636.72799999999995</v>
-      </c>
-      <c r="K11" s="12">
-        <v>378.68299999999999</v>
-      </c>
-      <c r="L11" s="12">
-        <v>288.02800000000002</v>
-      </c>
-      <c r="M11" s="12">
-        <v>326.55099999999999</v>
-      </c>
-      <c r="Q11" s="12">
-        <v>1618.6489999999999</v>
-      </c>
-      <c r="R11" s="12">
-        <v>1616.797</v>
-      </c>
-    </row>
-    <row r="12" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13">
+        <v>1059.9939999999999</v>
+      </c>
+      <c r="E11" s="13">
+        <v>985.68299999999999</v>
+      </c>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13">
+        <v>769.98199999999997</v>
+      </c>
+      <c r="H11" s="13">
+        <v>570.24400000000003</v>
+      </c>
+      <c r="I11" s="13">
+        <v>931.76800000000003</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1096.587</v>
+      </c>
+      <c r="K11" s="13">
+        <v>778.452</v>
+      </c>
+      <c r="L11" s="13">
+        <v>605.24599999999998</v>
+      </c>
+      <c r="M11" s="13">
+        <v>943.42499999999995</v>
+      </c>
+      <c r="O11" s="13">
+        <v>779.01300000000003</v>
+      </c>
+      <c r="T11" s="13">
+        <v>3487.203</v>
+      </c>
+      <c r="U11" s="13">
+        <v>3368.5819999999999</v>
+      </c>
+      <c r="V11" s="13">
+        <v>3397.3510000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
-      <c r="B12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13">
-        <v>1059.9939999999999</v>
-      </c>
-      <c r="E12" s="13">
-        <v>985.68299999999999</v>
-      </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13">
-        <v>769.98199999999997</v>
-      </c>
-      <c r="H12" s="13">
-        <v>570.24400000000003</v>
-      </c>
-      <c r="I12" s="13">
-        <v>931.76800000000003</v>
-      </c>
-      <c r="J12" s="13">
-        <v>1096.587</v>
-      </c>
-      <c r="K12" s="13">
-        <v>778.452</v>
-      </c>
-      <c r="L12" s="13">
-        <v>605.24599999999998</v>
-      </c>
-      <c r="M12" s="13">
-        <v>943.42499999999995</v>
-      </c>
-      <c r="P12" s="13">
-        <v>3487.203</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>3368.5819999999999</v>
-      </c>
-      <c r="R12" s="13">
-        <v>3397.3510000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="12">
+        <v>523.80399999999997</v>
+      </c>
+      <c r="E12" s="12">
+        <v>505.48599999999999</v>
+      </c>
+      <c r="G12" s="12">
+        <v>380.423</v>
+      </c>
+      <c r="H12" s="12">
+        <v>296.82499999999999</v>
+      </c>
+      <c r="I12" s="12">
+        <v>464.209</v>
+      </c>
+      <c r="J12" s="12">
+        <v>536.03899999999999</v>
+      </c>
+      <c r="K12" s="12">
+        <v>382.39499999999998</v>
+      </c>
+      <c r="L12" s="12">
+        <v>308.13799999999998</v>
+      </c>
+      <c r="M12" s="12">
+        <v>471.60700000000003</v>
+      </c>
+      <c r="O12" s="12">
+        <v>384.05099999999999</v>
+      </c>
+      <c r="T12" s="12">
+        <v>1757.271</v>
+      </c>
+      <c r="U12" s="12">
+        <v>1677.4970000000001</v>
+      </c>
+      <c r="V12" s="12">
+        <v>1680.6289999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="C13" s="12">
+        <f t="shared" ref="C13:H13" si="0">+C11-C12</f>
+        <v>0</v>
       </c>
       <c r="D13" s="12">
-        <v>523.80399999999997</v>
+        <f t="shared" si="0"/>
+        <v>536.18999999999994</v>
       </c>
       <c r="E13" s="12">
-        <v>505.48599999999999</v>
+        <f t="shared" si="0"/>
+        <v>480.197</v>
+      </c>
+      <c r="F13" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G13" s="12">
-        <v>380.423</v>
+        <f t="shared" si="0"/>
+        <v>389.55899999999997</v>
       </c>
       <c r="H13" s="12">
-        <v>296.82499999999999</v>
+        <f t="shared" si="0"/>
+        <v>273.41900000000004</v>
       </c>
       <c r="I13" s="12">
-        <v>464.209</v>
+        <f>+I11-I12</f>
+        <v>467.55900000000003</v>
       </c>
       <c r="J13" s="12">
-        <v>536.03899999999999</v>
+        <f t="shared" ref="J13:V13" si="1">+J11-J12</f>
+        <v>560.548</v>
       </c>
       <c r="K13" s="12">
-        <v>382.39499999999998</v>
+        <f t="shared" si="1"/>
+        <v>396.05700000000002</v>
       </c>
       <c r="L13" s="12">
-        <v>308.13799999999998</v>
+        <f t="shared" si="1"/>
+        <v>297.108</v>
       </c>
       <c r="M13" s="12">
-        <v>471.60700000000003</v>
-      </c>
-      <c r="P13" s="12">
-        <v>1757.271</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>1677.4970000000001</v>
-      </c>
-      <c r="R13" s="12">
-        <v>1680.6289999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>471.81799999999993</v>
+      </c>
+      <c r="N13" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="12">
+        <f t="shared" si="1"/>
+        <v>394.96200000000005</v>
+      </c>
+      <c r="T13" s="12">
+        <f t="shared" si="1"/>
+        <v>1729.932</v>
+      </c>
+      <c r="U13" s="12">
+        <f t="shared" si="1"/>
+        <v>1691.0849999999998</v>
+      </c>
+      <c r="V13" s="12">
+        <f t="shared" si="1"/>
+        <v>1716.7220000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="12">
-        <f t="shared" ref="C14:H14" si="0">+C12-C13</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D14" s="12">
-        <f t="shared" si="0"/>
-        <v>536.18999999999994</v>
+        <f>404.823+25</f>
+        <v>429.82299999999998</v>
       </c>
       <c r="E14" s="12">
-        <f t="shared" si="0"/>
-        <v>480.197</v>
-      </c>
-      <c r="F14" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>351.56299999999999</v>
       </c>
       <c r="G14" s="12">
-        <f t="shared" si="0"/>
-        <v>389.55899999999997</v>
+        <v>349.27</v>
       </c>
       <c r="H14" s="12">
-        <f t="shared" si="0"/>
-        <v>273.41900000000004</v>
+        <v>302.74900000000002</v>
       </c>
       <c r="I14" s="12">
-        <f>+I12-I13</f>
-        <v>467.55900000000003</v>
+        <v>361.24299999999999</v>
       </c>
       <c r="J14" s="12">
-        <f t="shared" ref="J14:R14" si="1">+J12-J13</f>
-        <v>560.548</v>
+        <v>430.64499999999998</v>
       </c>
       <c r="K14" s="12">
-        <f t="shared" si="1"/>
-        <v>396.05700000000002</v>
+        <v>354.471</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="1"/>
-        <v>297.108</v>
+        <v>325.62799999999999</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" si="1"/>
-        <v>471.81799999999993</v>
-      </c>
-      <c r="N14" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="12">
-        <f t="shared" si="1"/>
-        <v>1729.932</v>
-      </c>
-      <c r="Q14" s="12">
-        <f t="shared" si="1"/>
-        <v>1691.0849999999998</v>
-      </c>
-      <c r="R14" s="12">
-        <f t="shared" si="1"/>
-        <v>1716.7220000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+        <f>380.892+29</f>
+        <v>409.892</v>
+      </c>
+      <c r="O14" s="12">
+        <v>357.137</v>
+      </c>
+      <c r="T14" s="12">
+        <f>1416.313+25</f>
+        <v>1441.3130000000001</v>
+      </c>
+      <c r="U14" s="12">
+        <v>1443.9059999999999</v>
+      </c>
+      <c r="V14" s="12">
+        <f>1502.506+29</f>
+        <v>1531.5060000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="12">
-        <f>404.823+25</f>
-        <v>429.82299999999998</v>
+        <v>6.7069999999999999</v>
       </c>
       <c r="E15" s="12">
-        <v>351.56299999999999</v>
+        <v>5.92</v>
       </c>
       <c r="G15" s="12">
-        <v>349.27</v>
+        <v>4.3920000000000003</v>
       </c>
       <c r="H15" s="12">
-        <v>302.74900000000002</v>
+        <v>5.5279999999999996</v>
       </c>
       <c r="I15" s="12">
-        <v>361.24299999999999</v>
+        <v>6.2249999999999996</v>
       </c>
       <c r="J15" s="12">
-        <v>430.64499999999998</v>
+        <v>7.4180000000000001</v>
       </c>
       <c r="K15" s="12">
-        <v>354.471</v>
+        <v>4.9219999999999997</v>
       </c>
       <c r="L15" s="12">
-        <v>325.62799999999999</v>
+        <v>4.9290000000000003</v>
       </c>
       <c r="M15" s="12">
-        <f>380.892+29</f>
-        <v>409.892</v>
-      </c>
-      <c r="P15" s="12">
-        <f>1416.313+25</f>
-        <v>1441.3130000000001</v>
-      </c>
-      <c r="Q15" s="12">
-        <v>1443.9059999999999</v>
-      </c>
-      <c r="R15" s="12">
-        <f>1502.506+29</f>
-        <v>1531.5060000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+        <v>5.46</v>
+      </c>
+      <c r="O15" s="12">
+        <v>4.1680000000000001</v>
+      </c>
+      <c r="T15" s="12">
+        <v>21.664999999999999</v>
+      </c>
+      <c r="U15" s="12">
+        <v>23.562000000000001</v>
+      </c>
+      <c r="V15" s="12">
+        <v>21.823</v>
+      </c>
+    </row>
+    <row r="16" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="C16" s="12">
+        <f t="shared" ref="C16:H16" si="2">+C13-C14+C15</f>
+        <v>0</v>
       </c>
       <c r="D16" s="12">
-        <v>6.7069999999999999</v>
+        <f t="shared" si="2"/>
+        <v>113.07399999999996</v>
       </c>
       <c r="E16" s="12">
-        <v>5.92</v>
+        <f t="shared" si="2"/>
+        <v>134.554</v>
+      </c>
+      <c r="F16" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G16" s="12">
-        <v>4.3920000000000003</v>
+        <f t="shared" si="2"/>
+        <v>44.68099999999999</v>
       </c>
       <c r="H16" s="12">
-        <v>5.5279999999999996</v>
+        <f t="shared" si="2"/>
+        <v>-23.801999999999985</v>
       </c>
       <c r="I16" s="12">
-        <v>6.2249999999999996</v>
+        <f>+I13-I14+I15</f>
+        <v>112.54100000000003</v>
       </c>
       <c r="J16" s="12">
-        <v>7.4180000000000001</v>
+        <f t="shared" ref="J16:V16" si="3">+J13-J14+J15</f>
+        <v>137.32100000000003</v>
       </c>
       <c r="K16" s="12">
-        <v>4.9219999999999997</v>
+        <f t="shared" si="3"/>
+        <v>46.50800000000001</v>
       </c>
       <c r="L16" s="12">
-        <v>4.9290000000000003</v>
+        <f t="shared" si="3"/>
+        <v>-23.59099999999998</v>
       </c>
       <c r="M16" s="12">
-        <v>5.46</v>
-      </c>
-      <c r="P16" s="12">
-        <v>21.664999999999999</v>
-      </c>
-      <c r="Q16" s="12">
-        <v>23.562000000000001</v>
-      </c>
-      <c r="R16" s="12">
-        <v>21.823</v>
-      </c>
-    </row>
-    <row r="17" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>67.385999999999925</v>
+      </c>
+      <c r="N16" s="12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="12">
+        <f t="shared" si="3"/>
+        <v>41.993000000000045</v>
+      </c>
+      <c r="T16" s="12">
+        <f t="shared" si="3"/>
+        <v>310.28399999999993</v>
+      </c>
+      <c r="U16" s="12">
+        <f t="shared" si="3"/>
+        <v>270.74099999999987</v>
+      </c>
+      <c r="V16" s="12">
+        <f t="shared" si="3"/>
+        <v>207.03900000000013</v>
+      </c>
+    </row>
+    <row r="17" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="12">
-        <f t="shared" ref="C17:H17" si="2">+C14-C15+C16</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D17" s="12">
-        <f t="shared" si="2"/>
-        <v>113.07399999999996</v>
+        <v>5.0279999999999996</v>
       </c>
       <c r="E17" s="12">
-        <f t="shared" si="2"/>
-        <v>134.554</v>
-      </c>
-      <c r="F17" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="G17" s="12">
-        <f t="shared" si="2"/>
-        <v>44.68099999999999</v>
+        <v>9.1969999999999992</v>
       </c>
       <c r="H17" s="12">
-        <f t="shared" si="2"/>
-        <v>-23.801999999999985</v>
+        <v>8.3439999999999994</v>
       </c>
       <c r="I17" s="12">
-        <f>+I14-I15+I16</f>
-        <v>112.54100000000003</v>
+        <v>5.3639999999999999</v>
       </c>
       <c r="J17" s="12">
-        <f t="shared" ref="J17:R17" si="3">+J14-J15+J16</f>
-        <v>137.32100000000003</v>
+        <v>4.7969999999999997</v>
       </c>
       <c r="K17" s="12">
-        <f t="shared" si="3"/>
-        <v>46.50800000000001</v>
+        <v>6.8170000000000002</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" si="3"/>
-        <v>-23.59099999999998</v>
+        <v>4.8380000000000001</v>
       </c>
       <c r="M17" s="12">
-        <f t="shared" si="3"/>
-        <v>67.385999999999925</v>
-      </c>
-      <c r="N17" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="12">
-        <f t="shared" si="3"/>
-        <v>310.28399999999993</v>
-      </c>
-      <c r="Q17" s="12">
-        <f t="shared" si="3"/>
-        <v>270.74099999999987</v>
-      </c>
-      <c r="R17" s="12">
-        <f t="shared" si="3"/>
-        <v>207.03900000000013</v>
-      </c>
-    </row>
-    <row r="18" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+        <v>2.87</v>
+      </c>
+      <c r="O17" s="12">
+        <v>4.883</v>
+      </c>
+      <c r="T17" s="12">
+        <v>13.686999999999999</v>
+      </c>
+      <c r="U17" s="12">
+        <v>27.702999999999999</v>
+      </c>
+      <c r="V17" s="12">
+        <v>17.867000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" s="12">
-        <v>5.0279999999999996</v>
+        <v>1.867</v>
       </c>
       <c r="E18" s="12">
-        <v>1.87</v>
+        <v>-0.311</v>
       </c>
       <c r="G18" s="12">
-        <v>9.1969999999999992</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="H18" s="12">
-        <v>8.3439999999999994</v>
+        <v>0.47599999999999998</v>
       </c>
       <c r="I18" s="12">
-        <v>5.3639999999999999</v>
+        <v>1.2829999999999999</v>
       </c>
       <c r="J18" s="12">
-        <v>4.7969999999999997</v>
+        <v>-2.2869999999999999</v>
       </c>
       <c r="K18" s="12">
-        <v>6.8170000000000002</v>
+        <v>1.5509999999999999</v>
       </c>
       <c r="L18" s="12">
-        <v>4.8380000000000001</v>
+        <v>2.1640000000000001</v>
       </c>
       <c r="M18" s="12">
-        <v>2.87</v>
-      </c>
-      <c r="P18" s="12">
-        <v>13.686999999999999</v>
-      </c>
-      <c r="Q18" s="12">
-        <v>27.702999999999999</v>
-      </c>
-      <c r="R18" s="12">
-        <v>17.867000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+        <v>0.73199999999999998</v>
+      </c>
+      <c r="O18" s="12">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="T18" s="12">
+        <v>2.2210000000000001</v>
+      </c>
+      <c r="U18" s="12">
+        <v>-0.25700000000000001</v>
+      </c>
+      <c r="V18" s="12">
+        <v>4.718</v>
+      </c>
+    </row>
+    <row r="19" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="C19" s="12">
+        <f t="shared" ref="C19:H19" si="4">+C16+SUM(C17:C18)</f>
+        <v>0</v>
       </c>
       <c r="D19" s="12">
-        <v>1.867</v>
+        <f t="shared" si="4"/>
+        <v>119.96899999999995</v>
       </c>
       <c r="E19" s="12">
-        <v>-0.311</v>
+        <f t="shared" si="4"/>
+        <v>136.113</v>
+      </c>
+      <c r="F19" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="G19" s="12">
-        <v>0.27100000000000002</v>
+        <f t="shared" si="4"/>
+        <v>54.148999999999987</v>
       </c>
       <c r="H19" s="12">
-        <v>0.47599999999999998</v>
+        <f t="shared" si="4"/>
+        <v>-14.981999999999985</v>
       </c>
       <c r="I19" s="12">
-        <v>1.2829999999999999</v>
+        <f>+I16+SUM(I17:I18)</f>
+        <v>119.18800000000003</v>
       </c>
       <c r="J19" s="12">
-        <v>-2.2869999999999999</v>
+        <f t="shared" ref="J19:V19" si="5">+J16+SUM(J17:J18)</f>
+        <v>139.83100000000002</v>
       </c>
       <c r="K19" s="12">
-        <v>1.5509999999999999</v>
+        <f t="shared" si="5"/>
+        <v>54.876000000000012</v>
       </c>
       <c r="L19" s="12">
-        <v>2.1640000000000001</v>
+        <f t="shared" si="5"/>
+        <v>-16.588999999999977</v>
       </c>
       <c r="M19" s="12">
-        <v>0.73199999999999998</v>
-      </c>
-      <c r="P19" s="12">
-        <v>2.2210000000000001</v>
-      </c>
-      <c r="Q19" s="12">
-        <v>-0.25700000000000001</v>
-      </c>
-      <c r="R19" s="12">
-        <v>4.718</v>
-      </c>
-    </row>
-    <row r="20" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="5"/>
+        <v>70.987999999999928</v>
+      </c>
+      <c r="N19" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="12">
+        <f t="shared" si="5"/>
+        <v>47.273000000000046</v>
+      </c>
+      <c r="T19" s="12">
+        <f t="shared" si="5"/>
+        <v>326.19199999999995</v>
+      </c>
+      <c r="U19" s="12">
+        <f t="shared" si="5"/>
+        <v>298.1869999999999</v>
+      </c>
+      <c r="V19" s="12">
+        <f t="shared" si="5"/>
+        <v>229.62400000000014</v>
+      </c>
+    </row>
+    <row r="20" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="12">
-        <f t="shared" ref="C20:H20" si="4">+C17+SUM(C18:C19)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D20" s="12">
-        <f t="shared" si="4"/>
-        <v>119.96899999999995</v>
+        <v>26.629000000000001</v>
       </c>
       <c r="E20" s="12">
-        <f t="shared" si="4"/>
-        <v>136.113</v>
-      </c>
-      <c r="F20" s="12">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>32.604999999999997</v>
       </c>
       <c r="G20" s="12">
-        <f t="shared" si="4"/>
-        <v>54.148999999999987</v>
+        <v>11.849</v>
       </c>
       <c r="H20" s="12">
-        <f t="shared" si="4"/>
-        <v>-14.981999999999985</v>
+        <v>-3.2410000000000001</v>
       </c>
       <c r="I20" s="12">
-        <f>+I17+SUM(I18:I19)</f>
-        <v>119.18800000000003</v>
+        <v>29.030999999999999</v>
       </c>
       <c r="J20" s="12">
-        <f t="shared" ref="J20:R20" si="5">+J17+SUM(J18:J19)</f>
-        <v>139.83100000000002</v>
+        <v>37.274000000000001</v>
       </c>
       <c r="K20" s="12">
-        <f t="shared" si="5"/>
-        <v>54.876000000000012</v>
+        <v>12.628</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" si="5"/>
-        <v>-16.588999999999977</v>
+        <v>-6.3929999999999998</v>
       </c>
       <c r="M20" s="12">
-        <f t="shared" si="5"/>
-        <v>70.987999999999928</v>
-      </c>
-      <c r="N20" s="12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="12">
-        <f t="shared" si="5"/>
-        <v>326.19199999999995</v>
-      </c>
-      <c r="Q20" s="12">
-        <f t="shared" si="5"/>
-        <v>298.1869999999999</v>
-      </c>
-      <c r="R20" s="12">
-        <f t="shared" si="5"/>
-        <v>229.62400000000014</v>
-      </c>
-    </row>
-    <row r="21" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
+        <v>18.983000000000001</v>
+      </c>
+      <c r="O20" s="12">
+        <v>12.965</v>
+      </c>
+      <c r="T20" s="12">
+        <v>74.792000000000002</v>
+      </c>
+      <c r="U20" s="12">
+        <v>74.914000000000001</v>
+      </c>
+      <c r="V20" s="12">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="C21" s="12">
+        <f t="shared" ref="C21:H21" si="6">+C19-C20</f>
+        <v>0</v>
       </c>
       <c r="D21" s="12">
-        <v>26.629000000000001</v>
-      </c>
-      <c r="E21" s="12">
-        <v>32.604999999999997</v>
-      </c>
-      <c r="G21" s="12">
-        <v>11.849</v>
-      </c>
-      <c r="H21" s="12">
-        <v>-3.2410000000000001</v>
-      </c>
-      <c r="I21" s="12">
-        <v>29.030999999999999</v>
-      </c>
-      <c r="J21" s="12">
-        <v>37.274000000000001</v>
-      </c>
-      <c r="K21" s="12">
-        <v>12.628</v>
-      </c>
-      <c r="L21" s="12">
-        <v>-6.3929999999999998</v>
-      </c>
-      <c r="M21" s="12">
-        <v>18.983000000000001</v>
-      </c>
-      <c r="P21" s="12">
-        <v>74.792000000000002</v>
-      </c>
-      <c r="Q21" s="12">
-        <v>74.914000000000001</v>
-      </c>
-      <c r="R21" s="12">
-        <v>52.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="12">
-        <f t="shared" ref="C22:H22" si="6">+C20-C21</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="12">
         <f t="shared" si="6"/>
         <v>93.339999999999947</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E21" s="12">
         <f t="shared" si="6"/>
         <v>103.50800000000001</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F21" s="12">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G21" s="12">
         <f t="shared" si="6"/>
         <v>42.299999999999983</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H21" s="12">
         <f t="shared" si="6"/>
         <v>-11.740999999999985</v>
       </c>
-      <c r="I22" s="12">
-        <f>+I20-I21</f>
+      <c r="I21" s="12">
+        <f>+I19-I20</f>
         <v>90.157000000000039</v>
       </c>
-      <c r="J22" s="12">
-        <f t="shared" ref="J22:R22" si="7">+J20-J21</f>
+      <c r="J21" s="12">
+        <f t="shared" ref="J21:V21" si="7">+J19-J20</f>
         <v>102.55700000000002</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K21" s="12">
         <f t="shared" si="7"/>
         <v>42.248000000000012</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L21" s="12">
         <f t="shared" si="7"/>
         <v>-10.195999999999977</v>
       </c>
-      <c r="M22" s="12">
+      <c r="M21" s="12">
         <f t="shared" si="7"/>
         <v>52.004999999999924</v>
       </c>
-      <c r="N22" s="12">
+      <c r="N21" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="P22" s="12">
+      <c r="O21" s="12">
+        <f t="shared" si="7"/>
+        <v>34.30800000000005</v>
+      </c>
+      <c r="T21" s="12">
         <f t="shared" si="7"/>
         <v>251.39999999999995</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="U21" s="12">
         <f t="shared" si="7"/>
         <v>223.27299999999991</v>
       </c>
-      <c r="R22" s="12">
+      <c r="V21" s="12">
         <f t="shared" si="7"/>
         <v>177.22400000000013</v>
       </c>
     </row>
-    <row r="23" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="B24" s="2" t="s">
+    <row r="22" spans="1:54" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="7" t="e">
-        <f t="shared" ref="C24:I24" si="8">+C22/C25</f>
+      <c r="C23" s="7" t="e">
+        <f t="shared" ref="C23:I23" si="8">+C21/C24</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D23" s="7">
         <f t="shared" si="8"/>
         <v>1.5501378416979432</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E23" s="7">
         <f t="shared" si="8"/>
         <v>1.7012030767207942</v>
       </c>
-      <c r="F24" s="7" t="e">
+      <c r="F23" s="7" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G23" s="7">
         <f t="shared" si="8"/>
         <v>0.70708590341507416</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H23" s="7">
         <f t="shared" si="8"/>
         <v>-0.19868681569729046</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I23" s="7">
         <f t="shared" si="8"/>
         <v>1.5602145885610461</v>
       </c>
-      <c r="J24" s="7">
-        <f t="shared" ref="J24:R24" si="9">+J22/J25</f>
+      <c r="J23" s="7">
+        <f t="shared" ref="J23:V23" si="9">+J21/J24</f>
         <v>1.8101701496752334</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K23" s="7">
         <f t="shared" si="9"/>
         <v>0.75802921017691194</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L23" s="7">
         <f t="shared" si="9"/>
         <v>-0.1861365171513587</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M23" s="7">
         <f t="shared" si="9"/>
         <v>0.95352035203520213</v>
       </c>
-      <c r="N24" s="7" t="e">
+      <c r="N23" s="7" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="7">
+      <c r="O23" s="7">
+        <f t="shared" si="9"/>
+        <v>0.65190871605829803</v>
+      </c>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="7">
         <f t="shared" si="9"/>
         <v>4.105696367912202</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="U23" s="7">
         <f t="shared" si="9"/>
         <v>3.8275590146229392</v>
       </c>
-      <c r="R24" s="7">
+      <c r="V23" s="7">
         <f t="shared" si="9"/>
         <v>3.2412304766085107</v>
       </c>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+      <c r="AH23" s="3"/>
+      <c r="AI23" s="3"/>
+      <c r="AJ23" s="3"/>
+      <c r="AK23" s="3"/>
+      <c r="AL23" s="3"/>
+      <c r="AM23" s="3"/>
+      <c r="AN23" s="3"/>
+      <c r="AO23" s="3"/>
+      <c r="AP23" s="3"/>
+      <c r="AQ23" s="3"/>
+      <c r="AR23" s="3"/>
+      <c r="AS23" s="3"/>
+      <c r="AT23" s="3"/>
+      <c r="AU23" s="3"/>
+      <c r="AV23" s="3"/>
+      <c r="AW23" s="3"/>
+      <c r="AX23" s="3"/>
+      <c r="AY23" s="3"/>
+      <c r="AZ23" s="3"/>
+      <c r="BA23" s="3"/>
+      <c r="BB23" s="3"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="B24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3">
+        <v>60.213999999999999</v>
+      </c>
+      <c r="E24" s="3">
+        <v>60.844000000000001</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3">
+        <v>59.823</v>
+      </c>
+      <c r="H24" s="3">
+        <v>59.093000000000004</v>
+      </c>
+      <c r="I24" s="3">
+        <v>57.784999999999997</v>
+      </c>
+      <c r="J24" s="3">
+        <v>56.655999999999999</v>
+      </c>
+      <c r="K24" s="11">
+        <v>55.734000000000002</v>
+      </c>
+      <c r="L24" s="3">
+        <v>54.777000000000001</v>
+      </c>
+      <c r="M24" s="3">
+        <v>54.54</v>
+      </c>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3">
+        <v>52.627000000000002</v>
+      </c>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
       <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
+      <c r="T24" s="3">
+        <v>61.231999999999999</v>
+      </c>
+      <c r="U24" s="3">
+        <v>58.332999999999998</v>
+      </c>
+      <c r="V24" s="3">
+        <v>54.677999999999997</v>
+      </c>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
@@ -2000,51 +2150,28 @@
       <c r="AV24" s="3"/>
       <c r="AW24" s="3"/>
       <c r="AX24" s="3"/>
-    </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="AY24" s="3"/>
+      <c r="AZ24" s="3"/>
+      <c r="BA24" s="3"/>
+      <c r="BB24" s="3"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.2">
       <c r="C25" s="3"/>
-      <c r="D25" s="3">
-        <v>60.213999999999999</v>
-      </c>
-      <c r="E25" s="3">
-        <v>60.844000000000001</v>
-      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="3">
-        <v>59.823</v>
-      </c>
-      <c r="H25" s="3">
-        <v>59.093000000000004</v>
-      </c>
-      <c r="I25" s="3">
-        <v>57.784999999999997</v>
-      </c>
-      <c r="J25" s="3">
-        <v>56.655999999999999</v>
-      </c>
-      <c r="K25" s="11">
-        <v>55.734000000000002</v>
-      </c>
-      <c r="L25" s="3">
-        <v>54.777000000000001</v>
-      </c>
-      <c r="M25" s="3">
-        <v>54.54</v>
-      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
-      <c r="P25" s="3">
-        <v>61.231999999999999</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>58.332999999999998</v>
-      </c>
-      <c r="R25" s="3">
-        <v>54.677999999999997</v>
-      </c>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -2077,28 +2204,68 @@
       <c r="AV25" s="3"/>
       <c r="AW25" s="3"/>
       <c r="AX25" s="3"/>
-    </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
+      <c r="AY25" s="3"/>
+      <c r="AZ25" s="3"/>
+      <c r="BA25" s="3"/>
+      <c r="BB25" s="3"/>
+    </row>
+    <row r="26" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="B26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="10" t="e">
+        <f t="shared" ref="G26:H26" si="10">+G11/C11-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H26" s="10">
+        <f t="shared" si="10"/>
+        <v>-0.46203091715613476</v>
+      </c>
+      <c r="I26" s="10">
+        <f>+I11/E11-1</f>
+        <v>-5.4698112882133443E-2</v>
+      </c>
+      <c r="J26" s="10" t="e">
+        <f t="shared" ref="J26" si="11">+J11/F11-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K26" s="10">
+        <f t="shared" ref="K26" si="12">+K11/G11-1</f>
+        <v>1.1000257148868542E-2</v>
+      </c>
+      <c r="L26" s="10">
+        <f t="shared" ref="L26" si="13">+L11/H11-1</f>
+        <v>6.1380742278743794E-2</v>
+      </c>
+      <c r="M26" s="10">
+        <f t="shared" ref="M26" si="14">+M11/I11-1</f>
+        <v>1.2510624962436934E-2</v>
+      </c>
+      <c r="N26" s="10">
+        <f t="shared" ref="N26:O26" si="15">+N11/J11-1</f>
+        <v>-1</v>
+      </c>
+      <c r="O26" s="10">
+        <f t="shared" si="15"/>
+        <v>7.2066100414680534E-4</v>
+      </c>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
+      <c r="U26" s="10">
+        <f t="shared" ref="U26" si="16">+U11/T11-1</f>
+        <v>-3.4016086818002833E-2</v>
+      </c>
+      <c r="V26" s="10">
+        <f>+V11/U11-1</f>
+        <v>8.5403888045474385E-3</v>
+      </c>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
@@ -2127,61 +2294,83 @@
       <c r="AV26" s="3"/>
       <c r="AW26" s="3"/>
       <c r="AX26" s="3"/>
-    </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="B27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="10" t="e">
-        <f t="shared" ref="G27:H27" si="10">+G12/C12-1</f>
+      <c r="AY26" s="3"/>
+      <c r="AZ26" s="3"/>
+      <c r="BA26" s="3"/>
+      <c r="BB26" s="3"/>
+    </row>
+    <row r="27" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="8" t="e">
+        <f t="shared" ref="C27:H27" si="17">+C13/C11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H27" s="10">
-        <f t="shared" si="10"/>
-        <v>-0.46203091715613476</v>
-      </c>
-      <c r="I27" s="10">
-        <f>+I12/E12-1</f>
-        <v>-5.4698112882133443E-2</v>
-      </c>
-      <c r="J27" s="10" t="e">
-        <f t="shared" ref="J27" si="11">+J12/F12-1</f>
+      <c r="D27" s="8">
+        <f t="shared" si="17"/>
+        <v>0.50584248590086356</v>
+      </c>
+      <c r="E27" s="8">
+        <f t="shared" si="17"/>
+        <v>0.48717183922214341</v>
+      </c>
+      <c r="F27" s="8" t="e">
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K27" s="10">
-        <f t="shared" ref="K27" si="12">+K12/G12-1</f>
-        <v>1.1000257148868542E-2</v>
-      </c>
-      <c r="L27" s="10">
-        <f t="shared" ref="L27" si="13">+L12/H12-1</f>
-        <v>6.1380742278743794E-2</v>
-      </c>
-      <c r="M27" s="10">
-        <f t="shared" ref="M27" si="14">+M12/I12-1</f>
-        <v>1.2510624962436934E-2</v>
-      </c>
-      <c r="N27" s="10">
-        <f t="shared" ref="N27" si="15">+N12/J12-1</f>
-        <v>-1</v>
-      </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="10">
-        <f t="shared" ref="Q27:R27" si="16">+Q12/P12-1</f>
-        <v>-3.4016086818002833E-2</v>
-      </c>
-      <c r="R27" s="10">
-        <f>+R12/Q12-1</f>
-        <v>8.5403888045474385E-3</v>
-      </c>
+      <c r="G27" s="8">
+        <f t="shared" si="17"/>
+        <v>0.50593260621676872</v>
+      </c>
+      <c r="H27" s="8">
+        <f t="shared" si="17"/>
+        <v>0.47947720624855328</v>
+      </c>
+      <c r="I27" s="8">
+        <f>+I13/I11</f>
+        <v>0.50179765778605834</v>
+      </c>
+      <c r="J27" s="8">
+        <f t="shared" ref="J27:N27" si="18">+J13/J11</f>
+        <v>0.51117512791962705</v>
+      </c>
+      <c r="K27" s="8">
+        <f t="shared" si="18"/>
+        <v>0.50877510752108035</v>
+      </c>
+      <c r="L27" s="8">
+        <f t="shared" si="18"/>
+        <v>0.49088800256424664</v>
+      </c>
+      <c r="M27" s="8">
+        <f t="shared" si="18"/>
+        <v>0.50011182658928899</v>
+      </c>
+      <c r="N27" s="8" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O27" s="8">
+        <f t="shared" ref="O27" si="19">+O13/O11</f>
+        <v>0.50700309237458174</v>
+      </c>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
       <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
+      <c r="T27" s="8">
+        <f t="shared" ref="T27:V27" si="20">+T13/T11</f>
+        <v>0.49608009628346844</v>
+      </c>
+      <c r="U27" s="8">
+        <f t="shared" si="20"/>
+        <v>0.50201687238131654</v>
+      </c>
+      <c r="V27" s="8">
+        <f t="shared" si="20"/>
+        <v>0.50531193273818342</v>
+      </c>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
@@ -2210,76 +2399,83 @@
       <c r="AV27" s="3"/>
       <c r="AW27" s="3"/>
       <c r="AX27" s="3"/>
-    </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY27" s="3"/>
+      <c r="AZ27" s="3"/>
+      <c r="BA27" s="3"/>
+      <c r="BB27" s="3"/>
+    </row>
+    <row r="28" spans="1:54" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C28" s="8" t="e">
-        <f t="shared" ref="C28:H28" si="17">+C14/C12</f>
+        <f t="shared" ref="C28:H28" si="21">+C16/C11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" si="17"/>
-        <v>0.50584248590086356</v>
+        <f t="shared" si="21"/>
+        <v>0.10667418872182292</v>
       </c>
       <c r="E28" s="8">
-        <f t="shared" si="17"/>
-        <v>0.48717183922214341</v>
+        <f t="shared" si="21"/>
+        <v>0.1365083906286301</v>
       </c>
       <c r="F28" s="8" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="8">
-        <f t="shared" si="17"/>
-        <v>0.50593260621676872</v>
+        <f t="shared" si="21"/>
+        <v>5.8028629240683541E-2</v>
       </c>
       <c r="H28" s="8">
-        <f t="shared" si="17"/>
-        <v>0.47947720624855328</v>
+        <f t="shared" si="21"/>
+        <v>-4.174002707612879E-2</v>
       </c>
       <c r="I28" s="8">
-        <f>+I14/I12</f>
-        <v>0.50179765778605834</v>
+        <f>+I16/I11</f>
+        <v>0.12078221188106913</v>
       </c>
       <c r="J28" s="8">
-        <f t="shared" ref="J28:N28" si="18">+J14/J12</f>
-        <v>0.51117512791962705</v>
+        <f t="shared" ref="J28:N28" si="22">+J16/J11</f>
+        <v>0.12522581427647786</v>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="18"/>
-        <v>0.50877510752108035</v>
+        <f t="shared" si="22"/>
+        <v>5.9744210304553153E-2</v>
       </c>
       <c r="L28" s="8">
-        <f t="shared" si="18"/>
-        <v>0.49088800256424664</v>
+        <f t="shared" si="22"/>
+        <v>-3.8977539711125692E-2</v>
       </c>
       <c r="M28" s="8">
-        <f t="shared" si="18"/>
-        <v>0.50011182658928899</v>
+        <f t="shared" si="22"/>
+        <v>7.1426981477064874E-2</v>
       </c>
       <c r="N28" s="8" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="8">
-        <f t="shared" ref="P28:R28" si="19">+P14/P12</f>
-        <v>0.49608009628346844</v>
-      </c>
-      <c r="Q28" s="8">
-        <f t="shared" si="19"/>
-        <v>0.50201687238131654</v>
-      </c>
-      <c r="R28" s="8">
-        <f t="shared" si="19"/>
-        <v>0.50531193273818342</v>
-      </c>
+      <c r="O28" s="8">
+        <f t="shared" ref="O28" si="23">+O16/O11</f>
+        <v>5.3905390539053959E-2</v>
+      </c>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
       <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
+      <c r="T28" s="8">
+        <f t="shared" ref="T28:V28" si="24">+T16/T11</f>
+        <v>8.8977900053423889E-2</v>
+      </c>
+      <c r="U28" s="8">
+        <f t="shared" si="24"/>
+        <v>8.0372394081545256E-2</v>
+      </c>
+      <c r="V28" s="8">
+        <f t="shared" si="24"/>
+        <v>6.094130397477332E-2</v>
+      </c>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
@@ -2308,76 +2504,83 @@
       <c r="AV28" s="3"/>
       <c r="AW28" s="3"/>
       <c r="AX28" s="3"/>
-    </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY28" s="3"/>
+      <c r="AZ28" s="3"/>
+      <c r="BA28" s="3"/>
+      <c r="BB28" s="3"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C29" s="8" t="e">
-        <f t="shared" ref="C29:H29" si="20">+C17/C12</f>
+        <f t="shared" ref="C29:H29" si="25">+C20/C19</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" si="20"/>
-        <v>0.10667418872182292</v>
+        <f t="shared" si="25"/>
+        <v>0.22196567446590379</v>
       </c>
       <c r="E29" s="8">
-        <f t="shared" si="20"/>
-        <v>0.1365083906286301</v>
+        <f t="shared" si="25"/>
+        <v>0.23954361449677838</v>
       </c>
       <c r="F29" s="8" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="8">
-        <f t="shared" si="20"/>
-        <v>5.8028629240683541E-2</v>
+        <f t="shared" si="25"/>
+        <v>0.21882213891299937</v>
       </c>
       <c r="H29" s="8">
-        <f t="shared" si="20"/>
-        <v>-4.174002707612879E-2</v>
+        <f t="shared" si="25"/>
+        <v>0.21632625817647866</v>
       </c>
       <c r="I29" s="8">
-        <f>+I17/I12</f>
-        <v>0.12078221188106913</v>
+        <f>+I20/I19</f>
+        <v>0.24357317850790342</v>
       </c>
       <c r="J29" s="8">
-        <f t="shared" ref="J29:N29" si="21">+J17/J12</f>
-        <v>0.12522581427647786</v>
+        <f t="shared" ref="J29:N29" si="26">+J20/J19</f>
+        <v>0.26656463874248199</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="21"/>
-        <v>5.9744210304553153E-2</v>
+        <f t="shared" si="26"/>
+        <v>0.23011881332458628</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" si="21"/>
-        <v>-3.8977539711125692E-2</v>
+        <f t="shared" si="26"/>
+        <v>0.38537585146784065</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="21"/>
-        <v>7.1426981477064874E-2</v>
+        <f t="shared" si="26"/>
+        <v>0.2674113934749538</v>
       </c>
       <c r="N29" s="8" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O29" s="3"/>
-      <c r="P29" s="8">
-        <f t="shared" ref="P29:R29" si="22">+P17/P12</f>
-        <v>8.8977900053423889E-2</v>
-      </c>
-      <c r="Q29" s="8">
-        <f t="shared" si="22"/>
-        <v>8.0372394081545256E-2</v>
-      </c>
-      <c r="R29" s="8">
-        <f t="shared" si="22"/>
-        <v>6.094130397477332E-2</v>
-      </c>
+      <c r="O29" s="8">
+        <f t="shared" ref="O29" si="27">+O20/O19</f>
+        <v>0.27425803312673169</v>
+      </c>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8"/>
       <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
+      <c r="T29" s="8">
+        <f t="shared" ref="T29:V29" si="28">+T20/T19</f>
+        <v>0.22928827193799975</v>
+      </c>
+      <c r="U29" s="8">
+        <f t="shared" si="28"/>
+        <v>0.25123160969458774</v>
+      </c>
+      <c r="V29" s="8">
+        <f t="shared" si="28"/>
+        <v>0.22819914294673016</v>
+      </c>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
@@ -2406,72 +2609,28 @@
       <c r="AV29" s="3"/>
       <c r="AW29" s="3"/>
       <c r="AX29" s="3"/>
-    </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="8" t="e">
-        <f t="shared" ref="C30:H30" si="23">+C21/C20</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D30" s="8">
-        <f t="shared" si="23"/>
-        <v>0.22196567446590379</v>
-      </c>
-      <c r="E30" s="8">
-        <f t="shared" si="23"/>
-        <v>0.23954361449677838</v>
-      </c>
-      <c r="F30" s="8" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G30" s="8">
-        <f t="shared" si="23"/>
-        <v>0.21882213891299937</v>
-      </c>
-      <c r="H30" s="8">
-        <f t="shared" si="23"/>
-        <v>0.21632625817647866</v>
-      </c>
-      <c r="I30" s="8">
-        <f>+I21/I20</f>
-        <v>0.24357317850790342</v>
-      </c>
-      <c r="J30" s="8">
-        <f t="shared" ref="J30:N30" si="24">+J21/J20</f>
-        <v>0.26656463874248199</v>
-      </c>
-      <c r="K30" s="8">
-        <f t="shared" si="24"/>
-        <v>0.23011881332458628</v>
-      </c>
-      <c r="L30" s="8">
-        <f t="shared" si="24"/>
-        <v>0.38537585146784065</v>
-      </c>
-      <c r="M30" s="8">
-        <f t="shared" si="24"/>
-        <v>0.2674113934749538</v>
-      </c>
-      <c r="N30" s="8" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AY29" s="3"/>
+      <c r="AZ29" s="3"/>
+      <c r="BA29" s="3"/>
+      <c r="BB29" s="3"/>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
       <c r="O30" s="3"/>
-      <c r="P30" s="8">
-        <f t="shared" ref="P30:R30" si="25">+P21/P20</f>
-        <v>0.22928827193799975</v>
-      </c>
-      <c r="Q30" s="8">
-        <f t="shared" si="25"/>
-        <v>0.25123160969458774</v>
-      </c>
-      <c r="R30" s="8">
-        <f t="shared" si="25"/>
-        <v>0.22819914294673016</v>
-      </c>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
@@ -2504,8 +2663,12 @@
       <c r="AV30" s="3"/>
       <c r="AW30" s="3"/>
       <c r="AX30" s="3"/>
-    </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY30" s="3"/>
+      <c r="AZ30" s="3"/>
+      <c r="BA30" s="3"/>
+      <c r="BB30" s="3"/>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.2">
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -2554,8 +2717,12 @@
       <c r="AV31" s="3"/>
       <c r="AW31" s="3"/>
       <c r="AX31" s="3"/>
-    </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY31" s="3"/>
+      <c r="AZ31" s="3"/>
+      <c r="BA31" s="3"/>
+      <c r="BB31" s="3"/>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.2">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -2604,8 +2771,12 @@
       <c r="AV32" s="3"/>
       <c r="AW32" s="3"/>
       <c r="AX32" s="3"/>
-    </row>
-    <row r="33" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY32" s="3"/>
+      <c r="AZ32" s="3"/>
+      <c r="BA32" s="3"/>
+      <c r="BB32" s="3"/>
+    </row>
+    <row r="33" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -2654,8 +2825,12 @@
       <c r="AV33" s="3"/>
       <c r="AW33" s="3"/>
       <c r="AX33" s="3"/>
-    </row>
-    <row r="34" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY33" s="3"/>
+      <c r="AZ33" s="3"/>
+      <c r="BA33" s="3"/>
+      <c r="BB33" s="3"/>
+    </row>
+    <row r="34" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -2704,8 +2879,12 @@
       <c r="AV34" s="3"/>
       <c r="AW34" s="3"/>
       <c r="AX34" s="3"/>
-    </row>
-    <row r="35" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY34" s="3"/>
+      <c r="AZ34" s="3"/>
+      <c r="BA34" s="3"/>
+      <c r="BB34" s="3"/>
+    </row>
+    <row r="35" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -2754,8 +2933,12 @@
       <c r="AV35" s="3"/>
       <c r="AW35" s="3"/>
       <c r="AX35" s="3"/>
-    </row>
-    <row r="36" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY35" s="3"/>
+      <c r="AZ35" s="3"/>
+      <c r="BA35" s="3"/>
+      <c r="BB35" s="3"/>
+    </row>
+    <row r="36" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -2804,8 +2987,12 @@
       <c r="AV36" s="3"/>
       <c r="AW36" s="3"/>
       <c r="AX36" s="3"/>
-    </row>
-    <row r="37" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY36" s="3"/>
+      <c r="AZ36" s="3"/>
+      <c r="BA36" s="3"/>
+      <c r="BB36" s="3"/>
+    </row>
+    <row r="37" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -2854,8 +3041,12 @@
       <c r="AV37" s="3"/>
       <c r="AW37" s="3"/>
       <c r="AX37" s="3"/>
-    </row>
-    <row r="38" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY37" s="3"/>
+      <c r="AZ37" s="3"/>
+      <c r="BA37" s="3"/>
+      <c r="BB37" s="3"/>
+    </row>
+    <row r="38" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -2904,8 +3095,12 @@
       <c r="AV38" s="3"/>
       <c r="AW38" s="3"/>
       <c r="AX38" s="3"/>
-    </row>
-    <row r="39" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY38" s="3"/>
+      <c r="AZ38" s="3"/>
+      <c r="BA38" s="3"/>
+      <c r="BB38" s="3"/>
+    </row>
+    <row r="39" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -2954,8 +3149,12 @@
       <c r="AV39" s="3"/>
       <c r="AW39" s="3"/>
       <c r="AX39" s="3"/>
-    </row>
-    <row r="40" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY39" s="3"/>
+      <c r="AZ39" s="3"/>
+      <c r="BA39" s="3"/>
+      <c r="BB39" s="3"/>
+    </row>
+    <row r="40" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -3004,8 +3203,12 @@
       <c r="AV40" s="3"/>
       <c r="AW40" s="3"/>
       <c r="AX40" s="3"/>
-    </row>
-    <row r="41" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY40" s="3"/>
+      <c r="AZ40" s="3"/>
+      <c r="BA40" s="3"/>
+      <c r="BB40" s="3"/>
+    </row>
+    <row r="41" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -3054,8 +3257,12 @@
       <c r="AV41" s="3"/>
       <c r="AW41" s="3"/>
       <c r="AX41" s="3"/>
-    </row>
-    <row r="42" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY41" s="3"/>
+      <c r="AZ41" s="3"/>
+      <c r="BA41" s="3"/>
+      <c r="BB41" s="3"/>
+    </row>
+    <row r="42" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -3104,8 +3311,12 @@
       <c r="AV42" s="3"/>
       <c r="AW42" s="3"/>
       <c r="AX42" s="3"/>
-    </row>
-    <row r="43" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY42" s="3"/>
+      <c r="AZ42" s="3"/>
+      <c r="BA42" s="3"/>
+      <c r="BB42" s="3"/>
+    </row>
+    <row r="43" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -3154,8 +3365,12 @@
       <c r="AV43" s="3"/>
       <c r="AW43" s="3"/>
       <c r="AX43" s="3"/>
-    </row>
-    <row r="44" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY43" s="3"/>
+      <c r="AZ43" s="3"/>
+      <c r="BA43" s="3"/>
+      <c r="BB43" s="3"/>
+    </row>
+    <row r="44" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -3204,8 +3419,12 @@
       <c r="AV44" s="3"/>
       <c r="AW44" s="3"/>
       <c r="AX44" s="3"/>
-    </row>
-    <row r="45" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY44" s="3"/>
+      <c r="AZ44" s="3"/>
+      <c r="BA44" s="3"/>
+      <c r="BB44" s="3"/>
+    </row>
+    <row r="45" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -3254,8 +3473,12 @@
       <c r="AV45" s="3"/>
       <c r="AW45" s="3"/>
       <c r="AX45" s="3"/>
-    </row>
-    <row r="46" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY45" s="3"/>
+      <c r="AZ45" s="3"/>
+      <c r="BA45" s="3"/>
+      <c r="BB45" s="3"/>
+    </row>
+    <row r="46" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -3304,8 +3527,12 @@
       <c r="AV46" s="3"/>
       <c r="AW46" s="3"/>
       <c r="AX46" s="3"/>
-    </row>
-    <row r="47" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY46" s="3"/>
+      <c r="AZ46" s="3"/>
+      <c r="BA46" s="3"/>
+      <c r="BB46" s="3"/>
+    </row>
+    <row r="47" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -3354,8 +3581,12 @@
       <c r="AV47" s="3"/>
       <c r="AW47" s="3"/>
       <c r="AX47" s="3"/>
-    </row>
-    <row r="48" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY47" s="3"/>
+      <c r="AZ47" s="3"/>
+      <c r="BA47" s="3"/>
+      <c r="BB47" s="3"/>
+    </row>
+    <row r="48" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -3404,8 +3635,12 @@
       <c r="AV48" s="3"/>
       <c r="AW48" s="3"/>
       <c r="AX48" s="3"/>
-    </row>
-    <row r="49" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY48" s="3"/>
+      <c r="AZ48" s="3"/>
+      <c r="BA48" s="3"/>
+      <c r="BB48" s="3"/>
+    </row>
+    <row r="49" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -3454,8 +3689,12 @@
       <c r="AV49" s="3"/>
       <c r="AW49" s="3"/>
       <c r="AX49" s="3"/>
-    </row>
-    <row r="50" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY49" s="3"/>
+      <c r="AZ49" s="3"/>
+      <c r="BA49" s="3"/>
+      <c r="BB49" s="3"/>
+    </row>
+    <row r="50" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -3504,8 +3743,12 @@
       <c r="AV50" s="3"/>
       <c r="AW50" s="3"/>
       <c r="AX50" s="3"/>
-    </row>
-    <row r="51" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY50" s="3"/>
+      <c r="AZ50" s="3"/>
+      <c r="BA50" s="3"/>
+      <c r="BB50" s="3"/>
+    </row>
+    <row r="51" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -3554,8 +3797,12 @@
       <c r="AV51" s="3"/>
       <c r="AW51" s="3"/>
       <c r="AX51" s="3"/>
-    </row>
-    <row r="52" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY51" s="3"/>
+      <c r="AZ51" s="3"/>
+      <c r="BA51" s="3"/>
+      <c r="BB51" s="3"/>
+    </row>
+    <row r="52" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -3604,8 +3851,12 @@
       <c r="AV52" s="3"/>
       <c r="AW52" s="3"/>
       <c r="AX52" s="3"/>
-    </row>
-    <row r="53" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY52" s="3"/>
+      <c r="AZ52" s="3"/>
+      <c r="BA52" s="3"/>
+      <c r="BB52" s="3"/>
+    </row>
+    <row r="53" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -3654,8 +3905,12 @@
       <c r="AV53" s="3"/>
       <c r="AW53" s="3"/>
       <c r="AX53" s="3"/>
-    </row>
-    <row r="54" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY53" s="3"/>
+      <c r="AZ53" s="3"/>
+      <c r="BA53" s="3"/>
+      <c r="BB53" s="3"/>
+    </row>
+    <row r="54" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -3704,8 +3959,12 @@
       <c r="AV54" s="3"/>
       <c r="AW54" s="3"/>
       <c r="AX54" s="3"/>
-    </row>
-    <row r="55" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY54" s="3"/>
+      <c r="AZ54" s="3"/>
+      <c r="BA54" s="3"/>
+      <c r="BB54" s="3"/>
+    </row>
+    <row r="55" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -3754,8 +4013,12 @@
       <c r="AV55" s="3"/>
       <c r="AW55" s="3"/>
       <c r="AX55" s="3"/>
-    </row>
-    <row r="56" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY55" s="3"/>
+      <c r="AZ55" s="3"/>
+      <c r="BA55" s="3"/>
+      <c r="BB55" s="3"/>
+    </row>
+    <row r="56" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -3804,8 +4067,12 @@
       <c r="AV56" s="3"/>
       <c r="AW56" s="3"/>
       <c r="AX56" s="3"/>
-    </row>
-    <row r="57" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY56" s="3"/>
+      <c r="AZ56" s="3"/>
+      <c r="BA56" s="3"/>
+      <c r="BB56" s="3"/>
+    </row>
+    <row r="57" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -3854,8 +4121,12 @@
       <c r="AV57" s="3"/>
       <c r="AW57" s="3"/>
       <c r="AX57" s="3"/>
-    </row>
-    <row r="58" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY57" s="3"/>
+      <c r="AZ57" s="3"/>
+      <c r="BA57" s="3"/>
+      <c r="BB57" s="3"/>
+    </row>
+    <row r="58" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -3904,8 +4175,12 @@
       <c r="AV58" s="3"/>
       <c r="AW58" s="3"/>
       <c r="AX58" s="3"/>
-    </row>
-    <row r="59" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY58" s="3"/>
+      <c r="AZ58" s="3"/>
+      <c r="BA58" s="3"/>
+      <c r="BB58" s="3"/>
+    </row>
+    <row r="59" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -3954,8 +4229,12 @@
       <c r="AV59" s="3"/>
       <c r="AW59" s="3"/>
       <c r="AX59" s="3"/>
-    </row>
-    <row r="60" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY59" s="3"/>
+      <c r="AZ59" s="3"/>
+      <c r="BA59" s="3"/>
+      <c r="BB59" s="3"/>
+    </row>
+    <row r="60" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -4004,8 +4283,12 @@
       <c r="AV60" s="3"/>
       <c r="AW60" s="3"/>
       <c r="AX60" s="3"/>
-    </row>
-    <row r="61" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY60" s="3"/>
+      <c r="AZ60" s="3"/>
+      <c r="BA60" s="3"/>
+      <c r="BB60" s="3"/>
+    </row>
+    <row r="61" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -4054,8 +4337,12 @@
       <c r="AV61" s="3"/>
       <c r="AW61" s="3"/>
       <c r="AX61" s="3"/>
-    </row>
-    <row r="62" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY61" s="3"/>
+      <c r="AZ61" s="3"/>
+      <c r="BA61" s="3"/>
+      <c r="BB61" s="3"/>
+    </row>
+    <row r="62" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -4104,8 +4391,12 @@
       <c r="AV62" s="3"/>
       <c r="AW62" s="3"/>
       <c r="AX62" s="3"/>
-    </row>
-    <row r="63" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY62" s="3"/>
+      <c r="AZ62" s="3"/>
+      <c r="BA62" s="3"/>
+      <c r="BB62" s="3"/>
+    </row>
+    <row r="63" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -4154,8 +4445,12 @@
       <c r="AV63" s="3"/>
       <c r="AW63" s="3"/>
       <c r="AX63" s="3"/>
-    </row>
-    <row r="64" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY63" s="3"/>
+      <c r="AZ63" s="3"/>
+      <c r="BA63" s="3"/>
+      <c r="BB63" s="3"/>
+    </row>
+    <row r="64" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -4204,8 +4499,12 @@
       <c r="AV64" s="3"/>
       <c r="AW64" s="3"/>
       <c r="AX64" s="3"/>
-    </row>
-    <row r="65" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY64" s="3"/>
+      <c r="AZ64" s="3"/>
+      <c r="BA64" s="3"/>
+      <c r="BB64" s="3"/>
+    </row>
+    <row r="65" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -4254,8 +4553,12 @@
       <c r="AV65" s="3"/>
       <c r="AW65" s="3"/>
       <c r="AX65" s="3"/>
-    </row>
-    <row r="66" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY65" s="3"/>
+      <c r="AZ65" s="3"/>
+      <c r="BA65" s="3"/>
+      <c r="BB65" s="3"/>
+    </row>
+    <row r="66" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -4304,8 +4607,12 @@
       <c r="AV66" s="3"/>
       <c r="AW66" s="3"/>
       <c r="AX66" s="3"/>
-    </row>
-    <row r="67" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY66" s="3"/>
+      <c r="AZ66" s="3"/>
+      <c r="BA66" s="3"/>
+      <c r="BB66" s="3"/>
+    </row>
+    <row r="67" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -4354,8 +4661,12 @@
       <c r="AV67" s="3"/>
       <c r="AW67" s="3"/>
       <c r="AX67" s="3"/>
-    </row>
-    <row r="68" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY67" s="3"/>
+      <c r="AZ67" s="3"/>
+      <c r="BA67" s="3"/>
+      <c r="BB67" s="3"/>
+    </row>
+    <row r="68" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -4404,8 +4715,12 @@
       <c r="AV68" s="3"/>
       <c r="AW68" s="3"/>
       <c r="AX68" s="3"/>
-    </row>
-    <row r="69" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY68" s="3"/>
+      <c r="AZ68" s="3"/>
+      <c r="BA68" s="3"/>
+      <c r="BB68" s="3"/>
+    </row>
+    <row r="69" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -4454,8 +4769,12 @@
       <c r="AV69" s="3"/>
       <c r="AW69" s="3"/>
       <c r="AX69" s="3"/>
-    </row>
-    <row r="70" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY69" s="3"/>
+      <c r="AZ69" s="3"/>
+      <c r="BA69" s="3"/>
+      <c r="BB69" s="3"/>
+    </row>
+    <row r="70" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -4504,8 +4823,12 @@
       <c r="AV70" s="3"/>
       <c r="AW70" s="3"/>
       <c r="AX70" s="3"/>
-    </row>
-    <row r="71" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY70" s="3"/>
+      <c r="AZ70" s="3"/>
+      <c r="BA70" s="3"/>
+      <c r="BB70" s="3"/>
+    </row>
+    <row r="71" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -4554,8 +4877,12 @@
       <c r="AV71" s="3"/>
       <c r="AW71" s="3"/>
       <c r="AX71" s="3"/>
-    </row>
-    <row r="72" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY71" s="3"/>
+      <c r="AZ71" s="3"/>
+      <c r="BA71" s="3"/>
+      <c r="BB71" s="3"/>
+    </row>
+    <row r="72" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -4604,8 +4931,12 @@
       <c r="AV72" s="3"/>
       <c r="AW72" s="3"/>
       <c r="AX72" s="3"/>
-    </row>
-    <row r="73" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY72" s="3"/>
+      <c r="AZ72" s="3"/>
+      <c r="BA72" s="3"/>
+      <c r="BB72" s="3"/>
+    </row>
+    <row r="73" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -4654,8 +4985,12 @@
       <c r="AV73" s="3"/>
       <c r="AW73" s="3"/>
       <c r="AX73" s="3"/>
-    </row>
-    <row r="74" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY73" s="3"/>
+      <c r="AZ73" s="3"/>
+      <c r="BA73" s="3"/>
+      <c r="BB73" s="3"/>
+    </row>
+    <row r="74" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -4704,8 +5039,12 @@
       <c r="AV74" s="3"/>
       <c r="AW74" s="3"/>
       <c r="AX74" s="3"/>
-    </row>
-    <row r="75" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY74" s="3"/>
+      <c r="AZ74" s="3"/>
+      <c r="BA74" s="3"/>
+      <c r="BB74" s="3"/>
+    </row>
+    <row r="75" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -4754,8 +5093,12 @@
       <c r="AV75" s="3"/>
       <c r="AW75" s="3"/>
       <c r="AX75" s="3"/>
-    </row>
-    <row r="76" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY75" s="3"/>
+      <c r="AZ75" s="3"/>
+      <c r="BA75" s="3"/>
+      <c r="BB75" s="3"/>
+    </row>
+    <row r="76" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -4804,8 +5147,12 @@
       <c r="AV76" s="3"/>
       <c r="AW76" s="3"/>
       <c r="AX76" s="3"/>
-    </row>
-    <row r="77" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY76" s="3"/>
+      <c r="AZ76" s="3"/>
+      <c r="BA76" s="3"/>
+      <c r="BB76" s="3"/>
+    </row>
+    <row r="77" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -4854,8 +5201,12 @@
       <c r="AV77" s="3"/>
       <c r="AW77" s="3"/>
       <c r="AX77" s="3"/>
-    </row>
-    <row r="78" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY77" s="3"/>
+      <c r="AZ77" s="3"/>
+      <c r="BA77" s="3"/>
+      <c r="BB77" s="3"/>
+    </row>
+    <row r="78" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -4904,8 +5255,12 @@
       <c r="AV78" s="3"/>
       <c r="AW78" s="3"/>
       <c r="AX78" s="3"/>
-    </row>
-    <row r="79" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY78" s="3"/>
+      <c r="AZ78" s="3"/>
+      <c r="BA78" s="3"/>
+      <c r="BB78" s="3"/>
+    </row>
+    <row r="79" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -4954,8 +5309,12 @@
       <c r="AV79" s="3"/>
       <c r="AW79" s="3"/>
       <c r="AX79" s="3"/>
-    </row>
-    <row r="80" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY79" s="3"/>
+      <c r="AZ79" s="3"/>
+      <c r="BA79" s="3"/>
+      <c r="BB79" s="3"/>
+    </row>
+    <row r="80" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -5004,8 +5363,12 @@
       <c r="AV80" s="3"/>
       <c r="AW80" s="3"/>
       <c r="AX80" s="3"/>
-    </row>
-    <row r="81" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY80" s="3"/>
+      <c r="AZ80" s="3"/>
+      <c r="BA80" s="3"/>
+      <c r="BB80" s="3"/>
+    </row>
+    <row r="81" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -5054,8 +5417,12 @@
       <c r="AV81" s="3"/>
       <c r="AW81" s="3"/>
       <c r="AX81" s="3"/>
-    </row>
-    <row r="82" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY81" s="3"/>
+      <c r="AZ81" s="3"/>
+      <c r="BA81" s="3"/>
+      <c r="BB81" s="3"/>
+    </row>
+    <row r="82" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -5104,8 +5471,12 @@
       <c r="AV82" s="3"/>
       <c r="AW82" s="3"/>
       <c r="AX82" s="3"/>
-    </row>
-    <row r="83" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY82" s="3"/>
+      <c r="AZ82" s="3"/>
+      <c r="BA82" s="3"/>
+      <c r="BB82" s="3"/>
+    </row>
+    <row r="83" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -5154,8 +5525,12 @@
       <c r="AV83" s="3"/>
       <c r="AW83" s="3"/>
       <c r="AX83" s="3"/>
-    </row>
-    <row r="84" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY83" s="3"/>
+      <c r="AZ83" s="3"/>
+      <c r="BA83" s="3"/>
+      <c r="BB83" s="3"/>
+    </row>
+    <row r="84" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -5204,8 +5579,12 @@
       <c r="AV84" s="3"/>
       <c r="AW84" s="3"/>
       <c r="AX84" s="3"/>
-    </row>
-    <row r="85" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY84" s="3"/>
+      <c r="AZ84" s="3"/>
+      <c r="BA84" s="3"/>
+      <c r="BB84" s="3"/>
+    </row>
+    <row r="85" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -5254,8 +5633,12 @@
       <c r="AV85" s="3"/>
       <c r="AW85" s="3"/>
       <c r="AX85" s="3"/>
-    </row>
-    <row r="86" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY85" s="3"/>
+      <c r="AZ85" s="3"/>
+      <c r="BA85" s="3"/>
+      <c r="BB85" s="3"/>
+    </row>
+    <row r="86" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -5304,8 +5687,12 @@
       <c r="AV86" s="3"/>
       <c r="AW86" s="3"/>
       <c r="AX86" s="3"/>
-    </row>
-    <row r="87" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY86" s="3"/>
+      <c r="AZ86" s="3"/>
+      <c r="BA86" s="3"/>
+      <c r="BB86" s="3"/>
+    </row>
+    <row r="87" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -5354,8 +5741,12 @@
       <c r="AV87" s="3"/>
       <c r="AW87" s="3"/>
       <c r="AX87" s="3"/>
-    </row>
-    <row r="88" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY87" s="3"/>
+      <c r="AZ87" s="3"/>
+      <c r="BA87" s="3"/>
+      <c r="BB87" s="3"/>
+    </row>
+    <row r="88" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -5404,8 +5795,12 @@
       <c r="AV88" s="3"/>
       <c r="AW88" s="3"/>
       <c r="AX88" s="3"/>
-    </row>
-    <row r="89" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY88" s="3"/>
+      <c r="AZ88" s="3"/>
+      <c r="BA88" s="3"/>
+      <c r="BB88" s="3"/>
+    </row>
+    <row r="89" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -5454,8 +5849,12 @@
       <c r="AV89" s="3"/>
       <c r="AW89" s="3"/>
       <c r="AX89" s="3"/>
-    </row>
-    <row r="90" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY89" s="3"/>
+      <c r="AZ89" s="3"/>
+      <c r="BA89" s="3"/>
+      <c r="BB89" s="3"/>
+    </row>
+    <row r="90" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -5504,8 +5903,12 @@
       <c r="AV90" s="3"/>
       <c r="AW90" s="3"/>
       <c r="AX90" s="3"/>
-    </row>
-    <row r="91" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY90" s="3"/>
+      <c r="AZ90" s="3"/>
+      <c r="BA90" s="3"/>
+      <c r="BB90" s="3"/>
+    </row>
+    <row r="91" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -5554,8 +5957,12 @@
       <c r="AV91" s="3"/>
       <c r="AW91" s="3"/>
       <c r="AX91" s="3"/>
-    </row>
-    <row r="92" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY91" s="3"/>
+      <c r="AZ91" s="3"/>
+      <c r="BA91" s="3"/>
+      <c r="BB91" s="3"/>
+    </row>
+    <row r="92" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -5604,8 +6011,12 @@
       <c r="AV92" s="3"/>
       <c r="AW92" s="3"/>
       <c r="AX92" s="3"/>
-    </row>
-    <row r="93" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY92" s="3"/>
+      <c r="AZ92" s="3"/>
+      <c r="BA92" s="3"/>
+      <c r="BB92" s="3"/>
+    </row>
+    <row r="93" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -5654,8 +6065,12 @@
       <c r="AV93" s="3"/>
       <c r="AW93" s="3"/>
       <c r="AX93" s="3"/>
-    </row>
-    <row r="94" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY93" s="3"/>
+      <c r="AZ93" s="3"/>
+      <c r="BA93" s="3"/>
+      <c r="BB93" s="3"/>
+    </row>
+    <row r="94" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -5704,8 +6119,12 @@
       <c r="AV94" s="3"/>
       <c r="AW94" s="3"/>
       <c r="AX94" s="3"/>
-    </row>
-    <row r="95" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY94" s="3"/>
+      <c r="AZ94" s="3"/>
+      <c r="BA94" s="3"/>
+      <c r="BB94" s="3"/>
+    </row>
+    <row r="95" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -5754,8 +6173,12 @@
       <c r="AV95" s="3"/>
       <c r="AW95" s="3"/>
       <c r="AX95" s="3"/>
-    </row>
-    <row r="96" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY95" s="3"/>
+      <c r="AZ95" s="3"/>
+      <c r="BA95" s="3"/>
+      <c r="BB95" s="3"/>
+    </row>
+    <row r="96" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -5804,8 +6227,12 @@
       <c r="AV96" s="3"/>
       <c r="AW96" s="3"/>
       <c r="AX96" s="3"/>
-    </row>
-    <row r="97" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY96" s="3"/>
+      <c r="AZ96" s="3"/>
+      <c r="BA96" s="3"/>
+      <c r="BB96" s="3"/>
+    </row>
+    <row r="97" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -5854,8 +6281,12 @@
       <c r="AV97" s="3"/>
       <c r="AW97" s="3"/>
       <c r="AX97" s="3"/>
-    </row>
-    <row r="98" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY97" s="3"/>
+      <c r="AZ97" s="3"/>
+      <c r="BA97" s="3"/>
+      <c r="BB97" s="3"/>
+    </row>
+    <row r="98" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -5904,8 +6335,12 @@
       <c r="AV98" s="3"/>
       <c r="AW98" s="3"/>
       <c r="AX98" s="3"/>
-    </row>
-    <row r="99" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY98" s="3"/>
+      <c r="AZ98" s="3"/>
+      <c r="BA98" s="3"/>
+      <c r="BB98" s="3"/>
+    </row>
+    <row r="99" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -5954,8 +6389,12 @@
       <c r="AV99" s="3"/>
       <c r="AW99" s="3"/>
       <c r="AX99" s="3"/>
-    </row>
-    <row r="100" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY99" s="3"/>
+      <c r="AZ99" s="3"/>
+      <c r="BA99" s="3"/>
+      <c r="BB99" s="3"/>
+    </row>
+    <row r="100" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -6004,8 +6443,12 @@
       <c r="AV100" s="3"/>
       <c r="AW100" s="3"/>
       <c r="AX100" s="3"/>
-    </row>
-    <row r="101" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY100" s="3"/>
+      <c r="AZ100" s="3"/>
+      <c r="BA100" s="3"/>
+      <c r="BB100" s="3"/>
+    </row>
+    <row r="101" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -6054,8 +6497,12 @@
       <c r="AV101" s="3"/>
       <c r="AW101" s="3"/>
       <c r="AX101" s="3"/>
-    </row>
-    <row r="102" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY101" s="3"/>
+      <c r="AZ101" s="3"/>
+      <c r="BA101" s="3"/>
+      <c r="BB101" s="3"/>
+    </row>
+    <row r="102" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -6104,8 +6551,12 @@
       <c r="AV102" s="3"/>
       <c r="AW102" s="3"/>
       <c r="AX102" s="3"/>
-    </row>
-    <row r="103" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY102" s="3"/>
+      <c r="AZ102" s="3"/>
+      <c r="BA102" s="3"/>
+      <c r="BB102" s="3"/>
+    </row>
+    <row r="103" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -6154,8 +6605,12 @@
       <c r="AV103" s="3"/>
       <c r="AW103" s="3"/>
       <c r="AX103" s="3"/>
-    </row>
-    <row r="104" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY103" s="3"/>
+      <c r="AZ103" s="3"/>
+      <c r="BA103" s="3"/>
+      <c r="BB103" s="3"/>
+    </row>
+    <row r="104" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -6204,8 +6659,12 @@
       <c r="AV104" s="3"/>
       <c r="AW104" s="3"/>
       <c r="AX104" s="3"/>
-    </row>
-    <row r="105" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY104" s="3"/>
+      <c r="AZ104" s="3"/>
+      <c r="BA104" s="3"/>
+      <c r="BB104" s="3"/>
+    </row>
+    <row r="105" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -6254,8 +6713,12 @@
       <c r="AV105" s="3"/>
       <c r="AW105" s="3"/>
       <c r="AX105" s="3"/>
-    </row>
-    <row r="106" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY105" s="3"/>
+      <c r="AZ105" s="3"/>
+      <c r="BA105" s="3"/>
+      <c r="BB105" s="3"/>
+    </row>
+    <row r="106" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -6304,8 +6767,12 @@
       <c r="AV106" s="3"/>
       <c r="AW106" s="3"/>
       <c r="AX106" s="3"/>
-    </row>
-    <row r="107" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY106" s="3"/>
+      <c r="AZ106" s="3"/>
+      <c r="BA106" s="3"/>
+      <c r="BB106" s="3"/>
+    </row>
+    <row r="107" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -6354,8 +6821,12 @@
       <c r="AV107" s="3"/>
       <c r="AW107" s="3"/>
       <c r="AX107" s="3"/>
-    </row>
-    <row r="108" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY107" s="3"/>
+      <c r="AZ107" s="3"/>
+      <c r="BA107" s="3"/>
+      <c r="BB107" s="3"/>
+    </row>
+    <row r="108" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -6404,8 +6875,12 @@
       <c r="AV108" s="3"/>
       <c r="AW108" s="3"/>
       <c r="AX108" s="3"/>
-    </row>
-    <row r="109" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY108" s="3"/>
+      <c r="AZ108" s="3"/>
+      <c r="BA108" s="3"/>
+      <c r="BB108" s="3"/>
+    </row>
+    <row r="109" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -6454,8 +6929,12 @@
       <c r="AV109" s="3"/>
       <c r="AW109" s="3"/>
       <c r="AX109" s="3"/>
-    </row>
-    <row r="110" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY109" s="3"/>
+      <c r="AZ109" s="3"/>
+      <c r="BA109" s="3"/>
+      <c r="BB109" s="3"/>
+    </row>
+    <row r="110" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -6504,8 +6983,12 @@
       <c r="AV110" s="3"/>
       <c r="AW110" s="3"/>
       <c r="AX110" s="3"/>
-    </row>
-    <row r="111" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY110" s="3"/>
+      <c r="AZ110" s="3"/>
+      <c r="BA110" s="3"/>
+      <c r="BB110" s="3"/>
+    </row>
+    <row r="111" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -6554,8 +7037,12 @@
       <c r="AV111" s="3"/>
       <c r="AW111" s="3"/>
       <c r="AX111" s="3"/>
-    </row>
-    <row r="112" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY111" s="3"/>
+      <c r="AZ111" s="3"/>
+      <c r="BA111" s="3"/>
+      <c r="BB111" s="3"/>
+    </row>
+    <row r="112" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -6604,8 +7091,12 @@
       <c r="AV112" s="3"/>
       <c r="AW112" s="3"/>
       <c r="AX112" s="3"/>
-    </row>
-    <row r="113" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY112" s="3"/>
+      <c r="AZ112" s="3"/>
+      <c r="BA112" s="3"/>
+      <c r="BB112" s="3"/>
+    </row>
+    <row r="113" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -6654,8 +7145,12 @@
       <c r="AV113" s="3"/>
       <c r="AW113" s="3"/>
       <c r="AX113" s="3"/>
-    </row>
-    <row r="114" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY113" s="3"/>
+      <c r="AZ113" s="3"/>
+      <c r="BA113" s="3"/>
+      <c r="BB113" s="3"/>
+    </row>
+    <row r="114" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -6704,8 +7199,12 @@
       <c r="AV114" s="3"/>
       <c r="AW114" s="3"/>
       <c r="AX114" s="3"/>
-    </row>
-    <row r="115" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY114" s="3"/>
+      <c r="AZ114" s="3"/>
+      <c r="BA114" s="3"/>
+      <c r="BB114" s="3"/>
+    </row>
+    <row r="115" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -6754,8 +7253,12 @@
       <c r="AV115" s="3"/>
       <c r="AW115" s="3"/>
       <c r="AX115" s="3"/>
-    </row>
-    <row r="116" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY115" s="3"/>
+      <c r="AZ115" s="3"/>
+      <c r="BA115" s="3"/>
+      <c r="BB115" s="3"/>
+    </row>
+    <row r="116" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -6804,8 +7307,12 @@
       <c r="AV116" s="3"/>
       <c r="AW116" s="3"/>
       <c r="AX116" s="3"/>
-    </row>
-    <row r="117" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY116" s="3"/>
+      <c r="AZ116" s="3"/>
+      <c r="BA116" s="3"/>
+      <c r="BB116" s="3"/>
+    </row>
+    <row r="117" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -6854,8 +7361,12 @@
       <c r="AV117" s="3"/>
       <c r="AW117" s="3"/>
       <c r="AX117" s="3"/>
-    </row>
-    <row r="118" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY117" s="3"/>
+      <c r="AZ117" s="3"/>
+      <c r="BA117" s="3"/>
+      <c r="BB117" s="3"/>
+    </row>
+    <row r="118" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -6904,8 +7415,12 @@
       <c r="AV118" s="3"/>
       <c r="AW118" s="3"/>
       <c r="AX118" s="3"/>
-    </row>
-    <row r="119" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY118" s="3"/>
+      <c r="AZ118" s="3"/>
+      <c r="BA118" s="3"/>
+      <c r="BB118" s="3"/>
+    </row>
+    <row r="119" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -6954,8 +7469,12 @@
       <c r="AV119" s="3"/>
       <c r="AW119" s="3"/>
       <c r="AX119" s="3"/>
-    </row>
-    <row r="120" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY119" s="3"/>
+      <c r="AZ119" s="3"/>
+      <c r="BA119" s="3"/>
+      <c r="BB119" s="3"/>
+    </row>
+    <row r="120" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -7004,8 +7523,12 @@
       <c r="AV120" s="3"/>
       <c r="AW120" s="3"/>
       <c r="AX120" s="3"/>
-    </row>
-    <row r="121" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY120" s="3"/>
+      <c r="AZ120" s="3"/>
+      <c r="BA120" s="3"/>
+      <c r="BB120" s="3"/>
+    </row>
+    <row r="121" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -7054,8 +7577,12 @@
       <c r="AV121" s="3"/>
       <c r="AW121" s="3"/>
       <c r="AX121" s="3"/>
-    </row>
-    <row r="122" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY121" s="3"/>
+      <c r="AZ121" s="3"/>
+      <c r="BA121" s="3"/>
+      <c r="BB121" s="3"/>
+    </row>
+    <row r="122" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -7104,8 +7631,12 @@
       <c r="AV122" s="3"/>
       <c r="AW122" s="3"/>
       <c r="AX122" s="3"/>
-    </row>
-    <row r="123" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY122" s="3"/>
+      <c r="AZ122" s="3"/>
+      <c r="BA122" s="3"/>
+      <c r="BB122" s="3"/>
+    </row>
+    <row r="123" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -7154,8 +7685,12 @@
       <c r="AV123" s="3"/>
       <c r="AW123" s="3"/>
       <c r="AX123" s="3"/>
-    </row>
-    <row r="124" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY123" s="3"/>
+      <c r="AZ123" s="3"/>
+      <c r="BA123" s="3"/>
+      <c r="BB123" s="3"/>
+    </row>
+    <row r="124" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -7204,8 +7739,12 @@
       <c r="AV124" s="3"/>
       <c r="AW124" s="3"/>
       <c r="AX124" s="3"/>
-    </row>
-    <row r="125" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY124" s="3"/>
+      <c r="AZ124" s="3"/>
+      <c r="BA124" s="3"/>
+      <c r="BB124" s="3"/>
+    </row>
+    <row r="125" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -7254,8 +7793,12 @@
       <c r="AV125" s="3"/>
       <c r="AW125" s="3"/>
       <c r="AX125" s="3"/>
-    </row>
-    <row r="126" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY125" s="3"/>
+      <c r="AZ125" s="3"/>
+      <c r="BA125" s="3"/>
+      <c r="BB125" s="3"/>
+    </row>
+    <row r="126" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -7304,8 +7847,12 @@
       <c r="AV126" s="3"/>
       <c r="AW126" s="3"/>
       <c r="AX126" s="3"/>
-    </row>
-    <row r="127" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY126" s="3"/>
+      <c r="AZ126" s="3"/>
+      <c r="BA126" s="3"/>
+      <c r="BB126" s="3"/>
+    </row>
+    <row r="127" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -7354,8 +7901,12 @@
       <c r="AV127" s="3"/>
       <c r="AW127" s="3"/>
       <c r="AX127" s="3"/>
-    </row>
-    <row r="128" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY127" s="3"/>
+      <c r="AZ127" s="3"/>
+      <c r="BA127" s="3"/>
+      <c r="BB127" s="3"/>
+    </row>
+    <row r="128" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -7404,8 +7955,12 @@
       <c r="AV128" s="3"/>
       <c r="AW128" s="3"/>
       <c r="AX128" s="3"/>
-    </row>
-    <row r="129" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY128" s="3"/>
+      <c r="AZ128" s="3"/>
+      <c r="BA128" s="3"/>
+      <c r="BB128" s="3"/>
+    </row>
+    <row r="129" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -7454,8 +8009,12 @@
       <c r="AV129" s="3"/>
       <c r="AW129" s="3"/>
       <c r="AX129" s="3"/>
-    </row>
-    <row r="130" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY129" s="3"/>
+      <c r="AZ129" s="3"/>
+      <c r="BA129" s="3"/>
+      <c r="BB129" s="3"/>
+    </row>
+    <row r="130" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -7504,8 +8063,12 @@
       <c r="AV130" s="3"/>
       <c r="AW130" s="3"/>
       <c r="AX130" s="3"/>
-    </row>
-    <row r="131" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY130" s="3"/>
+      <c r="AZ130" s="3"/>
+      <c r="BA130" s="3"/>
+      <c r="BB130" s="3"/>
+    </row>
+    <row r="131" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -7554,8 +8117,12 @@
       <c r="AV131" s="3"/>
       <c r="AW131" s="3"/>
       <c r="AX131" s="3"/>
-    </row>
-    <row r="132" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY131" s="3"/>
+      <c r="AZ131" s="3"/>
+      <c r="BA131" s="3"/>
+      <c r="BB131" s="3"/>
+    </row>
+    <row r="132" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -7604,8 +8171,12 @@
       <c r="AV132" s="3"/>
       <c r="AW132" s="3"/>
       <c r="AX132" s="3"/>
-    </row>
-    <row r="133" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY132" s="3"/>
+      <c r="AZ132" s="3"/>
+      <c r="BA132" s="3"/>
+      <c r="BB132" s="3"/>
+    </row>
+    <row r="133" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -7654,8 +8225,12 @@
       <c r="AV133" s="3"/>
       <c r="AW133" s="3"/>
       <c r="AX133" s="3"/>
-    </row>
-    <row r="134" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY133" s="3"/>
+      <c r="AZ133" s="3"/>
+      <c r="BA133" s="3"/>
+      <c r="BB133" s="3"/>
+    </row>
+    <row r="134" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -7704,8 +8279,12 @@
       <c r="AV134" s="3"/>
       <c r="AW134" s="3"/>
       <c r="AX134" s="3"/>
-    </row>
-    <row r="135" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY134" s="3"/>
+      <c r="AZ134" s="3"/>
+      <c r="BA134" s="3"/>
+      <c r="BB134" s="3"/>
+    </row>
+    <row r="135" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -7754,8 +8333,12 @@
       <c r="AV135" s="3"/>
       <c r="AW135" s="3"/>
       <c r="AX135" s="3"/>
-    </row>
-    <row r="136" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY135" s="3"/>
+      <c r="AZ135" s="3"/>
+      <c r="BA135" s="3"/>
+      <c r="BB135" s="3"/>
+    </row>
+    <row r="136" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -7804,8 +8387,12 @@
       <c r="AV136" s="3"/>
       <c r="AW136" s="3"/>
       <c r="AX136" s="3"/>
-    </row>
-    <row r="137" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY136" s="3"/>
+      <c r="AZ136" s="3"/>
+      <c r="BA136" s="3"/>
+      <c r="BB136" s="3"/>
+    </row>
+    <row r="137" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -7854,8 +8441,12 @@
       <c r="AV137" s="3"/>
       <c r="AW137" s="3"/>
       <c r="AX137" s="3"/>
-    </row>
-    <row r="138" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY137" s="3"/>
+      <c r="AZ137" s="3"/>
+      <c r="BA137" s="3"/>
+      <c r="BB137" s="3"/>
+    </row>
+    <row r="138" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -7904,8 +8495,12 @@
       <c r="AV138" s="3"/>
       <c r="AW138" s="3"/>
       <c r="AX138" s="3"/>
-    </row>
-    <row r="139" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY138" s="3"/>
+      <c r="AZ138" s="3"/>
+      <c r="BA138" s="3"/>
+      <c r="BB138" s="3"/>
+    </row>
+    <row r="139" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -7954,8 +8549,12 @@
       <c r="AV139" s="3"/>
       <c r="AW139" s="3"/>
       <c r="AX139" s="3"/>
-    </row>
-    <row r="140" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY139" s="3"/>
+      <c r="AZ139" s="3"/>
+      <c r="BA139" s="3"/>
+      <c r="BB139" s="3"/>
+    </row>
+    <row r="140" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -8004,8 +8603,12 @@
       <c r="AV140" s="3"/>
       <c r="AW140" s="3"/>
       <c r="AX140" s="3"/>
-    </row>
-    <row r="141" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY140" s="3"/>
+      <c r="AZ140" s="3"/>
+      <c r="BA140" s="3"/>
+      <c r="BB140" s="3"/>
+    </row>
+    <row r="141" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -8054,8 +8657,12 @@
       <c r="AV141" s="3"/>
       <c r="AW141" s="3"/>
       <c r="AX141" s="3"/>
-    </row>
-    <row r="142" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY141" s="3"/>
+      <c r="AZ141" s="3"/>
+      <c r="BA141" s="3"/>
+      <c r="BB141" s="3"/>
+    </row>
+    <row r="142" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -8104,8 +8711,12 @@
       <c r="AV142" s="3"/>
       <c r="AW142" s="3"/>
       <c r="AX142" s="3"/>
-    </row>
-    <row r="143" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY142" s="3"/>
+      <c r="AZ142" s="3"/>
+      <c r="BA142" s="3"/>
+      <c r="BB142" s="3"/>
+    </row>
+    <row r="143" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -8154,8 +8765,12 @@
       <c r="AV143" s="3"/>
       <c r="AW143" s="3"/>
       <c r="AX143" s="3"/>
-    </row>
-    <row r="144" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY143" s="3"/>
+      <c r="AZ143" s="3"/>
+      <c r="BA143" s="3"/>
+      <c r="BB143" s="3"/>
+    </row>
+    <row r="144" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -8204,8 +8819,12 @@
       <c r="AV144" s="3"/>
       <c r="AW144" s="3"/>
       <c r="AX144" s="3"/>
-    </row>
-    <row r="145" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY144" s="3"/>
+      <c r="AZ144" s="3"/>
+      <c r="BA144" s="3"/>
+      <c r="BB144" s="3"/>
+    </row>
+    <row r="145" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -8254,8 +8873,12 @@
       <c r="AV145" s="3"/>
       <c r="AW145" s="3"/>
       <c r="AX145" s="3"/>
-    </row>
-    <row r="146" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY145" s="3"/>
+      <c r="AZ145" s="3"/>
+      <c r="BA145" s="3"/>
+      <c r="BB145" s="3"/>
+    </row>
+    <row r="146" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -8304,8 +8927,12 @@
       <c r="AV146" s="3"/>
       <c r="AW146" s="3"/>
       <c r="AX146" s="3"/>
-    </row>
-    <row r="147" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY146" s="3"/>
+      <c r="AZ146" s="3"/>
+      <c r="BA146" s="3"/>
+      <c r="BB146" s="3"/>
+    </row>
+    <row r="147" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -8354,8 +8981,12 @@
       <c r="AV147" s="3"/>
       <c r="AW147" s="3"/>
       <c r="AX147" s="3"/>
-    </row>
-    <row r="148" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY147" s="3"/>
+      <c r="AZ147" s="3"/>
+      <c r="BA147" s="3"/>
+      <c r="BB147" s="3"/>
+    </row>
+    <row r="148" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -8404,8 +9035,12 @@
       <c r="AV148" s="3"/>
       <c r="AW148" s="3"/>
       <c r="AX148" s="3"/>
-    </row>
-    <row r="149" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY148" s="3"/>
+      <c r="AZ148" s="3"/>
+      <c r="BA148" s="3"/>
+      <c r="BB148" s="3"/>
+    </row>
+    <row r="149" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -8454,8 +9089,12 @@
       <c r="AV149" s="3"/>
       <c r="AW149" s="3"/>
       <c r="AX149" s="3"/>
-    </row>
-    <row r="150" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY149" s="3"/>
+      <c r="AZ149" s="3"/>
+      <c r="BA149" s="3"/>
+      <c r="BB149" s="3"/>
+    </row>
+    <row r="150" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -8504,8 +9143,12 @@
       <c r="AV150" s="3"/>
       <c r="AW150" s="3"/>
       <c r="AX150" s="3"/>
-    </row>
-    <row r="151" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY150" s="3"/>
+      <c r="AZ150" s="3"/>
+      <c r="BA150" s="3"/>
+      <c r="BB150" s="3"/>
+    </row>
+    <row r="151" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -8554,8 +9197,12 @@
       <c r="AV151" s="3"/>
       <c r="AW151" s="3"/>
       <c r="AX151" s="3"/>
-    </row>
-    <row r="152" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY151" s="3"/>
+      <c r="AZ151" s="3"/>
+      <c r="BA151" s="3"/>
+      <c r="BB151" s="3"/>
+    </row>
+    <row r="152" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -8604,8 +9251,12 @@
       <c r="AV152" s="3"/>
       <c r="AW152" s="3"/>
       <c r="AX152" s="3"/>
-    </row>
-    <row r="153" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY152" s="3"/>
+      <c r="AZ152" s="3"/>
+      <c r="BA152" s="3"/>
+      <c r="BB152" s="3"/>
+    </row>
+    <row r="153" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -8654,8 +9305,12 @@
       <c r="AV153" s="3"/>
       <c r="AW153" s="3"/>
       <c r="AX153" s="3"/>
-    </row>
-    <row r="154" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY153" s="3"/>
+      <c r="AZ153" s="3"/>
+      <c r="BA153" s="3"/>
+      <c r="BB153" s="3"/>
+    </row>
+    <row r="154" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -8704,8 +9359,12 @@
       <c r="AV154" s="3"/>
       <c r="AW154" s="3"/>
       <c r="AX154" s="3"/>
-    </row>
-    <row r="155" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY154" s="3"/>
+      <c r="AZ154" s="3"/>
+      <c r="BA154" s="3"/>
+      <c r="BB154" s="3"/>
+    </row>
+    <row r="155" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -8754,8 +9413,12 @@
       <c r="AV155" s="3"/>
       <c r="AW155" s="3"/>
       <c r="AX155" s="3"/>
-    </row>
-    <row r="156" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY155" s="3"/>
+      <c r="AZ155" s="3"/>
+      <c r="BA155" s="3"/>
+      <c r="BB155" s="3"/>
+    </row>
+    <row r="156" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -8804,8 +9467,12 @@
       <c r="AV156" s="3"/>
       <c r="AW156" s="3"/>
       <c r="AX156" s="3"/>
-    </row>
-    <row r="157" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY156" s="3"/>
+      <c r="AZ156" s="3"/>
+      <c r="BA156" s="3"/>
+      <c r="BB156" s="3"/>
+    </row>
+    <row r="157" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -8854,8 +9521,12 @@
       <c r="AV157" s="3"/>
       <c r="AW157" s="3"/>
       <c r="AX157" s="3"/>
-    </row>
-    <row r="158" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY157" s="3"/>
+      <c r="AZ157" s="3"/>
+      <c r="BA157" s="3"/>
+      <c r="BB157" s="3"/>
+    </row>
+    <row r="158" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -8904,8 +9575,12 @@
       <c r="AV158" s="3"/>
       <c r="AW158" s="3"/>
       <c r="AX158" s="3"/>
-    </row>
-    <row r="159" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY158" s="3"/>
+      <c r="AZ158" s="3"/>
+      <c r="BA158" s="3"/>
+      <c r="BB158" s="3"/>
+    </row>
+    <row r="159" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -8954,8 +9629,12 @@
       <c r="AV159" s="3"/>
       <c r="AW159" s="3"/>
       <c r="AX159" s="3"/>
-    </row>
-    <row r="160" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY159" s="3"/>
+      <c r="AZ159" s="3"/>
+      <c r="BA159" s="3"/>
+      <c r="BB159" s="3"/>
+    </row>
+    <row r="160" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -9004,8 +9683,12 @@
       <c r="AV160" s="3"/>
       <c r="AW160" s="3"/>
       <c r="AX160" s="3"/>
-    </row>
-    <row r="161" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY160" s="3"/>
+      <c r="AZ160" s="3"/>
+      <c r="BA160" s="3"/>
+      <c r="BB160" s="3"/>
+    </row>
+    <row r="161" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -9054,8 +9737,12 @@
       <c r="AV161" s="3"/>
       <c r="AW161" s="3"/>
       <c r="AX161" s="3"/>
-    </row>
-    <row r="162" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY161" s="3"/>
+      <c r="AZ161" s="3"/>
+      <c r="BA161" s="3"/>
+      <c r="BB161" s="3"/>
+    </row>
+    <row r="162" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -9104,8 +9791,12 @@
       <c r="AV162" s="3"/>
       <c r="AW162" s="3"/>
       <c r="AX162" s="3"/>
-    </row>
-    <row r="163" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY162" s="3"/>
+      <c r="AZ162" s="3"/>
+      <c r="BA162" s="3"/>
+      <c r="BB162" s="3"/>
+    </row>
+    <row r="163" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -9154,8 +9845,12 @@
       <c r="AV163" s="3"/>
       <c r="AW163" s="3"/>
       <c r="AX163" s="3"/>
-    </row>
-    <row r="164" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY163" s="3"/>
+      <c r="AZ163" s="3"/>
+      <c r="BA163" s="3"/>
+      <c r="BB163" s="3"/>
+    </row>
+    <row r="164" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -9204,8 +9899,12 @@
       <c r="AV164" s="3"/>
       <c r="AW164" s="3"/>
       <c r="AX164" s="3"/>
-    </row>
-    <row r="165" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY164" s="3"/>
+      <c r="AZ164" s="3"/>
+      <c r="BA164" s="3"/>
+      <c r="BB164" s="3"/>
+    </row>
+    <row r="165" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -9254,8 +9953,12 @@
       <c r="AV165" s="3"/>
       <c r="AW165" s="3"/>
       <c r="AX165" s="3"/>
-    </row>
-    <row r="166" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY165" s="3"/>
+      <c r="AZ165" s="3"/>
+      <c r="BA165" s="3"/>
+      <c r="BB165" s="3"/>
+    </row>
+    <row r="166" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -9304,8 +10007,12 @@
       <c r="AV166" s="3"/>
       <c r="AW166" s="3"/>
       <c r="AX166" s="3"/>
-    </row>
-    <row r="167" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY166" s="3"/>
+      <c r="AZ166" s="3"/>
+      <c r="BA166" s="3"/>
+      <c r="BB166" s="3"/>
+    </row>
+    <row r="167" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -9354,8 +10061,12 @@
       <c r="AV167" s="3"/>
       <c r="AW167" s="3"/>
       <c r="AX167" s="3"/>
-    </row>
-    <row r="168" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY167" s="3"/>
+      <c r="AZ167" s="3"/>
+      <c r="BA167" s="3"/>
+      <c r="BB167" s="3"/>
+    </row>
+    <row r="168" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -9404,8 +10115,12 @@
       <c r="AV168" s="3"/>
       <c r="AW168" s="3"/>
       <c r="AX168" s="3"/>
-    </row>
-    <row r="169" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY168" s="3"/>
+      <c r="AZ168" s="3"/>
+      <c r="BA168" s="3"/>
+      <c r="BB168" s="3"/>
+    </row>
+    <row r="169" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -9454,8 +10169,12 @@
       <c r="AV169" s="3"/>
       <c r="AW169" s="3"/>
       <c r="AX169" s="3"/>
-    </row>
-    <row r="170" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY169" s="3"/>
+      <c r="AZ169" s="3"/>
+      <c r="BA169" s="3"/>
+      <c r="BB169" s="3"/>
+    </row>
+    <row r="170" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -9504,8 +10223,12 @@
       <c r="AV170" s="3"/>
       <c r="AW170" s="3"/>
       <c r="AX170" s="3"/>
-    </row>
-    <row r="171" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY170" s="3"/>
+      <c r="AZ170" s="3"/>
+      <c r="BA170" s="3"/>
+      <c r="BB170" s="3"/>
+    </row>
+    <row r="171" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -9554,8 +10277,12 @@
       <c r="AV171" s="3"/>
       <c r="AW171" s="3"/>
       <c r="AX171" s="3"/>
-    </row>
-    <row r="172" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY171" s="3"/>
+      <c r="AZ171" s="3"/>
+      <c r="BA171" s="3"/>
+      <c r="BB171" s="3"/>
+    </row>
+    <row r="172" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -9604,8 +10331,12 @@
       <c r="AV172" s="3"/>
       <c r="AW172" s="3"/>
       <c r="AX172" s="3"/>
-    </row>
-    <row r="173" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY172" s="3"/>
+      <c r="AZ172" s="3"/>
+      <c r="BA172" s="3"/>
+      <c r="BB172" s="3"/>
+    </row>
+    <row r="173" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -9654,8 +10385,12 @@
       <c r="AV173" s="3"/>
       <c r="AW173" s="3"/>
       <c r="AX173" s="3"/>
-    </row>
-    <row r="174" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY173" s="3"/>
+      <c r="AZ173" s="3"/>
+      <c r="BA173" s="3"/>
+      <c r="BB173" s="3"/>
+    </row>
+    <row r="174" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -9704,8 +10439,12 @@
       <c r="AV174" s="3"/>
       <c r="AW174" s="3"/>
       <c r="AX174" s="3"/>
-    </row>
-    <row r="175" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY174" s="3"/>
+      <c r="AZ174" s="3"/>
+      <c r="BA174" s="3"/>
+      <c r="BB174" s="3"/>
+    </row>
+    <row r="175" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -9754,8 +10493,12 @@
       <c r="AV175" s="3"/>
       <c r="AW175" s="3"/>
       <c r="AX175" s="3"/>
-    </row>
-    <row r="176" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY175" s="3"/>
+      <c r="AZ175" s="3"/>
+      <c r="BA175" s="3"/>
+      <c r="BB175" s="3"/>
+    </row>
+    <row r="176" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -9804,8 +10547,12 @@
       <c r="AV176" s="3"/>
       <c r="AW176" s="3"/>
       <c r="AX176" s="3"/>
-    </row>
-    <row r="177" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY176" s="3"/>
+      <c r="AZ176" s="3"/>
+      <c r="BA176" s="3"/>
+      <c r="BB176" s="3"/>
+    </row>
+    <row r="177" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -9854,8 +10601,12 @@
       <c r="AV177" s="3"/>
       <c r="AW177" s="3"/>
       <c r="AX177" s="3"/>
-    </row>
-    <row r="178" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY177" s="3"/>
+      <c r="AZ177" s="3"/>
+      <c r="BA177" s="3"/>
+      <c r="BB177" s="3"/>
+    </row>
+    <row r="178" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -9904,8 +10655,12 @@
       <c r="AV178" s="3"/>
       <c r="AW178" s="3"/>
       <c r="AX178" s="3"/>
-    </row>
-    <row r="179" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY178" s="3"/>
+      <c r="AZ178" s="3"/>
+      <c r="BA178" s="3"/>
+      <c r="BB178" s="3"/>
+    </row>
+    <row r="179" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -9954,8 +10709,12 @@
       <c r="AV179" s="3"/>
       <c r="AW179" s="3"/>
       <c r="AX179" s="3"/>
-    </row>
-    <row r="180" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY179" s="3"/>
+      <c r="AZ179" s="3"/>
+      <c r="BA179" s="3"/>
+      <c r="BB179" s="3"/>
+    </row>
+    <row r="180" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -10004,8 +10763,12 @@
       <c r="AV180" s="3"/>
       <c r="AW180" s="3"/>
       <c r="AX180" s="3"/>
-    </row>
-    <row r="181" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY180" s="3"/>
+      <c r="AZ180" s="3"/>
+      <c r="BA180" s="3"/>
+      <c r="BB180" s="3"/>
+    </row>
+    <row r="181" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -10054,8 +10817,12 @@
       <c r="AV181" s="3"/>
       <c r="AW181" s="3"/>
       <c r="AX181" s="3"/>
-    </row>
-    <row r="182" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY181" s="3"/>
+      <c r="AZ181" s="3"/>
+      <c r="BA181" s="3"/>
+      <c r="BB181" s="3"/>
+    </row>
+    <row r="182" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -10104,8 +10871,12 @@
       <c r="AV182" s="3"/>
       <c r="AW182" s="3"/>
       <c r="AX182" s="3"/>
-    </row>
-    <row r="183" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY182" s="3"/>
+      <c r="AZ182" s="3"/>
+      <c r="BA182" s="3"/>
+      <c r="BB182" s="3"/>
+    </row>
+    <row r="183" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -10154,8 +10925,12 @@
       <c r="AV183" s="3"/>
       <c r="AW183" s="3"/>
       <c r="AX183" s="3"/>
-    </row>
-    <row r="184" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY183" s="3"/>
+      <c r="AZ183" s="3"/>
+      <c r="BA183" s="3"/>
+      <c r="BB183" s="3"/>
+    </row>
+    <row r="184" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -10204,8 +10979,12 @@
       <c r="AV184" s="3"/>
       <c r="AW184" s="3"/>
       <c r="AX184" s="3"/>
-    </row>
-    <row r="185" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY184" s="3"/>
+      <c r="AZ184" s="3"/>
+      <c r="BA184" s="3"/>
+      <c r="BB184" s="3"/>
+    </row>
+    <row r="185" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -10254,8 +11033,12 @@
       <c r="AV185" s="3"/>
       <c r="AW185" s="3"/>
       <c r="AX185" s="3"/>
-    </row>
-    <row r="186" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY185" s="3"/>
+      <c r="AZ185" s="3"/>
+      <c r="BA185" s="3"/>
+      <c r="BB185" s="3"/>
+    </row>
+    <row r="186" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -10304,8 +11087,12 @@
       <c r="AV186" s="3"/>
       <c r="AW186" s="3"/>
       <c r="AX186" s="3"/>
-    </row>
-    <row r="187" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY186" s="3"/>
+      <c r="AZ186" s="3"/>
+      <c r="BA186" s="3"/>
+      <c r="BB186" s="3"/>
+    </row>
+    <row r="187" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -10354,8 +11141,12 @@
       <c r="AV187" s="3"/>
       <c r="AW187" s="3"/>
       <c r="AX187" s="3"/>
-    </row>
-    <row r="188" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY187" s="3"/>
+      <c r="AZ187" s="3"/>
+      <c r="BA187" s="3"/>
+      <c r="BB187" s="3"/>
+    </row>
+    <row r="188" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -10404,8 +11195,12 @@
       <c r="AV188" s="3"/>
       <c r="AW188" s="3"/>
       <c r="AX188" s="3"/>
-    </row>
-    <row r="189" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY188" s="3"/>
+      <c r="AZ188" s="3"/>
+      <c r="BA188" s="3"/>
+      <c r="BB188" s="3"/>
+    </row>
+    <row r="189" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -10454,8 +11249,12 @@
       <c r="AV189" s="3"/>
       <c r="AW189" s="3"/>
       <c r="AX189" s="3"/>
-    </row>
-    <row r="190" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY189" s="3"/>
+      <c r="AZ189" s="3"/>
+      <c r="BA189" s="3"/>
+      <c r="BB189" s="3"/>
+    </row>
+    <row r="190" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -10504,8 +11303,12 @@
       <c r="AV190" s="3"/>
       <c r="AW190" s="3"/>
       <c r="AX190" s="3"/>
-    </row>
-    <row r="191" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY190" s="3"/>
+      <c r="AZ190" s="3"/>
+      <c r="BA190" s="3"/>
+      <c r="BB190" s="3"/>
+    </row>
+    <row r="191" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -10554,8 +11357,12 @@
       <c r="AV191" s="3"/>
       <c r="AW191" s="3"/>
       <c r="AX191" s="3"/>
-    </row>
-    <row r="192" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY191" s="3"/>
+      <c r="AZ191" s="3"/>
+      <c r="BA191" s="3"/>
+      <c r="BB191" s="3"/>
+    </row>
+    <row r="192" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -10604,8 +11411,12 @@
       <c r="AV192" s="3"/>
       <c r="AW192" s="3"/>
       <c r="AX192" s="3"/>
-    </row>
-    <row r="193" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY192" s="3"/>
+      <c r="AZ192" s="3"/>
+      <c r="BA192" s="3"/>
+      <c r="BB192" s="3"/>
+    </row>
+    <row r="193" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -10654,8 +11465,12 @@
       <c r="AV193" s="3"/>
       <c r="AW193" s="3"/>
       <c r="AX193" s="3"/>
-    </row>
-    <row r="194" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY193" s="3"/>
+      <c r="AZ193" s="3"/>
+      <c r="BA193" s="3"/>
+      <c r="BB193" s="3"/>
+    </row>
+    <row r="194" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -10704,8 +11519,12 @@
       <c r="AV194" s="3"/>
       <c r="AW194" s="3"/>
       <c r="AX194" s="3"/>
-    </row>
-    <row r="195" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY194" s="3"/>
+      <c r="AZ194" s="3"/>
+      <c r="BA194" s="3"/>
+      <c r="BB194" s="3"/>
+    </row>
+    <row r="195" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -10754,8 +11573,12 @@
       <c r="AV195" s="3"/>
       <c r="AW195" s="3"/>
       <c r="AX195" s="3"/>
-    </row>
-    <row r="196" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY195" s="3"/>
+      <c r="AZ195" s="3"/>
+      <c r="BA195" s="3"/>
+      <c r="BB195" s="3"/>
+    </row>
+    <row r="196" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -10804,8 +11627,12 @@
       <c r="AV196" s="3"/>
       <c r="AW196" s="3"/>
       <c r="AX196" s="3"/>
-    </row>
-    <row r="197" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY196" s="3"/>
+      <c r="AZ196" s="3"/>
+      <c r="BA196" s="3"/>
+      <c r="BB196" s="3"/>
+    </row>
+    <row r="197" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -10854,8 +11681,12 @@
       <c r="AV197" s="3"/>
       <c r="AW197" s="3"/>
       <c r="AX197" s="3"/>
-    </row>
-    <row r="198" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY197" s="3"/>
+      <c r="AZ197" s="3"/>
+      <c r="BA197" s="3"/>
+      <c r="BB197" s="3"/>
+    </row>
+    <row r="198" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -10904,8 +11735,12 @@
       <c r="AV198" s="3"/>
       <c r="AW198" s="3"/>
       <c r="AX198" s="3"/>
-    </row>
-    <row r="199" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY198" s="3"/>
+      <c r="AZ198" s="3"/>
+      <c r="BA198" s="3"/>
+      <c r="BB198" s="3"/>
+    </row>
+    <row r="199" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -10954,8 +11789,12 @@
       <c r="AV199" s="3"/>
       <c r="AW199" s="3"/>
       <c r="AX199" s="3"/>
-    </row>
-    <row r="200" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY199" s="3"/>
+      <c r="AZ199" s="3"/>
+      <c r="BA199" s="3"/>
+      <c r="BB199" s="3"/>
+    </row>
+    <row r="200" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -11004,8 +11843,12 @@
       <c r="AV200" s="3"/>
       <c r="AW200" s="3"/>
       <c r="AX200" s="3"/>
-    </row>
-    <row r="201" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY200" s="3"/>
+      <c r="AZ200" s="3"/>
+      <c r="BA200" s="3"/>
+      <c r="BB200" s="3"/>
+    </row>
+    <row r="201" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -11054,8 +11897,12 @@
       <c r="AV201" s="3"/>
       <c r="AW201" s="3"/>
       <c r="AX201" s="3"/>
-    </row>
-    <row r="202" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY201" s="3"/>
+      <c r="AZ201" s="3"/>
+      <c r="BA201" s="3"/>
+      <c r="BB201" s="3"/>
+    </row>
+    <row r="202" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -11104,8 +11951,12 @@
       <c r="AV202" s="3"/>
       <c r="AW202" s="3"/>
       <c r="AX202" s="3"/>
-    </row>
-    <row r="203" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY202" s="3"/>
+      <c r="AZ202" s="3"/>
+      <c r="BA202" s="3"/>
+      <c r="BB202" s="3"/>
+    </row>
+    <row r="203" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -11154,8 +12005,12 @@
       <c r="AV203" s="3"/>
       <c r="AW203" s="3"/>
       <c r="AX203" s="3"/>
-    </row>
-    <row r="204" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY203" s="3"/>
+      <c r="AZ203" s="3"/>
+      <c r="BA203" s="3"/>
+      <c r="BB203" s="3"/>
+    </row>
+    <row r="204" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -11204,8 +12059,12 @@
       <c r="AV204" s="3"/>
       <c r="AW204" s="3"/>
       <c r="AX204" s="3"/>
-    </row>
-    <row r="205" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY204" s="3"/>
+      <c r="AZ204" s="3"/>
+      <c r="BA204" s="3"/>
+      <c r="BB204" s="3"/>
+    </row>
+    <row r="205" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -11254,8 +12113,12 @@
       <c r="AV205" s="3"/>
       <c r="AW205" s="3"/>
       <c r="AX205" s="3"/>
-    </row>
-    <row r="206" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY205" s="3"/>
+      <c r="AZ205" s="3"/>
+      <c r="BA205" s="3"/>
+      <c r="BB205" s="3"/>
+    </row>
+    <row r="206" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -11304,8 +12167,12 @@
       <c r="AV206" s="3"/>
       <c r="AW206" s="3"/>
       <c r="AX206" s="3"/>
-    </row>
-    <row r="207" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY206" s="3"/>
+      <c r="AZ206" s="3"/>
+      <c r="BA206" s="3"/>
+      <c r="BB206" s="3"/>
+    </row>
+    <row r="207" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -11354,8 +12221,12 @@
       <c r="AV207" s="3"/>
       <c r="AW207" s="3"/>
       <c r="AX207" s="3"/>
-    </row>
-    <row r="208" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY207" s="3"/>
+      <c r="AZ207" s="3"/>
+      <c r="BA207" s="3"/>
+      <c r="BB207" s="3"/>
+    </row>
+    <row r="208" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -11404,8 +12275,12 @@
       <c r="AV208" s="3"/>
       <c r="AW208" s="3"/>
       <c r="AX208" s="3"/>
-    </row>
-    <row r="209" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY208" s="3"/>
+      <c r="AZ208" s="3"/>
+      <c r="BA208" s="3"/>
+      <c r="BB208" s="3"/>
+    </row>
+    <row r="209" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -11454,8 +12329,12 @@
       <c r="AV209" s="3"/>
       <c r="AW209" s="3"/>
       <c r="AX209" s="3"/>
-    </row>
-    <row r="210" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY209" s="3"/>
+      <c r="AZ209" s="3"/>
+      <c r="BA209" s="3"/>
+      <c r="BB209" s="3"/>
+    </row>
+    <row r="210" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -11504,8 +12383,12 @@
       <c r="AV210" s="3"/>
       <c r="AW210" s="3"/>
       <c r="AX210" s="3"/>
-    </row>
-    <row r="211" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY210" s="3"/>
+      <c r="AZ210" s="3"/>
+      <c r="BA210" s="3"/>
+      <c r="BB210" s="3"/>
+    </row>
+    <row r="211" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -11554,8 +12437,12 @@
       <c r="AV211" s="3"/>
       <c r="AW211" s="3"/>
       <c r="AX211" s="3"/>
-    </row>
-    <row r="212" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY211" s="3"/>
+      <c r="AZ211" s="3"/>
+      <c r="BA211" s="3"/>
+      <c r="BB211" s="3"/>
+    </row>
+    <row r="212" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -11604,8 +12491,12 @@
       <c r="AV212" s="3"/>
       <c r="AW212" s="3"/>
       <c r="AX212" s="3"/>
-    </row>
-    <row r="213" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY212" s="3"/>
+      <c r="AZ212" s="3"/>
+      <c r="BA212" s="3"/>
+      <c r="BB212" s="3"/>
+    </row>
+    <row r="213" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -11654,8 +12545,12 @@
       <c r="AV213" s="3"/>
       <c r="AW213" s="3"/>
       <c r="AX213" s="3"/>
-    </row>
-    <row r="214" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY213" s="3"/>
+      <c r="AZ213" s="3"/>
+      <c r="BA213" s="3"/>
+      <c r="BB213" s="3"/>
+    </row>
+    <row r="214" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -11704,8 +12599,12 @@
       <c r="AV214" s="3"/>
       <c r="AW214" s="3"/>
       <c r="AX214" s="3"/>
-    </row>
-    <row r="215" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY214" s="3"/>
+      <c r="AZ214" s="3"/>
+      <c r="BA214" s="3"/>
+      <c r="BB214" s="3"/>
+    </row>
+    <row r="215" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -11754,8 +12653,12 @@
       <c r="AV215" s="3"/>
       <c r="AW215" s="3"/>
       <c r="AX215" s="3"/>
-    </row>
-    <row r="216" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY215" s="3"/>
+      <c r="AZ215" s="3"/>
+      <c r="BA215" s="3"/>
+      <c r="BB215" s="3"/>
+    </row>
+    <row r="216" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -11804,8 +12707,12 @@
       <c r="AV216" s="3"/>
       <c r="AW216" s="3"/>
       <c r="AX216" s="3"/>
-    </row>
-    <row r="217" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY216" s="3"/>
+      <c r="AZ216" s="3"/>
+      <c r="BA216" s="3"/>
+      <c r="BB216" s="3"/>
+    </row>
+    <row r="217" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -11854,8 +12761,12 @@
       <c r="AV217" s="3"/>
       <c r="AW217" s="3"/>
       <c r="AX217" s="3"/>
-    </row>
-    <row r="218" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY217" s="3"/>
+      <c r="AZ217" s="3"/>
+      <c r="BA217" s="3"/>
+      <c r="BB217" s="3"/>
+    </row>
+    <row r="218" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -11904,8 +12815,12 @@
       <c r="AV218" s="3"/>
       <c r="AW218" s="3"/>
       <c r="AX218" s="3"/>
-    </row>
-    <row r="219" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY218" s="3"/>
+      <c r="AZ218" s="3"/>
+      <c r="BA218" s="3"/>
+      <c r="BB218" s="3"/>
+    </row>
+    <row r="219" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -11954,8 +12869,12 @@
       <c r="AV219" s="3"/>
       <c r="AW219" s="3"/>
       <c r="AX219" s="3"/>
-    </row>
-    <row r="220" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY219" s="3"/>
+      <c r="AZ219" s="3"/>
+      <c r="BA219" s="3"/>
+      <c r="BB219" s="3"/>
+    </row>
+    <row r="220" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -12004,8 +12923,12 @@
       <c r="AV220" s="3"/>
       <c r="AW220" s="3"/>
       <c r="AX220" s="3"/>
-    </row>
-    <row r="221" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY220" s="3"/>
+      <c r="AZ220" s="3"/>
+      <c r="BA220" s="3"/>
+      <c r="BB220" s="3"/>
+    </row>
+    <row r="221" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -12054,8 +12977,12 @@
       <c r="AV221" s="3"/>
       <c r="AW221" s="3"/>
       <c r="AX221" s="3"/>
-    </row>
-    <row r="222" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY221" s="3"/>
+      <c r="AZ221" s="3"/>
+      <c r="BA221" s="3"/>
+      <c r="BB221" s="3"/>
+    </row>
+    <row r="222" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -12104,8 +13031,12 @@
       <c r="AV222" s="3"/>
       <c r="AW222" s="3"/>
       <c r="AX222" s="3"/>
-    </row>
-    <row r="223" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY222" s="3"/>
+      <c r="AZ222" s="3"/>
+      <c r="BA222" s="3"/>
+      <c r="BB222" s="3"/>
+    </row>
+    <row r="223" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -12154,8 +13085,12 @@
       <c r="AV223" s="3"/>
       <c r="AW223" s="3"/>
       <c r="AX223" s="3"/>
-    </row>
-    <row r="224" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY223" s="3"/>
+      <c r="AZ223" s="3"/>
+      <c r="BA223" s="3"/>
+      <c r="BB223" s="3"/>
+    </row>
+    <row r="224" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -12204,8 +13139,12 @@
       <c r="AV224" s="3"/>
       <c r="AW224" s="3"/>
       <c r="AX224" s="3"/>
-    </row>
-    <row r="225" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY224" s="3"/>
+      <c r="AZ224" s="3"/>
+      <c r="BA224" s="3"/>
+      <c r="BB224" s="3"/>
+    </row>
+    <row r="225" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -12254,8 +13193,12 @@
       <c r="AV225" s="3"/>
       <c r="AW225" s="3"/>
       <c r="AX225" s="3"/>
-    </row>
-    <row r="226" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY225" s="3"/>
+      <c r="AZ225" s="3"/>
+      <c r="BA225" s="3"/>
+      <c r="BB225" s="3"/>
+    </row>
+    <row r="226" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -12304,8 +13247,12 @@
       <c r="AV226" s="3"/>
       <c r="AW226" s="3"/>
       <c r="AX226" s="3"/>
-    </row>
-    <row r="227" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY226" s="3"/>
+      <c r="AZ226" s="3"/>
+      <c r="BA226" s="3"/>
+      <c r="BB226" s="3"/>
+    </row>
+    <row r="227" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -12354,8 +13301,12 @@
       <c r="AV227" s="3"/>
       <c r="AW227" s="3"/>
       <c r="AX227" s="3"/>
-    </row>
-    <row r="228" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY227" s="3"/>
+      <c r="AZ227" s="3"/>
+      <c r="BA227" s="3"/>
+      <c r="BB227" s="3"/>
+    </row>
+    <row r="228" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -12404,8 +13355,12 @@
       <c r="AV228" s="3"/>
       <c r="AW228" s="3"/>
       <c r="AX228" s="3"/>
-    </row>
-    <row r="229" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY228" s="3"/>
+      <c r="AZ228" s="3"/>
+      <c r="BA228" s="3"/>
+      <c r="BB228" s="3"/>
+    </row>
+    <row r="229" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -12454,8 +13409,12 @@
       <c r="AV229" s="3"/>
       <c r="AW229" s="3"/>
       <c r="AX229" s="3"/>
-    </row>
-    <row r="230" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY229" s="3"/>
+      <c r="AZ229" s="3"/>
+      <c r="BA229" s="3"/>
+      <c r="BB229" s="3"/>
+    </row>
+    <row r="230" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -12504,8 +13463,12 @@
       <c r="AV230" s="3"/>
       <c r="AW230" s="3"/>
       <c r="AX230" s="3"/>
-    </row>
-    <row r="231" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY230" s="3"/>
+      <c r="AZ230" s="3"/>
+      <c r="BA230" s="3"/>
+      <c r="BB230" s="3"/>
+    </row>
+    <row r="231" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -12554,8 +13517,12 @@
       <c r="AV231" s="3"/>
       <c r="AW231" s="3"/>
       <c r="AX231" s="3"/>
-    </row>
-    <row r="232" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY231" s="3"/>
+      <c r="AZ231" s="3"/>
+      <c r="BA231" s="3"/>
+      <c r="BB231" s="3"/>
+    </row>
+    <row r="232" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -12604,8 +13571,12 @@
       <c r="AV232" s="3"/>
       <c r="AW232" s="3"/>
       <c r="AX232" s="3"/>
-    </row>
-    <row r="233" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY232" s="3"/>
+      <c r="AZ232" s="3"/>
+      <c r="BA232" s="3"/>
+      <c r="BB232" s="3"/>
+    </row>
+    <row r="233" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -12654,8 +13625,12 @@
       <c r="AV233" s="3"/>
       <c r="AW233" s="3"/>
       <c r="AX233" s="3"/>
-    </row>
-    <row r="234" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY233" s="3"/>
+      <c r="AZ233" s="3"/>
+      <c r="BA233" s="3"/>
+      <c r="BB233" s="3"/>
+    </row>
+    <row r="234" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -12704,8 +13679,12 @@
       <c r="AV234" s="3"/>
       <c r="AW234" s="3"/>
       <c r="AX234" s="3"/>
-    </row>
-    <row r="235" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY234" s="3"/>
+      <c r="AZ234" s="3"/>
+      <c r="BA234" s="3"/>
+      <c r="BB234" s="3"/>
+    </row>
+    <row r="235" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -12754,8 +13733,12 @@
       <c r="AV235" s="3"/>
       <c r="AW235" s="3"/>
       <c r="AX235" s="3"/>
-    </row>
-    <row r="236" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY235" s="3"/>
+      <c r="AZ235" s="3"/>
+      <c r="BA235" s="3"/>
+      <c r="BB235" s="3"/>
+    </row>
+    <row r="236" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -12804,8 +13787,12 @@
       <c r="AV236" s="3"/>
       <c r="AW236" s="3"/>
       <c r="AX236" s="3"/>
-    </row>
-    <row r="237" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY236" s="3"/>
+      <c r="AZ236" s="3"/>
+      <c r="BA236" s="3"/>
+      <c r="BB236" s="3"/>
+    </row>
+    <row r="237" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -12854,8 +13841,12 @@
       <c r="AV237" s="3"/>
       <c r="AW237" s="3"/>
       <c r="AX237" s="3"/>
-    </row>
-    <row r="238" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY237" s="3"/>
+      <c r="AZ237" s="3"/>
+      <c r="BA237" s="3"/>
+      <c r="BB237" s="3"/>
+    </row>
+    <row r="238" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -12904,8 +13895,12 @@
       <c r="AV238" s="3"/>
       <c r="AW238" s="3"/>
       <c r="AX238" s="3"/>
-    </row>
-    <row r="239" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY238" s="3"/>
+      <c r="AZ238" s="3"/>
+      <c r="BA238" s="3"/>
+      <c r="BB238" s="3"/>
+    </row>
+    <row r="239" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -12954,8 +13949,12 @@
       <c r="AV239" s="3"/>
       <c r="AW239" s="3"/>
       <c r="AX239" s="3"/>
-    </row>
-    <row r="240" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY239" s="3"/>
+      <c r="AZ239" s="3"/>
+      <c r="BA239" s="3"/>
+      <c r="BB239" s="3"/>
+    </row>
+    <row r="240" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -13004,8 +14003,12 @@
       <c r="AV240" s="3"/>
       <c r="AW240" s="3"/>
       <c r="AX240" s="3"/>
-    </row>
-    <row r="241" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY240" s="3"/>
+      <c r="AZ240" s="3"/>
+      <c r="BA240" s="3"/>
+      <c r="BB240" s="3"/>
+    </row>
+    <row r="241" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -13054,8 +14057,12 @@
       <c r="AV241" s="3"/>
       <c r="AW241" s="3"/>
       <c r="AX241" s="3"/>
-    </row>
-    <row r="242" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY241" s="3"/>
+      <c r="AZ241" s="3"/>
+      <c r="BA241" s="3"/>
+      <c r="BB241" s="3"/>
+    </row>
+    <row r="242" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -13104,8 +14111,12 @@
       <c r="AV242" s="3"/>
       <c r="AW242" s="3"/>
       <c r="AX242" s="3"/>
-    </row>
-    <row r="243" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY242" s="3"/>
+      <c r="AZ242" s="3"/>
+      <c r="BA242" s="3"/>
+      <c r="BB242" s="3"/>
+    </row>
+    <row r="243" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -13154,8 +14165,12 @@
       <c r="AV243" s="3"/>
       <c r="AW243" s="3"/>
       <c r="AX243" s="3"/>
-    </row>
-    <row r="244" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY243" s="3"/>
+      <c r="AZ243" s="3"/>
+      <c r="BA243" s="3"/>
+      <c r="BB243" s="3"/>
+    </row>
+    <row r="244" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -13204,8 +14219,12 @@
       <c r="AV244" s="3"/>
       <c r="AW244" s="3"/>
       <c r="AX244" s="3"/>
-    </row>
-    <row r="245" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY244" s="3"/>
+      <c r="AZ244" s="3"/>
+      <c r="BA244" s="3"/>
+      <c r="BB244" s="3"/>
+    </row>
+    <row r="245" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -13254,8 +14273,12 @@
       <c r="AV245" s="3"/>
       <c r="AW245" s="3"/>
       <c r="AX245" s="3"/>
-    </row>
-    <row r="246" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY245" s="3"/>
+      <c r="AZ245" s="3"/>
+      <c r="BA245" s="3"/>
+      <c r="BB245" s="3"/>
+    </row>
+    <row r="246" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -13304,8 +14327,12 @@
       <c r="AV246" s="3"/>
       <c r="AW246" s="3"/>
       <c r="AX246" s="3"/>
-    </row>
-    <row r="247" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY246" s="3"/>
+      <c r="AZ246" s="3"/>
+      <c r="BA246" s="3"/>
+      <c r="BB246" s="3"/>
+    </row>
+    <row r="247" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -13354,8 +14381,12 @@
       <c r="AV247" s="3"/>
       <c r="AW247" s="3"/>
       <c r="AX247" s="3"/>
-    </row>
-    <row r="248" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY247" s="3"/>
+      <c r="AZ247" s="3"/>
+      <c r="BA247" s="3"/>
+      <c r="BB247" s="3"/>
+    </row>
+    <row r="248" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -13404,8 +14435,12 @@
       <c r="AV248" s="3"/>
       <c r="AW248" s="3"/>
       <c r="AX248" s="3"/>
-    </row>
-    <row r="249" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY248" s="3"/>
+      <c r="AZ248" s="3"/>
+      <c r="BA248" s="3"/>
+      <c r="BB248" s="3"/>
+    </row>
+    <row r="249" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -13454,8 +14489,12 @@
       <c r="AV249" s="3"/>
       <c r="AW249" s="3"/>
       <c r="AX249" s="3"/>
-    </row>
-    <row r="250" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY249" s="3"/>
+      <c r="AZ249" s="3"/>
+      <c r="BA249" s="3"/>
+      <c r="BB249" s="3"/>
+    </row>
+    <row r="250" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -13504,8 +14543,12 @@
       <c r="AV250" s="3"/>
       <c r="AW250" s="3"/>
       <c r="AX250" s="3"/>
-    </row>
-    <row r="251" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY250" s="3"/>
+      <c r="AZ250" s="3"/>
+      <c r="BA250" s="3"/>
+      <c r="BB250" s="3"/>
+    </row>
+    <row r="251" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -13554,8 +14597,12 @@
       <c r="AV251" s="3"/>
       <c r="AW251" s="3"/>
       <c r="AX251" s="3"/>
-    </row>
-    <row r="252" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY251" s="3"/>
+      <c r="AZ251" s="3"/>
+      <c r="BA251" s="3"/>
+      <c r="BB251" s="3"/>
+    </row>
+    <row r="252" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -13604,8 +14651,12 @@
       <c r="AV252" s="3"/>
       <c r="AW252" s="3"/>
       <c r="AX252" s="3"/>
-    </row>
-    <row r="253" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY252" s="3"/>
+      <c r="AZ252" s="3"/>
+      <c r="BA252" s="3"/>
+      <c r="BB252" s="3"/>
+    </row>
+    <row r="253" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -13654,8 +14705,12 @@
       <c r="AV253" s="3"/>
       <c r="AW253" s="3"/>
       <c r="AX253" s="3"/>
-    </row>
-    <row r="254" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY253" s="3"/>
+      <c r="AZ253" s="3"/>
+      <c r="BA253" s="3"/>
+      <c r="BB253" s="3"/>
+    </row>
+    <row r="254" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -13704,8 +14759,12 @@
       <c r="AV254" s="3"/>
       <c r="AW254" s="3"/>
       <c r="AX254" s="3"/>
-    </row>
-    <row r="255" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY254" s="3"/>
+      <c r="AZ254" s="3"/>
+      <c r="BA254" s="3"/>
+      <c r="BB254" s="3"/>
+    </row>
+    <row r="255" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -13754,8 +14813,12 @@
       <c r="AV255" s="3"/>
       <c r="AW255" s="3"/>
       <c r="AX255" s="3"/>
-    </row>
-    <row r="256" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY255" s="3"/>
+      <c r="AZ255" s="3"/>
+      <c r="BA255" s="3"/>
+      <c r="BB255" s="3"/>
+    </row>
+    <row r="256" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -13804,8 +14867,12 @@
       <c r="AV256" s="3"/>
       <c r="AW256" s="3"/>
       <c r="AX256" s="3"/>
-    </row>
-    <row r="257" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY256" s="3"/>
+      <c r="AZ256" s="3"/>
+      <c r="BA256" s="3"/>
+      <c r="BB256" s="3"/>
+    </row>
+    <row r="257" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -13854,8 +14921,12 @@
       <c r="AV257" s="3"/>
       <c r="AW257" s="3"/>
       <c r="AX257" s="3"/>
-    </row>
-    <row r="258" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY257" s="3"/>
+      <c r="AZ257" s="3"/>
+      <c r="BA257" s="3"/>
+      <c r="BB257" s="3"/>
+    </row>
+    <row r="258" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -13904,8 +14975,12 @@
       <c r="AV258" s="3"/>
       <c r="AW258" s="3"/>
       <c r="AX258" s="3"/>
-    </row>
-    <row r="259" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY258" s="3"/>
+      <c r="AZ258" s="3"/>
+      <c r="BA258" s="3"/>
+      <c r="BB258" s="3"/>
+    </row>
+    <row r="259" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -13954,8 +15029,12 @@
       <c r="AV259" s="3"/>
       <c r="AW259" s="3"/>
       <c r="AX259" s="3"/>
-    </row>
-    <row r="260" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY259" s="3"/>
+      <c r="AZ259" s="3"/>
+      <c r="BA259" s="3"/>
+      <c r="BB259" s="3"/>
+    </row>
+    <row r="260" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -14004,8 +15083,12 @@
       <c r="AV260" s="3"/>
       <c r="AW260" s="3"/>
       <c r="AX260" s="3"/>
-    </row>
-    <row r="261" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY260" s="3"/>
+      <c r="AZ260" s="3"/>
+      <c r="BA260" s="3"/>
+      <c r="BB260" s="3"/>
+    </row>
+    <row r="261" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -14054,8 +15137,12 @@
       <c r="AV261" s="3"/>
       <c r="AW261" s="3"/>
       <c r="AX261" s="3"/>
-    </row>
-    <row r="262" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY261" s="3"/>
+      <c r="AZ261" s="3"/>
+      <c r="BA261" s="3"/>
+      <c r="BB261" s="3"/>
+    </row>
+    <row r="262" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -14104,8 +15191,12 @@
       <c r="AV262" s="3"/>
       <c r="AW262" s="3"/>
       <c r="AX262" s="3"/>
-    </row>
-    <row r="263" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY262" s="3"/>
+      <c r="AZ262" s="3"/>
+      <c r="BA262" s="3"/>
+      <c r="BB262" s="3"/>
+    </row>
+    <row r="263" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -14154,8 +15245,12 @@
       <c r="AV263" s="3"/>
       <c r="AW263" s="3"/>
       <c r="AX263" s="3"/>
-    </row>
-    <row r="264" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY263" s="3"/>
+      <c r="AZ263" s="3"/>
+      <c r="BA263" s="3"/>
+      <c r="BB263" s="3"/>
+    </row>
+    <row r="264" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -14204,8 +15299,12 @@
       <c r="AV264" s="3"/>
       <c r="AW264" s="3"/>
       <c r="AX264" s="3"/>
-    </row>
-    <row r="265" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY264" s="3"/>
+      <c r="AZ264" s="3"/>
+      <c r="BA264" s="3"/>
+      <c r="BB264" s="3"/>
+    </row>
+    <row r="265" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -14254,8 +15353,12 @@
       <c r="AV265" s="3"/>
       <c r="AW265" s="3"/>
       <c r="AX265" s="3"/>
-    </row>
-    <row r="266" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY265" s="3"/>
+      <c r="AZ265" s="3"/>
+      <c r="BA265" s="3"/>
+      <c r="BB265" s="3"/>
+    </row>
+    <row r="266" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -14304,8 +15407,12 @@
       <c r="AV266" s="3"/>
       <c r="AW266" s="3"/>
       <c r="AX266" s="3"/>
-    </row>
-    <row r="267" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY266" s="3"/>
+      <c r="AZ266" s="3"/>
+      <c r="BA266" s="3"/>
+      <c r="BB266" s="3"/>
+    </row>
+    <row r="267" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -14354,8 +15461,12 @@
       <c r="AV267" s="3"/>
       <c r="AW267" s="3"/>
       <c r="AX267" s="3"/>
-    </row>
-    <row r="268" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY267" s="3"/>
+      <c r="AZ267" s="3"/>
+      <c r="BA267" s="3"/>
+      <c r="BB267" s="3"/>
+    </row>
+    <row r="268" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -14404,8 +15515,12 @@
       <c r="AV268" s="3"/>
       <c r="AW268" s="3"/>
       <c r="AX268" s="3"/>
-    </row>
-    <row r="269" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY268" s="3"/>
+      <c r="AZ268" s="3"/>
+      <c r="BA268" s="3"/>
+      <c r="BB268" s="3"/>
+    </row>
+    <row r="269" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -14454,8 +15569,12 @@
       <c r="AV269" s="3"/>
       <c r="AW269" s="3"/>
       <c r="AX269" s="3"/>
-    </row>
-    <row r="270" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY269" s="3"/>
+      <c r="AZ269" s="3"/>
+      <c r="BA269" s="3"/>
+      <c r="BB269" s="3"/>
+    </row>
+    <row r="270" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -14504,8 +15623,12 @@
       <c r="AV270" s="3"/>
       <c r="AW270" s="3"/>
       <c r="AX270" s="3"/>
-    </row>
-    <row r="271" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY270" s="3"/>
+      <c r="AZ270" s="3"/>
+      <c r="BA270" s="3"/>
+      <c r="BB270" s="3"/>
+    </row>
+    <row r="271" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -14554,8 +15677,12 @@
       <c r="AV271" s="3"/>
       <c r="AW271" s="3"/>
       <c r="AX271" s="3"/>
-    </row>
-    <row r="272" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY271" s="3"/>
+      <c r="AZ271" s="3"/>
+      <c r="BA271" s="3"/>
+      <c r="BB271" s="3"/>
+    </row>
+    <row r="272" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -14604,8 +15731,12 @@
       <c r="AV272" s="3"/>
       <c r="AW272" s="3"/>
       <c r="AX272" s="3"/>
-    </row>
-    <row r="273" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY272" s="3"/>
+      <c r="AZ272" s="3"/>
+      <c r="BA272" s="3"/>
+      <c r="BB272" s="3"/>
+    </row>
+    <row r="273" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -14654,8 +15785,12 @@
       <c r="AV273" s="3"/>
       <c r="AW273" s="3"/>
       <c r="AX273" s="3"/>
-    </row>
-    <row r="274" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY273" s="3"/>
+      <c r="AZ273" s="3"/>
+      <c r="BA273" s="3"/>
+      <c r="BB273" s="3"/>
+    </row>
+    <row r="274" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -14704,8 +15839,12 @@
       <c r="AV274" s="3"/>
       <c r="AW274" s="3"/>
       <c r="AX274" s="3"/>
-    </row>
-    <row r="275" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY274" s="3"/>
+      <c r="AZ274" s="3"/>
+      <c r="BA274" s="3"/>
+      <c r="BB274" s="3"/>
+    </row>
+    <row r="275" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -14754,8 +15893,12 @@
       <c r="AV275" s="3"/>
       <c r="AW275" s="3"/>
       <c r="AX275" s="3"/>
-    </row>
-    <row r="276" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY275" s="3"/>
+      <c r="AZ275" s="3"/>
+      <c r="BA275" s="3"/>
+      <c r="BB275" s="3"/>
+    </row>
+    <row r="276" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -14804,8 +15947,12 @@
       <c r="AV276" s="3"/>
       <c r="AW276" s="3"/>
       <c r="AX276" s="3"/>
-    </row>
-    <row r="277" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY276" s="3"/>
+      <c r="AZ276" s="3"/>
+      <c r="BA276" s="3"/>
+      <c r="BB276" s="3"/>
+    </row>
+    <row r="277" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -14854,8 +16001,12 @@
       <c r="AV277" s="3"/>
       <c r="AW277" s="3"/>
       <c r="AX277" s="3"/>
-    </row>
-    <row r="278" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY277" s="3"/>
+      <c r="AZ277" s="3"/>
+      <c r="BA277" s="3"/>
+      <c r="BB277" s="3"/>
+    </row>
+    <row r="278" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -14904,8 +16055,12 @@
       <c r="AV278" s="3"/>
       <c r="AW278" s="3"/>
       <c r="AX278" s="3"/>
-    </row>
-    <row r="279" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY278" s="3"/>
+      <c r="AZ278" s="3"/>
+      <c r="BA278" s="3"/>
+      <c r="BB278" s="3"/>
+    </row>
+    <row r="279" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -14954,8 +16109,12 @@
       <c r="AV279" s="3"/>
       <c r="AW279" s="3"/>
       <c r="AX279" s="3"/>
-    </row>
-    <row r="280" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY279" s="3"/>
+      <c r="AZ279" s="3"/>
+      <c r="BA279" s="3"/>
+      <c r="BB279" s="3"/>
+    </row>
+    <row r="280" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -15004,8 +16163,12 @@
       <c r="AV280" s="3"/>
       <c r="AW280" s="3"/>
       <c r="AX280" s="3"/>
-    </row>
-    <row r="281" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY280" s="3"/>
+      <c r="AZ280" s="3"/>
+      <c r="BA280" s="3"/>
+      <c r="BB280" s="3"/>
+    </row>
+    <row r="281" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -15054,8 +16217,12 @@
       <c r="AV281" s="3"/>
       <c r="AW281" s="3"/>
       <c r="AX281" s="3"/>
-    </row>
-    <row r="282" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY281" s="3"/>
+      <c r="AZ281" s="3"/>
+      <c r="BA281" s="3"/>
+      <c r="BB281" s="3"/>
+    </row>
+    <row r="282" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -15104,8 +16271,12 @@
       <c r="AV282" s="3"/>
       <c r="AW282" s="3"/>
       <c r="AX282" s="3"/>
-    </row>
-    <row r="283" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY282" s="3"/>
+      <c r="AZ282" s="3"/>
+      <c r="BA282" s="3"/>
+      <c r="BB282" s="3"/>
+    </row>
+    <row r="283" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -15154,8 +16325,12 @@
       <c r="AV283" s="3"/>
       <c r="AW283" s="3"/>
       <c r="AX283" s="3"/>
-    </row>
-    <row r="284" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY283" s="3"/>
+      <c r="AZ283" s="3"/>
+      <c r="BA283" s="3"/>
+      <c r="BB283" s="3"/>
+    </row>
+    <row r="284" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -15204,8 +16379,12 @@
       <c r="AV284" s="3"/>
       <c r="AW284" s="3"/>
       <c r="AX284" s="3"/>
-    </row>
-    <row r="285" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY284" s="3"/>
+      <c r="AZ284" s="3"/>
+      <c r="BA284" s="3"/>
+      <c r="BB284" s="3"/>
+    </row>
+    <row r="285" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -15254,8 +16433,12 @@
       <c r="AV285" s="3"/>
       <c r="AW285" s="3"/>
       <c r="AX285" s="3"/>
-    </row>
-    <row r="286" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY285" s="3"/>
+      <c r="AZ285" s="3"/>
+      <c r="BA285" s="3"/>
+      <c r="BB285" s="3"/>
+    </row>
+    <row r="286" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -15304,8 +16487,12 @@
       <c r="AV286" s="3"/>
       <c r="AW286" s="3"/>
       <c r="AX286" s="3"/>
-    </row>
-    <row r="287" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY286" s="3"/>
+      <c r="AZ286" s="3"/>
+      <c r="BA286" s="3"/>
+      <c r="BB286" s="3"/>
+    </row>
+    <row r="287" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -15354,8 +16541,12 @@
       <c r="AV287" s="3"/>
       <c r="AW287" s="3"/>
       <c r="AX287" s="3"/>
-    </row>
-    <row r="288" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY287" s="3"/>
+      <c r="AZ287" s="3"/>
+      <c r="BA287" s="3"/>
+      <c r="BB287" s="3"/>
+    </row>
+    <row r="288" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -15404,8 +16595,12 @@
       <c r="AV288" s="3"/>
       <c r="AW288" s="3"/>
       <c r="AX288" s="3"/>
-    </row>
-    <row r="289" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY288" s="3"/>
+      <c r="AZ288" s="3"/>
+      <c r="BA288" s="3"/>
+      <c r="BB288" s="3"/>
+    </row>
+    <row r="289" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -15454,8 +16649,12 @@
       <c r="AV289" s="3"/>
       <c r="AW289" s="3"/>
       <c r="AX289" s="3"/>
-    </row>
-    <row r="290" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY289" s="3"/>
+      <c r="AZ289" s="3"/>
+      <c r="BA289" s="3"/>
+      <c r="BB289" s="3"/>
+    </row>
+    <row r="290" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -15504,8 +16703,12 @@
       <c r="AV290" s="3"/>
       <c r="AW290" s="3"/>
       <c r="AX290" s="3"/>
-    </row>
-    <row r="291" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY290" s="3"/>
+      <c r="AZ290" s="3"/>
+      <c r="BA290" s="3"/>
+      <c r="BB290" s="3"/>
+    </row>
+    <row r="291" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -15554,8 +16757,12 @@
       <c r="AV291" s="3"/>
       <c r="AW291" s="3"/>
       <c r="AX291" s="3"/>
-    </row>
-    <row r="292" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY291" s="3"/>
+      <c r="AZ291" s="3"/>
+      <c r="BA291" s="3"/>
+      <c r="BB291" s="3"/>
+    </row>
+    <row r="292" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -15604,8 +16811,12 @@
       <c r="AV292" s="3"/>
       <c r="AW292" s="3"/>
       <c r="AX292" s="3"/>
-    </row>
-    <row r="293" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY292" s="3"/>
+      <c r="AZ292" s="3"/>
+      <c r="BA292" s="3"/>
+      <c r="BB292" s="3"/>
+    </row>
+    <row r="293" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -15654,8 +16865,12 @@
       <c r="AV293" s="3"/>
       <c r="AW293" s="3"/>
       <c r="AX293" s="3"/>
-    </row>
-    <row r="294" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY293" s="3"/>
+      <c r="AZ293" s="3"/>
+      <c r="BA293" s="3"/>
+      <c r="BB293" s="3"/>
+    </row>
+    <row r="294" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -15704,8 +16919,12 @@
       <c r="AV294" s="3"/>
       <c r="AW294" s="3"/>
       <c r="AX294" s="3"/>
-    </row>
-    <row r="295" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY294" s="3"/>
+      <c r="AZ294" s="3"/>
+      <c r="BA294" s="3"/>
+      <c r="BB294" s="3"/>
+    </row>
+    <row r="295" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -15754,8 +16973,12 @@
       <c r="AV295" s="3"/>
       <c r="AW295" s="3"/>
       <c r="AX295" s="3"/>
-    </row>
-    <row r="296" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY295" s="3"/>
+      <c r="AZ295" s="3"/>
+      <c r="BA295" s="3"/>
+      <c r="BB295" s="3"/>
+    </row>
+    <row r="296" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -15804,8 +17027,12 @@
       <c r="AV296" s="3"/>
       <c r="AW296" s="3"/>
       <c r="AX296" s="3"/>
-    </row>
-    <row r="297" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY296" s="3"/>
+      <c r="AZ296" s="3"/>
+      <c r="BA296" s="3"/>
+      <c r="BB296" s="3"/>
+    </row>
+    <row r="297" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -15854,8 +17081,12 @@
       <c r="AV297" s="3"/>
       <c r="AW297" s="3"/>
       <c r="AX297" s="3"/>
-    </row>
-    <row r="298" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY297" s="3"/>
+      <c r="AZ297" s="3"/>
+      <c r="BA297" s="3"/>
+      <c r="BB297" s="3"/>
+    </row>
+    <row r="298" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -15904,8 +17135,12 @@
       <c r="AV298" s="3"/>
       <c r="AW298" s="3"/>
       <c r="AX298" s="3"/>
-    </row>
-    <row r="299" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY298" s="3"/>
+      <c r="AZ298" s="3"/>
+      <c r="BA298" s="3"/>
+      <c r="BB298" s="3"/>
+    </row>
+    <row r="299" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -15954,8 +17189,12 @@
       <c r="AV299" s="3"/>
       <c r="AW299" s="3"/>
       <c r="AX299" s="3"/>
-    </row>
-    <row r="300" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY299" s="3"/>
+      <c r="AZ299" s="3"/>
+      <c r="BA299" s="3"/>
+      <c r="BB299" s="3"/>
+    </row>
+    <row r="300" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -16004,8 +17243,12 @@
       <c r="AV300" s="3"/>
       <c r="AW300" s="3"/>
       <c r="AX300" s="3"/>
-    </row>
-    <row r="301" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY300" s="3"/>
+      <c r="AZ300" s="3"/>
+      <c r="BA300" s="3"/>
+      <c r="BB300" s="3"/>
+    </row>
+    <row r="301" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -16054,8 +17297,12 @@
       <c r="AV301" s="3"/>
       <c r="AW301" s="3"/>
       <c r="AX301" s="3"/>
-    </row>
-    <row r="302" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY301" s="3"/>
+      <c r="AZ301" s="3"/>
+      <c r="BA301" s="3"/>
+      <c r="BB301" s="3"/>
+    </row>
+    <row r="302" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -16104,8 +17351,12 @@
       <c r="AV302" s="3"/>
       <c r="AW302" s="3"/>
       <c r="AX302" s="3"/>
-    </row>
-    <row r="303" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY302" s="3"/>
+      <c r="AZ302" s="3"/>
+      <c r="BA302" s="3"/>
+      <c r="BB302" s="3"/>
+    </row>
+    <row r="303" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="3"/>
@@ -16154,8 +17405,12 @@
       <c r="AV303" s="3"/>
       <c r="AW303" s="3"/>
       <c r="AX303" s="3"/>
-    </row>
-    <row r="304" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY303" s="3"/>
+      <c r="AZ303" s="3"/>
+      <c r="BA303" s="3"/>
+      <c r="BB303" s="3"/>
+    </row>
+    <row r="304" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
@@ -16204,8 +17459,12 @@
       <c r="AV304" s="3"/>
       <c r="AW304" s="3"/>
       <c r="AX304" s="3"/>
-    </row>
-    <row r="305" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY304" s="3"/>
+      <c r="AZ304" s="3"/>
+      <c r="BA304" s="3"/>
+      <c r="BB304" s="3"/>
+    </row>
+    <row r="305" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="3"/>
@@ -16254,8 +17513,12 @@
       <c r="AV305" s="3"/>
       <c r="AW305" s="3"/>
       <c r="AX305" s="3"/>
-    </row>
-    <row r="306" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY305" s="3"/>
+      <c r="AZ305" s="3"/>
+      <c r="BA305" s="3"/>
+      <c r="BB305" s="3"/>
+    </row>
+    <row r="306" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="3"/>
@@ -16304,8 +17567,12 @@
       <c r="AV306" s="3"/>
       <c r="AW306" s="3"/>
       <c r="AX306" s="3"/>
-    </row>
-    <row r="307" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY306" s="3"/>
+      <c r="AZ306" s="3"/>
+      <c r="BA306" s="3"/>
+      <c r="BB306" s="3"/>
+    </row>
+    <row r="307" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="3"/>
@@ -16354,8 +17621,12 @@
       <c r="AV307" s="3"/>
       <c r="AW307" s="3"/>
       <c r="AX307" s="3"/>
-    </row>
-    <row r="308" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY307" s="3"/>
+      <c r="AZ307" s="3"/>
+      <c r="BA307" s="3"/>
+      <c r="BB307" s="3"/>
+    </row>
+    <row r="308" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="3"/>
@@ -16404,8 +17675,12 @@
       <c r="AV308" s="3"/>
       <c r="AW308" s="3"/>
       <c r="AX308" s="3"/>
-    </row>
-    <row r="309" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY308" s="3"/>
+      <c r="AZ308" s="3"/>
+      <c r="BA308" s="3"/>
+      <c r="BB308" s="3"/>
+    </row>
+    <row r="309" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="3"/>
@@ -16454,8 +17729,12 @@
       <c r="AV309" s="3"/>
       <c r="AW309" s="3"/>
       <c r="AX309" s="3"/>
-    </row>
-    <row r="310" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY309" s="3"/>
+      <c r="AZ309" s="3"/>
+      <c r="BA309" s="3"/>
+      <c r="BB309" s="3"/>
+    </row>
+    <row r="310" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="3"/>
@@ -16504,8 +17783,12 @@
       <c r="AV310" s="3"/>
       <c r="AW310" s="3"/>
       <c r="AX310" s="3"/>
-    </row>
-    <row r="311" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY310" s="3"/>
+      <c r="AZ310" s="3"/>
+      <c r="BA310" s="3"/>
+      <c r="BB310" s="3"/>
+    </row>
+    <row r="311" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="3"/>
@@ -16554,8 +17837,12 @@
       <c r="AV311" s="3"/>
       <c r="AW311" s="3"/>
       <c r="AX311" s="3"/>
-    </row>
-    <row r="312" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY311" s="3"/>
+      <c r="AZ311" s="3"/>
+      <c r="BA311" s="3"/>
+      <c r="BB311" s="3"/>
+    </row>
+    <row r="312" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
@@ -16604,8 +17891,12 @@
       <c r="AV312" s="3"/>
       <c r="AW312" s="3"/>
       <c r="AX312" s="3"/>
-    </row>
-    <row r="313" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY312" s="3"/>
+      <c r="AZ312" s="3"/>
+      <c r="BA312" s="3"/>
+      <c r="BB312" s="3"/>
+    </row>
+    <row r="313" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="3"/>
@@ -16654,8 +17945,12 @@
       <c r="AV313" s="3"/>
       <c r="AW313" s="3"/>
       <c r="AX313" s="3"/>
-    </row>
-    <row r="314" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY313" s="3"/>
+      <c r="AZ313" s="3"/>
+      <c r="BA313" s="3"/>
+      <c r="BB313" s="3"/>
+    </row>
+    <row r="314" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -16704,8 +17999,12 @@
       <c r="AV314" s="3"/>
       <c r="AW314" s="3"/>
       <c r="AX314" s="3"/>
-    </row>
-    <row r="315" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY314" s="3"/>
+      <c r="AZ314" s="3"/>
+      <c r="BA314" s="3"/>
+      <c r="BB314" s="3"/>
+    </row>
+    <row r="315" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="3"/>
@@ -16754,8 +18053,12 @@
       <c r="AV315" s="3"/>
       <c r="AW315" s="3"/>
       <c r="AX315" s="3"/>
-    </row>
-    <row r="316" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY315" s="3"/>
+      <c r="AZ315" s="3"/>
+      <c r="BA315" s="3"/>
+      <c r="BB315" s="3"/>
+    </row>
+    <row r="316" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
@@ -16804,8 +18107,12 @@
       <c r="AV316" s="3"/>
       <c r="AW316" s="3"/>
       <c r="AX316" s="3"/>
-    </row>
-    <row r="317" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY316" s="3"/>
+      <c r="AZ316" s="3"/>
+      <c r="BA316" s="3"/>
+      <c r="BB316" s="3"/>
+    </row>
+    <row r="317" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
       <c r="E317" s="3"/>
@@ -16854,8 +18161,12 @@
       <c r="AV317" s="3"/>
       <c r="AW317" s="3"/>
       <c r="AX317" s="3"/>
-    </row>
-    <row r="318" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY317" s="3"/>
+      <c r="AZ317" s="3"/>
+      <c r="BA317" s="3"/>
+      <c r="BB317" s="3"/>
+    </row>
+    <row r="318" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
@@ -16904,8 +18215,12 @@
       <c r="AV318" s="3"/>
       <c r="AW318" s="3"/>
       <c r="AX318" s="3"/>
-    </row>
-    <row r="319" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY318" s="3"/>
+      <c r="AZ318" s="3"/>
+      <c r="BA318" s="3"/>
+      <c r="BB318" s="3"/>
+    </row>
+    <row r="319" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
       <c r="E319" s="3"/>
@@ -16954,8 +18269,12 @@
       <c r="AV319" s="3"/>
       <c r="AW319" s="3"/>
       <c r="AX319" s="3"/>
-    </row>
-    <row r="320" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY319" s="3"/>
+      <c r="AZ319" s="3"/>
+      <c r="BA319" s="3"/>
+      <c r="BB319" s="3"/>
+    </row>
+    <row r="320" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
       <c r="E320" s="3"/>
@@ -17004,8 +18323,12 @@
       <c r="AV320" s="3"/>
       <c r="AW320" s="3"/>
       <c r="AX320" s="3"/>
-    </row>
-    <row r="321" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY320" s="3"/>
+      <c r="AZ320" s="3"/>
+      <c r="BA320" s="3"/>
+      <c r="BB320" s="3"/>
+    </row>
+    <row r="321" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
       <c r="E321" s="3"/>
@@ -17054,8 +18377,12 @@
       <c r="AV321" s="3"/>
       <c r="AW321" s="3"/>
       <c r="AX321" s="3"/>
-    </row>
-    <row r="322" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY321" s="3"/>
+      <c r="AZ321" s="3"/>
+      <c r="BA321" s="3"/>
+      <c r="BB321" s="3"/>
+    </row>
+    <row r="322" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
       <c r="E322" s="3"/>
@@ -17104,8 +18431,12 @@
       <c r="AV322" s="3"/>
       <c r="AW322" s="3"/>
       <c r="AX322" s="3"/>
-    </row>
-    <row r="323" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY322" s="3"/>
+      <c r="AZ322" s="3"/>
+      <c r="BA322" s="3"/>
+      <c r="BB322" s="3"/>
+    </row>
+    <row r="323" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
       <c r="E323" s="3"/>
@@ -17154,8 +18485,12 @@
       <c r="AV323" s="3"/>
       <c r="AW323" s="3"/>
       <c r="AX323" s="3"/>
-    </row>
-    <row r="324" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY323" s="3"/>
+      <c r="AZ323" s="3"/>
+      <c r="BA323" s="3"/>
+      <c r="BB323" s="3"/>
+    </row>
+    <row r="324" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
       <c r="E324" s="3"/>
@@ -17204,8 +18539,12 @@
       <c r="AV324" s="3"/>
       <c r="AW324" s="3"/>
       <c r="AX324" s="3"/>
-    </row>
-    <row r="325" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY324" s="3"/>
+      <c r="AZ324" s="3"/>
+      <c r="BA324" s="3"/>
+      <c r="BB324" s="3"/>
+    </row>
+    <row r="325" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
       <c r="E325" s="3"/>
@@ -17254,8 +18593,12 @@
       <c r="AV325" s="3"/>
       <c r="AW325" s="3"/>
       <c r="AX325" s="3"/>
-    </row>
-    <row r="326" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY325" s="3"/>
+      <c r="AZ325" s="3"/>
+      <c r="BA325" s="3"/>
+      <c r="BB325" s="3"/>
+    </row>
+    <row r="326" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C326" s="3"/>
       <c r="D326" s="3"/>
       <c r="E326" s="3"/>
@@ -17304,8 +18647,12 @@
       <c r="AV326" s="3"/>
       <c r="AW326" s="3"/>
       <c r="AX326" s="3"/>
-    </row>
-    <row r="327" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY326" s="3"/>
+      <c r="AZ326" s="3"/>
+      <c r="BA326" s="3"/>
+      <c r="BB326" s="3"/>
+    </row>
+    <row r="327" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
       <c r="E327" s="3"/>
@@ -17354,8 +18701,12 @@
       <c r="AV327" s="3"/>
       <c r="AW327" s="3"/>
       <c r="AX327" s="3"/>
-    </row>
-    <row r="328" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY327" s="3"/>
+      <c r="AZ327" s="3"/>
+      <c r="BA327" s="3"/>
+      <c r="BB327" s="3"/>
+    </row>
+    <row r="328" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
       <c r="E328" s="3"/>
@@ -17404,8 +18755,12 @@
       <c r="AV328" s="3"/>
       <c r="AW328" s="3"/>
       <c r="AX328" s="3"/>
-    </row>
-    <row r="329" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY328" s="3"/>
+      <c r="AZ328" s="3"/>
+      <c r="BA328" s="3"/>
+      <c r="BB328" s="3"/>
+    </row>
+    <row r="329" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
       <c r="E329" s="3"/>
@@ -17454,8 +18809,12 @@
       <c r="AV329" s="3"/>
       <c r="AW329" s="3"/>
       <c r="AX329" s="3"/>
-    </row>
-    <row r="330" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY329" s="3"/>
+      <c r="AZ329" s="3"/>
+      <c r="BA329" s="3"/>
+      <c r="BB329" s="3"/>
+    </row>
+    <row r="330" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
       <c r="E330" s="3"/>
@@ -17504,8 +18863,12 @@
       <c r="AV330" s="3"/>
       <c r="AW330" s="3"/>
       <c r="AX330" s="3"/>
-    </row>
-    <row r="331" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY330" s="3"/>
+      <c r="AZ330" s="3"/>
+      <c r="BA330" s="3"/>
+      <c r="BB330" s="3"/>
+    </row>
+    <row r="331" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
       <c r="E331" s="3"/>
@@ -17554,8 +18917,12 @@
       <c r="AV331" s="3"/>
       <c r="AW331" s="3"/>
       <c r="AX331" s="3"/>
-    </row>
-    <row r="332" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY331" s="3"/>
+      <c r="AZ331" s="3"/>
+      <c r="BA331" s="3"/>
+      <c r="BB331" s="3"/>
+    </row>
+    <row r="332" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
       <c r="E332" s="3"/>
@@ -17604,8 +18971,12 @@
       <c r="AV332" s="3"/>
       <c r="AW332" s="3"/>
       <c r="AX332" s="3"/>
-    </row>
-    <row r="333" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY332" s="3"/>
+      <c r="AZ332" s="3"/>
+      <c r="BA332" s="3"/>
+      <c r="BB332" s="3"/>
+    </row>
+    <row r="333" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
       <c r="E333" s="3"/>
@@ -17654,8 +19025,12 @@
       <c r="AV333" s="3"/>
       <c r="AW333" s="3"/>
       <c r="AX333" s="3"/>
-    </row>
-    <row r="334" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY333" s="3"/>
+      <c r="AZ333" s="3"/>
+      <c r="BA333" s="3"/>
+      <c r="BB333" s="3"/>
+    </row>
+    <row r="334" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
       <c r="E334" s="3"/>
@@ -17704,8 +19079,12 @@
       <c r="AV334" s="3"/>
       <c r="AW334" s="3"/>
       <c r="AX334" s="3"/>
-    </row>
-    <row r="335" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY334" s="3"/>
+      <c r="AZ334" s="3"/>
+      <c r="BA334" s="3"/>
+      <c r="BB334" s="3"/>
+    </row>
+    <row r="335" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
       <c r="E335" s="3"/>
@@ -17754,8 +19133,12 @@
       <c r="AV335" s="3"/>
       <c r="AW335" s="3"/>
       <c r="AX335" s="3"/>
-    </row>
-    <row r="336" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY335" s="3"/>
+      <c r="AZ335" s="3"/>
+      <c r="BA335" s="3"/>
+      <c r="BB335" s="3"/>
+    </row>
+    <row r="336" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
       <c r="E336" s="3"/>
@@ -17804,8 +19187,12 @@
       <c r="AV336" s="3"/>
       <c r="AW336" s="3"/>
       <c r="AX336" s="3"/>
-    </row>
-    <row r="337" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY336" s="3"/>
+      <c r="AZ336" s="3"/>
+      <c r="BA336" s="3"/>
+      <c r="BB336" s="3"/>
+    </row>
+    <row r="337" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
       <c r="E337" s="3"/>
@@ -17854,8 +19241,12 @@
       <c r="AV337" s="3"/>
       <c r="AW337" s="3"/>
       <c r="AX337" s="3"/>
-    </row>
-    <row r="338" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY337" s="3"/>
+      <c r="AZ337" s="3"/>
+      <c r="BA337" s="3"/>
+      <c r="BB337" s="3"/>
+    </row>
+    <row r="338" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
       <c r="E338" s="3"/>
@@ -17904,8 +19295,12 @@
       <c r="AV338" s="3"/>
       <c r="AW338" s="3"/>
       <c r="AX338" s="3"/>
-    </row>
-    <row r="339" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY338" s="3"/>
+      <c r="AZ338" s="3"/>
+      <c r="BA338" s="3"/>
+      <c r="BB338" s="3"/>
+    </row>
+    <row r="339" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
       <c r="E339" s="3"/>
@@ -17954,8 +19349,12 @@
       <c r="AV339" s="3"/>
       <c r="AW339" s="3"/>
       <c r="AX339" s="3"/>
-    </row>
-    <row r="340" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY339" s="3"/>
+      <c r="AZ339" s="3"/>
+      <c r="BA339" s="3"/>
+      <c r="BB339" s="3"/>
+    </row>
+    <row r="340" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
       <c r="E340" s="3"/>
@@ -18004,8 +19403,12 @@
       <c r="AV340" s="3"/>
       <c r="AW340" s="3"/>
       <c r="AX340" s="3"/>
-    </row>
-    <row r="341" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY340" s="3"/>
+      <c r="AZ340" s="3"/>
+      <c r="BA340" s="3"/>
+      <c r="BB340" s="3"/>
+    </row>
+    <row r="341" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
       <c r="E341" s="3"/>
@@ -18054,8 +19457,12 @@
       <c r="AV341" s="3"/>
       <c r="AW341" s="3"/>
       <c r="AX341" s="3"/>
-    </row>
-    <row r="342" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY341" s="3"/>
+      <c r="AZ341" s="3"/>
+      <c r="BA341" s="3"/>
+      <c r="BB341" s="3"/>
+    </row>
+    <row r="342" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
       <c r="E342" s="3"/>
@@ -18104,8 +19511,12 @@
       <c r="AV342" s="3"/>
       <c r="AW342" s="3"/>
       <c r="AX342" s="3"/>
-    </row>
-    <row r="343" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY342" s="3"/>
+      <c r="AZ342" s="3"/>
+      <c r="BA342" s="3"/>
+      <c r="BB342" s="3"/>
+    </row>
+    <row r="343" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
       <c r="E343" s="3"/>
@@ -18154,8 +19565,12 @@
       <c r="AV343" s="3"/>
       <c r="AW343" s="3"/>
       <c r="AX343" s="3"/>
-    </row>
-    <row r="344" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY343" s="3"/>
+      <c r="AZ343" s="3"/>
+      <c r="BA343" s="3"/>
+      <c r="BB343" s="3"/>
+    </row>
+    <row r="344" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
       <c r="E344" s="3"/>
@@ -18204,8 +19619,12 @@
       <c r="AV344" s="3"/>
       <c r="AW344" s="3"/>
       <c r="AX344" s="3"/>
-    </row>
-    <row r="345" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY344" s="3"/>
+      <c r="AZ344" s="3"/>
+      <c r="BA344" s="3"/>
+      <c r="BB344" s="3"/>
+    </row>
+    <row r="345" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
       <c r="E345" s="3"/>
@@ -18254,8 +19673,12 @@
       <c r="AV345" s="3"/>
       <c r="AW345" s="3"/>
       <c r="AX345" s="3"/>
-    </row>
-    <row r="346" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY345" s="3"/>
+      <c r="AZ345" s="3"/>
+      <c r="BA345" s="3"/>
+      <c r="BB345" s="3"/>
+    </row>
+    <row r="346" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
       <c r="E346" s="3"/>
@@ -18304,8 +19727,12 @@
       <c r="AV346" s="3"/>
       <c r="AW346" s="3"/>
       <c r="AX346" s="3"/>
-    </row>
-    <row r="347" spans="3:50" x14ac:dyDescent="0.2">
+      <c r="AY346" s="3"/>
+      <c r="AZ346" s="3"/>
+      <c r="BA346" s="3"/>
+      <c r="BB346" s="3"/>
+    </row>
+    <row r="347" spans="3:54" x14ac:dyDescent="0.2">
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
       <c r="E347" s="3"/>
@@ -18354,56 +19781,10 @@
       <c r="AV347" s="3"/>
       <c r="AW347" s="3"/>
       <c r="AX347" s="3"/>
-    </row>
-    <row r="348" spans="3:50" x14ac:dyDescent="0.2">
-      <c r="C348" s="3"/>
-      <c r="D348" s="3"/>
-      <c r="E348" s="3"/>
-      <c r="F348" s="3"/>
-      <c r="G348" s="3"/>
-      <c r="H348" s="3"/>
-      <c r="I348" s="3"/>
-      <c r="J348" s="3"/>
-      <c r="K348" s="3"/>
-      <c r="L348" s="3"/>
-      <c r="M348" s="3"/>
-      <c r="N348" s="3"/>
-      <c r="O348" s="3"/>
-      <c r="P348" s="3"/>
-      <c r="Q348" s="3"/>
-      <c r="R348" s="3"/>
-      <c r="S348" s="3"/>
-      <c r="T348" s="3"/>
-      <c r="U348" s="3"/>
-      <c r="V348" s="3"/>
-      <c r="W348" s="3"/>
-      <c r="X348" s="3"/>
-      <c r="Y348" s="3"/>
-      <c r="Z348" s="3"/>
-      <c r="AA348" s="3"/>
-      <c r="AB348" s="3"/>
-      <c r="AC348" s="3"/>
-      <c r="AD348" s="3"/>
-      <c r="AE348" s="3"/>
-      <c r="AF348" s="3"/>
-      <c r="AG348" s="3"/>
-      <c r="AH348" s="3"/>
-      <c r="AI348" s="3"/>
-      <c r="AJ348" s="3"/>
-      <c r="AK348" s="3"/>
-      <c r="AL348" s="3"/>
-      <c r="AM348" s="3"/>
-      <c r="AN348" s="3"/>
-      <c r="AO348" s="3"/>
-      <c r="AP348" s="3"/>
-      <c r="AQ348" s="3"/>
-      <c r="AR348" s="3"/>
-      <c r="AS348" s="3"/>
-      <c r="AT348" s="3"/>
-      <c r="AU348" s="3"/>
-      <c r="AV348" s="3"/>
-      <c r="AW348" s="3"/>
-      <c r="AX348" s="3"/>
+      <c r="AY347" s="3"/>
+      <c r="AZ347" s="3"/>
+      <c r="BA347" s="3"/>
+      <c r="BB347" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
